--- a/COMISSÕES POR REGIAO.xlsx
+++ b/COMISSÕES POR REGIAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APRENDIZADO APP\MEDICOES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4541789-54FC-4E78-B124-F4765EE206B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17EFBF0-BD91-4258-B874-43319CCEDCC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" xr2:uid="{8E7E61FA-AA35-49DA-A0A0-B5261C3AB08E}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" xr2:uid="{8E7E61FA-AA35-49DA-A0A0-B5261C3AB08E}"/>
   </bookViews>
   <sheets>
     <sheet name="BAIXADA" sheetId="1" r:id="rId1"/>
@@ -3619,253 +3619,6 @@
     </dxf>
     <dxf>
       <font>
-        <sz val="10"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -4101,6 +3854,253 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4158,36 +4158,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}" name="TBL_BAIXADA" displayName="TBL_BAIXADA" ref="B2:G51" totalsRowShown="0" headerRowDxfId="50" dataDxfId="48" headerRowBorderDxfId="49" tableBorderDxfId="47" totalsRowBorderDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}" name="TBL_BAIXADA" displayName="TBL_BAIXADA" ref="B2:G51" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
   <autoFilter ref="B2:G51" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G50">
     <sortCondition ref="D2:D50"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="2" xr3:uid="{019F32D2-C233-43C9-9576-4AE595F1C1BA}" name="SEI" dataDxfId="45"/>
-    <tableColumn id="1" xr3:uid="{AEDA410C-7924-46EC-AEAB-7AE262BECCD2}" name="FISCAL NOMEADO" dataDxfId="44"/>
-    <tableColumn id="7" xr3:uid="{19466E79-BFE7-4E2E-A742-DD97531E2EF3}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{7880C9F9-C6BC-479F-9DA9-E17F6116251F}" name="STATUS" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{DA47CCE5-2317-4B1E-8640-27A34A02D8B9}" name="MUNICIPIO" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{DCC92333-101D-46D3-9AB3-309FAD98BBFB}" name="EMPRESA" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{019F32D2-C233-43C9-9576-4AE595F1C1BA}" name="SEI" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{AEDA410C-7924-46EC-AEAB-7AE262BECCD2}" name="FISCAL NOMEADO" dataDxfId="53"/>
+    <tableColumn id="7" xr3:uid="{19466E79-BFE7-4E2E-A742-DD97531E2EF3}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{7880C9F9-C6BC-479F-9DA9-E17F6116251F}" name="STATUS" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{DA47CCE5-2317-4B1E-8640-27A34A02D8B9}" name="MUNICIPIO" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{DCC92333-101D-46D3-9AB3-309FAD98BBFB}" name="EMPRESA" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}" name="Tabela2" displayName="Tabela2" ref="B2:G21" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58" tableBorderDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}" name="Tabela2" displayName="Tabela2" ref="B2:G21" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47" tableBorderDxfId="46">
   <autoFilter ref="B2:G21" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G20">
     <sortCondition ref="D2:D20"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{16E9EBD3-F35D-4598-A9F2-0A4D20432CE9}" name="SEI" dataDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{E30337A4-09C3-4048-9E77-97431DB2FF42}" name="FISCAL NOMEADO" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{E188BB43-7D82-4633-A725-9027F38B6D00}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="54"/>
-    <tableColumn id="4" xr3:uid="{8E3CCA43-C0CA-43A2-BFF6-C18CE15835DE}" name="STATUS" dataDxfId="53"/>
-    <tableColumn id="5" xr3:uid="{4BDB1FC4-3FA9-4D47-842C-749A9777B396}" name="MUNICIPIO" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{080468F4-AE50-4958-86EA-366972343A8C}" name="EMPRESA" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{16E9EBD3-F35D-4598-A9F2-0A4D20432CE9}" name="SEI" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{E30337A4-09C3-4048-9E77-97431DB2FF42}" name="FISCAL NOMEADO" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{E188BB43-7D82-4633-A725-9027F38B6D00}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{8E3CCA43-C0CA-43A2-BFF6-C18CE15835DE}" name="STATUS" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{4BDB1FC4-3FA9-4D47-842C-749A9777B396}" name="MUNICIPIO" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{080468F4-AE50-4958-86EA-366972343A8C}" name="EMPRESA" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4589,7 +4589,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69DBBD80-2FBA-444A-B434-052B47DD7E2E}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:S62"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
@@ -4602,7 +4602,7 @@
     <col min="8" max="8" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="100" t="s">
         <v>142</v>
@@ -4613,7 +4613,7 @@
       <c r="F1" s="101"/>
       <c r="G1" s="101"/>
     </row>
-    <row r="2" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B2" s="41" t="s">
         <v>35</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -4656,7 +4656,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4679,7 +4679,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -4701,12 +4701,8 @@
       <c r="G5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="S5">
-        <f>1331-2.43</f>
-        <v>1328.57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4729,7 +4725,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4752,7 +4748,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4775,7 +4771,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4798,7 +4794,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4821,7 +4817,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4844,7 +4840,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -4867,7 +4863,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -4890,7 +4886,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -4913,7 +4909,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -4936,7 +4932,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>

--- a/COMISSÕES POR REGIAO.xlsx
+++ b/COMISSÕES POR REGIAO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APRENDIZADO APP\MEDICOES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17EFBF0-BD91-4258-B874-43319CCEDCC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F85BCE3-E8F9-48E9-907D-22A0C9D82E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" xr2:uid="{8E7E61FA-AA35-49DA-A0A0-B5261C3AB08E}"/>
   </bookViews>
@@ -21,9 +21,9 @@
     <sheet name="AUXILIAR" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela111" hidden="1">Tabela11</definedName>
-    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela141" hidden="1">Tabela14</definedName>
-    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela61" hidden="1">Tabela6</definedName>
+    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela11" hidden="1">Tabela11</definedName>
+    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela14" hidden="1">Tabela14</definedName>
+    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela6" hidden="1">Tabela6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">BAIXADA!$B$1:$G$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">NORTE!$B$1:$G$23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">SUL!$B$1:$F$32</definedName>
@@ -286,7 +286,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Tabela11">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela111"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela11"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -295,7 +295,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Tabela14">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela141"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela14"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -304,7 +304,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Tabela6" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela61"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela6"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -4252,7 +4252,7 @@
   <autoFilter ref="A1:F130" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}">
     <filterColumn colId="0">
       <filters>
-        <filter val="330001/001081/2025"/>
+        <filter val="170026/001837/2022"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -8717,7 +8717,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>219</v>
       </c>
@@ -9183,7 +9183,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>275</v>
       </c>

--- a/COMISSÕES POR REGIAO.xlsx
+++ b/COMISSÕES POR REGIAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APRENDIZADO APP\MEDICOES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F85BCE3-E8F9-48E9-907D-22A0C9D82E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A278225-D55D-4E98-B593-04A004518304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" xr2:uid="{8E7E61FA-AA35-49DA-A0A0-B5261C3AB08E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" activeTab="4" xr2:uid="{8E7E61FA-AA35-49DA-A0A0-B5261C3AB08E}"/>
   </bookViews>
   <sheets>
     <sheet name="BAIXADA" sheetId="1" r:id="rId1"/>
@@ -21,9 +21,9 @@
     <sheet name="AUXILIAR" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela11" hidden="1">Tabela11</definedName>
-    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela14" hidden="1">Tabela14</definedName>
-    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela6" hidden="1">Tabela6</definedName>
+    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela111" hidden="1">Tabela11</definedName>
+    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela141" hidden="1">Tabela14</definedName>
+    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela61" hidden="1">Tabela6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">BAIXADA!$B$1:$G$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">NORTE!$B$1:$G$23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">SUL!$B$1:$F$32</definedName>
@@ -286,7 +286,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Tabela11">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela11"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela111"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -295,7 +295,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Tabela14">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela14"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela141"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -304,7 +304,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Tabela6" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela6"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela61"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -4159,7 +4159,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}" name="TBL_BAIXADA" displayName="TBL_BAIXADA" ref="B2:G51" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
-  <autoFilter ref="B2:G51" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}"/>
+  <autoFilter ref="B2:G51" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="CARLOS FERNANDES"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G50">
     <sortCondition ref="D2:D50"/>
   </sortState>
@@ -4249,13 +4255,7 @@
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}" name="TBL_AUX_COMISSAO" displayName="TBL_AUX_COMISSAO" ref="A1:F130" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:F130" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="170026/001837/2022"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F130" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F121">
     <sortCondition ref="A1:A124"/>
   </sortState>
@@ -4656,7 +4656,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4679,7 +4679,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -4725,7 +4725,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -4932,7 +4932,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -4978,7 +4978,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -5024,7 +5024,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -5484,7 +5484,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -5553,7 +5553,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -5576,7 +5576,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -5599,7 +5599,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -5622,7 +5622,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -5645,7 +5645,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -5691,7 +5691,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -5714,7 +5714,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -5737,6 +5737,7 @@
         <v>86</v>
       </c>
     </row>
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="59" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="G59" s="74"/>
     </row>
@@ -8116,7 +8117,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>189</v>
       </c>
@@ -8150,7 +8151,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>106</v>
       </c>
@@ -8177,7 +8178,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>52</v>
       </c>
@@ -8204,7 +8205,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>102</v>
       </c>
@@ -8231,7 +8232,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>213</v>
       </c>
@@ -8258,7 +8259,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>176</v>
       </c>
@@ -8285,7 +8286,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>181</v>
       </c>
@@ -8312,7 +8313,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>209</v>
       </c>
@@ -8339,7 +8340,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>168</v>
       </c>
@@ -8366,7 +8367,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>182</v>
       </c>
@@ -8393,7 +8394,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>212</v>
       </c>
@@ -8420,7 +8421,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>119</v>
       </c>
@@ -8447,7 +8448,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>262</v>
       </c>
@@ -8474,7 +8475,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>172</v>
       </c>
@@ -8501,7 +8502,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>80</v>
       </c>
@@ -8528,7 +8529,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>250</v>
       </c>
@@ -8555,7 +8556,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>113</v>
       </c>
@@ -8582,7 +8583,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>165</v>
       </c>
@@ -8609,7 +8610,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>10</v>
       </c>
@@ -8636,7 +8637,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>79</v>
       </c>
@@ -8663,7 +8664,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>132</v>
       </c>
@@ -8690,7 +8691,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>152</v>
       </c>
@@ -8744,7 +8745,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>169</v>
       </c>
@@ -8771,7 +8772,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>116</v>
       </c>
@@ -8798,7 +8799,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>78</v>
       </c>
@@ -8825,7 +8826,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>145</v>
       </c>
@@ -8852,7 +8853,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>21</v>
       </c>
@@ -8879,7 +8880,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>170</v>
       </c>
@@ -8906,7 +8907,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>51</v>
       </c>
@@ -8933,7 +8934,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>240</v>
       </c>
@@ -8960,7 +8961,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>233</v>
       </c>
@@ -8987,7 +8988,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>269</v>
       </c>
@@ -9021,7 +9022,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>171</v>
       </c>
@@ -9048,7 +9049,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>274</v>
       </c>
@@ -9075,7 +9076,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>221</v>
       </c>
@@ -9102,7 +9103,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>265</v>
       </c>
@@ -9129,7 +9130,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>174</v>
       </c>
@@ -9156,7 +9157,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>96</v>
       </c>
@@ -9183,7 +9184,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>275</v>
       </c>
@@ -9210,7 +9211,7 @@
         <v>CONTINGENCIA</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>266</v>
       </c>
@@ -9237,7 +9238,7 @@
         <v>CONTINGENCIA</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>245</v>
       </c>
@@ -9264,7 +9265,7 @@
         <v>CONTINGENCIA</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>277</v>
       </c>
@@ -9291,7 +9292,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>261</v>
       </c>
@@ -9318,7 +9319,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>211</v>
       </c>
@@ -9345,7 +9346,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>223</v>
       </c>
@@ -9372,7 +9373,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>155</v>
       </c>
@@ -9399,7 +9400,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>153</v>
       </c>
@@ -9426,7 +9427,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>104</v>
       </c>
@@ -9453,7 +9454,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>154</v>
       </c>
@@ -9480,7 +9481,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>120</v>
       </c>
@@ -9507,7 +9508,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>164</v>
       </c>
@@ -9534,7 +9535,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>151</v>
       </c>
@@ -9561,7 +9562,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>128</v>
       </c>
@@ -9588,7 +9589,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>259</v>
       </c>
@@ -9615,7 +9616,7 @@
         <v>CONTINGENCIA</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>81</v>
       </c>
@@ -9642,7 +9643,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>161</v>
       </c>
@@ -9669,7 +9670,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>83</v>
       </c>
@@ -9696,7 +9697,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>30</v>
       </c>
@@ -9723,7 +9724,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>136</v>
       </c>
@@ -9750,7 +9751,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>162</v>
       </c>
@@ -9777,7 +9778,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>121</v>
       </c>
@@ -9804,7 +9805,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>156</v>
       </c>
@@ -9831,7 +9832,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>134</v>
       </c>
@@ -9858,7 +9859,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>157</v>
       </c>
@@ -9892,7 +9893,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>82</v>
       </c>
@@ -9919,7 +9920,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>8</v>
       </c>
@@ -9946,7 +9947,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>16</v>
       </c>
@@ -9973,7 +9974,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>17</v>
       </c>
@@ -10000,7 +10001,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>19</v>
       </c>
@@ -10027,7 +10028,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>135</v>
       </c>
@@ -10054,7 +10055,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>158</v>
       </c>
@@ -10081,7 +10082,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>159</v>
       </c>
@@ -10108,7 +10109,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>160</v>
       </c>
@@ -10135,7 +10136,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>7</v>
       </c>
@@ -10162,7 +10163,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>24</v>
       </c>
@@ -10189,7 +10190,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>94</v>
       </c>
@@ -10216,7 +10217,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>26</v>
       </c>
@@ -10243,7 +10244,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>22</v>
       </c>
@@ -10270,7 +10271,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>133</v>
       </c>
@@ -10297,7 +10298,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>5</v>
       </c>
@@ -10324,7 +10325,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>27</v>
       </c>
@@ -10351,7 +10352,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>34</v>
       </c>
@@ -10378,7 +10379,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>0</v>
       </c>
@@ -10405,7 +10406,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>32</v>
       </c>
@@ -10432,7 +10433,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>147</v>
       </c>
@@ -10459,7 +10460,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>29</v>
       </c>
@@ -10486,7 +10487,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>14</v>
       </c>
@@ -10513,7 +10514,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>12</v>
       </c>
@@ -10540,7 +10541,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>111</v>
       </c>
@@ -10567,7 +10568,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>146</v>
       </c>
@@ -10594,7 +10595,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>236</v>
       </c>
@@ -10621,7 +10622,7 @@
         <v>CONTINGENCIA</v>
       </c>
     </row>
-    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>242</v>
       </c>
@@ -10648,7 +10649,7 @@
         <v>CONTINGENCIA</v>
       </c>
     </row>
-    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>2</v>
       </c>
@@ -10675,7 +10676,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>248</v>
       </c>
@@ -10702,7 +10703,7 @@
         <v>CONTINGENCIA</v>
       </c>
     </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>4</v>
       </c>
@@ -10729,7 +10730,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>173</v>
       </c>
@@ -10763,7 +10764,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>115</v>
       </c>
@@ -10790,7 +10791,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>175</v>
       </c>
@@ -10817,7 +10818,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>226</v>
       </c>
@@ -10844,7 +10845,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>180</v>
       </c>
@@ -10871,7 +10872,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>215</v>
       </c>
@@ -10898,7 +10899,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>256</v>
       </c>
@@ -10925,7 +10926,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>163</v>
       </c>
@@ -10952,7 +10953,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>143</v>
       </c>
@@ -10979,7 +10980,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>183</v>
       </c>
@@ -11006,7 +11007,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>191</v>
       </c>
@@ -11033,7 +11034,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>218</v>
       </c>
@@ -11060,7 +11061,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>217</v>
       </c>
@@ -11087,7 +11088,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>184</v>
       </c>
@@ -11114,7 +11115,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>185</v>
       </c>
@@ -11141,7 +11142,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>186</v>
       </c>
@@ -11168,7 +11169,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>255</v>
       </c>
@@ -11195,7 +11196,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
         <v>257</v>
       </c>
@@ -11222,7 +11223,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>187</v>
       </c>
@@ -11249,7 +11250,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>188</v>
       </c>
@@ -11276,7 +11277,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>230</v>
       </c>
@@ -11303,7 +11304,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>251</v>
       </c>
@@ -11330,7 +11331,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>144</v>
       </c>
@@ -11357,7 +11358,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>281</v>
       </c>
@@ -11384,7 +11385,7 @@
         <v>CONTINGENCIA</v>
       </c>
     </row>
-    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>190</v>
       </c>
@@ -11411,7 +11412,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>192</v>
       </c>
@@ -11438,7 +11439,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>224</v>
       </c>
@@ -11465,7 +11466,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="16" t="s">
         <v>287</v>
       </c>
@@ -11492,7 +11493,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="24" t="s">
         <v>289</v>
       </c>
@@ -11519,7 +11520,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="24" t="s">
         <v>339</v>
       </c>
@@ -11546,7 +11547,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="24" t="s">
         <v>341</v>
       </c>
@@ -11573,7 +11574,7 @@
         <v>CIVIS</v>
       </c>
     </row>
-    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="24" t="s">
         <v>343</v>
       </c>
@@ -11600,7 +11601,7 @@
         <v>ESPECIAIS</v>
       </c>
     </row>
-    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="24" t="s">
         <v>345</v>
       </c>

--- a/COMISSÕES POR REGIAO.xlsx
+++ b/COMISSÕES POR REGIAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APRENDIZADO APP\MEDICOES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A278225-D55D-4E98-B593-04A004518304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BC49D8-30B8-4930-84CC-31AD6CF13773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" activeTab="4" xr2:uid="{8E7E61FA-AA35-49DA-A0A0-B5261C3AB08E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" activeTab="2" xr2:uid="{8E7E61FA-AA35-49DA-A0A0-B5261C3AB08E}"/>
   </bookViews>
   <sheets>
     <sheet name="BAIXADA" sheetId="1" r:id="rId1"/>
@@ -2284,7 +2284,7 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2364,12 +2364,6 @@
     </xf>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2496,9 +2490,6 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="25" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="44" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2534,9 +2525,6 @@
     <xf numFmtId="1" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="25" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2546,6 +2534,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="62">
@@ -2614,86 +2605,25 @@
   </cellStyles>
   <dxfs count="61">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -2706,19 +2636,12 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <font>
+        <sz val="10"/>
+        <color auto="1"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2728,113 +2651,6 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
         <bottom/>
       </border>
     </dxf>
@@ -2857,108 +2673,7 @@
       </font>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
+        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -2987,25 +2702,21 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
       <border diagonalUp="0" diagonalDown="0">
-        <left/>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -3015,8 +2726,149 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -3043,6 +2895,18 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
@@ -3050,29 +2914,7 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3214,56 +3056,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color auto="1"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -4119,6 +3911,203 @@
       <font>
         <b val="0"/>
         <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
       </font>
       <border>
         <left style="medium">
@@ -4158,7 +4147,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}" name="TBL_BAIXADA" displayName="TBL_BAIXADA" ref="B2:G51" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}" name="TBL_BAIXADA" displayName="TBL_BAIXADA" ref="B2:G51" totalsRowShown="0" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="47">
   <autoFilter ref="B2:G51" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}">
     <filterColumn colId="2">
       <filters>
@@ -4170,119 +4159,119 @@
     <sortCondition ref="D2:D50"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="2" xr3:uid="{019F32D2-C233-43C9-9576-4AE595F1C1BA}" name="SEI" dataDxfId="54"/>
-    <tableColumn id="1" xr3:uid="{AEDA410C-7924-46EC-AEAB-7AE262BECCD2}" name="FISCAL NOMEADO" dataDxfId="53"/>
-    <tableColumn id="7" xr3:uid="{19466E79-BFE7-4E2E-A742-DD97531E2EF3}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{7880C9F9-C6BC-479F-9DA9-E17F6116251F}" name="STATUS" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{DA47CCE5-2317-4B1E-8640-27A34A02D8B9}" name="MUNICIPIO" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{DCC92333-101D-46D3-9AB3-309FAD98BBFB}" name="EMPRESA" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{019F32D2-C233-43C9-9576-4AE595F1C1BA}" name="SEI" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{AEDA410C-7924-46EC-AEAB-7AE262BECCD2}" name="FISCAL NOMEADO" dataDxfId="45"/>
+    <tableColumn id="7" xr3:uid="{19466E79-BFE7-4E2E-A742-DD97531E2EF3}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{7880C9F9-C6BC-479F-9DA9-E17F6116251F}" name="STATUS" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{DA47CCE5-2317-4B1E-8640-27A34A02D8B9}" name="MUNICIPIO" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{DCC92333-101D-46D3-9AB3-309FAD98BBFB}" name="EMPRESA" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}" name="Tabela2" displayName="Tabela2" ref="B2:G21" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47" tableBorderDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}" name="Tabela2" displayName="Tabela2" ref="B2:G21" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" tableBorderDxfId="38">
   <autoFilter ref="B2:G21" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G20">
     <sortCondition ref="D2:D20"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{16E9EBD3-F35D-4598-A9F2-0A4D20432CE9}" name="SEI" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{E30337A4-09C3-4048-9E77-97431DB2FF42}" name="FISCAL NOMEADO" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{E188BB43-7D82-4633-A725-9027F38B6D00}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{8E3CCA43-C0CA-43A2-BFF6-C18CE15835DE}" name="STATUS" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{4BDB1FC4-3FA9-4D47-842C-749A9777B396}" name="MUNICIPIO" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{080468F4-AE50-4958-86EA-366972343A8C}" name="EMPRESA" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{16E9EBD3-F35D-4598-A9F2-0A4D20432CE9}" name="SEI" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{E30337A4-09C3-4048-9E77-97431DB2FF42}" name="FISCAL NOMEADO" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{E188BB43-7D82-4633-A725-9027F38B6D00}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{8E3CCA43-C0CA-43A2-BFF6-C18CE15835DE}" name="STATUS" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{4BDB1FC4-3FA9-4D47-842C-749A9777B396}" name="MUNICIPIO" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{080468F4-AE50-4958-86EA-366972343A8C}" name="EMPRESA" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B825E509-0D21-4897-AEA1-45396A5B8904}" name="Tabela3" displayName="Tabela3" ref="B2:G31" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38" tableBorderDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B825E509-0D21-4897-AEA1-45396A5B8904}" name="Tabela3" displayName="Tabela3" ref="B2:G31" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30" tableBorderDxfId="29">
   <autoFilter ref="B2:G31" xr:uid="{B825E509-0D21-4897-AEA1-45396A5B8904}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G31">
     <sortCondition ref="D2:D31"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{AF3D376D-5669-42C7-85B7-D133DE0C7C9F}" name="SEI" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{51805C44-CC05-4045-9BCE-C493679844E5}" name="FISCAL NOMEADO" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{5E18CB63-80F1-40CE-AC25-4FF6D6C56801}" name="GESTOR(A) ATUANTE" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{8A899838-F31E-4B62-AD60-CACBA61F7301}" name="STATUS" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{A189C6A4-301D-4BC4-893D-C571D3C65C4F}" name="MUNICIPIO" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{1FE96F05-55E0-47E2-950A-C4FE6590F71E}" name="EMPRESA" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{AF3D376D-5669-42C7-85B7-D133DE0C7C9F}" name="SEI" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{51805C44-CC05-4045-9BCE-C493679844E5}" name="FISCAL NOMEADO" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{5E18CB63-80F1-40CE-AC25-4FF6D6C56801}" name="GESTOR(A) ATUANTE" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{8A899838-F31E-4B62-AD60-CACBA61F7301}" name="STATUS" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{A189C6A4-301D-4BC4-893D-C571D3C65C4F}" name="MUNICIPIO" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{1FE96F05-55E0-47E2-950A-C4FE6590F71E}" name="EMPRESA" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{07EEB8F3-2A08-4F77-A71A-F14F310E745B}" name="Tabela59" displayName="Tabela59" ref="B2:G21" totalsRowShown="0" headerRowDxfId="30" headerRowBorderDxfId="29" tableBorderDxfId="28" totalsRowBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{07EEB8F3-2A08-4F77-A71A-F14F310E745B}" name="Tabela59" displayName="Tabela59" ref="B2:G21" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
   <autoFilter ref="B2:G21" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:G10">
     <sortCondition ref="D2:D21"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{1B0B707C-42D7-439C-BC86-F2074086CDFA}" name="SEI" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{E4E4A98E-5F6A-4D1A-BF5C-90DB3AF4D029}" name="FISCAL NOMEADO" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{3F530A0F-746C-40A5-87E4-3EF4BC754B35}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{6289C995-291C-4CD2-9F38-F7B7C1C4C572}" name="STATUS" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{C32C9B37-692D-406F-BC6A-231C43E51674}" name="MUNICIPIO" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{AEFC288F-DB80-4821-8DAC-8848204495B7}" name="EMPRESA" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{1B0B707C-42D7-439C-BC86-F2074086CDFA}" name="SEI" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{E4E4A98E-5F6A-4D1A-BF5C-90DB3AF4D029}" name="FISCAL NOMEADO" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{3F530A0F-746C-40A5-87E4-3EF4BC754B35}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{6289C995-291C-4CD2-9F38-F7B7C1C4C572}" name="STATUS" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{C32C9B37-692D-406F-BC6A-231C43E51674}" name="MUNICIPIO" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{AEFC288F-DB80-4821-8DAC-8848204495B7}" name="EMPRESA" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}" name="Tabela5" displayName="Tabela5" ref="B2:G27" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}" name="Tabela5" displayName="Tabela5" ref="B2:G27" totalsRowShown="0" headerRowDxfId="59" headerRowBorderDxfId="58" tableBorderDxfId="57" totalsRowBorderDxfId="56">
   <autoFilter ref="B2:G27" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:G23">
     <sortCondition ref="D2:D26"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8FECF49A-25BA-405F-A561-286D71FB284B}" name="SEI" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{88A1DC3F-1E69-48FA-B7AB-F895C771F55E}" name="FISCAL NOMEADO" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{B977B564-9125-4E72-A174-DD668115187D}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{6A4D0185-1909-4BA9-A2C1-58CDBA8CD45C}" name="STATUS" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{539417AD-B8A4-4898-AB74-66F05A603AF4}" name="MUNICIPIO" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{235BE65E-B850-4BB7-8E87-322FA0E9FAE2}" name="EMPRESA" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{8FECF49A-25BA-405F-A561-286D71FB284B}" name="SEI" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{88A1DC3F-1E69-48FA-B7AB-F895C771F55E}" name="FISCAL NOMEADO" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{B977B564-9125-4E72-A174-DD668115187D}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="55"/>
+    <tableColumn id="4" xr3:uid="{6A4D0185-1909-4BA9-A2C1-58CDBA8CD45C}" name="STATUS" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{539417AD-B8A4-4898-AB74-66F05A603AF4}" name="MUNICIPIO" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{235BE65E-B850-4BB7-8E87-322FA0E9FAE2}" name="EMPRESA" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}" name="TBL_AUX_COMISSAO" displayName="TBL_AUX_COMISSAO" ref="A1:F130" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}" name="TBL_AUX_COMISSAO" displayName="TBL_AUX_COMISSAO" ref="A1:F130" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="A1:F130" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F121">
     <sortCondition ref="A1:A124"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6940CE63-D3EF-4410-99DC-5338DACC9347}" name="SEI" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{BC273B88-930A-4795-B862-FBC8E6F6BDFE}" name="GESTOR" dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{6940CE63-D3EF-4410-99DC-5338DACC9347}" name="SEI" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{BC273B88-930A-4795-B862-FBC8E6F6BDFE}" name="GESTOR" dataDxfId="8">
       <calculatedColumnFormula>UPPER(TRIM(UPPER(IFERROR(VLOOKUP(A2,INDIRECT("'BAIXADA'!$B$3:$I$51"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'NORTE'!$B$3:$I$21"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'SUL'!$B$3:$I$31"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'CONTIGENCIA'!$B$3:$I$22"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'ESPECIAIS'!$B$3:$I$27"),3,FALSE),""))))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2DD541AF-D366-4FA1-934F-2D706DEB3424}" name="REGIAO" dataDxfId="3">
+    <tableColumn id="3" xr3:uid="{2DD541AF-D366-4FA1-934F-2D706DEB3424}" name="REGIAO" dataDxfId="7">
       <calculatedColumnFormula>IF(OR(B2="CARLOS FERNANDES", B2="GISELLE G. FONSECA"), "BAIXADA",
  IF(OR(B2="ISADORA ROSALINO", B2="JEHNIFFER PIRES"), "NORTE",
  IF(OR(B2="LUIZ FILHO", B2="MARCUS", B2="JAQUELINE PASTÓRIO"), "SUL",
  IF(OR(B2="AIMAR FILHO", B2="ERICK HYLARIO", B2="IGOR CARNEIRO", B2="CESAR", B2="DANRLEI"), "ESPECIAIS",""))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{48CC14BF-DA39-4E7A-9D30-3BF4E557740A}" name="Coluna1" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{73F6C358-23B2-4118-8542-3EF0D7731680}" name="STATUS" dataDxfId="1">
+    <tableColumn id="4" xr3:uid="{48CC14BF-DA39-4E7A-9D30-3BF4E557740A}" name="Coluna1" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{73F6C358-23B2-4118-8542-3EF0D7731680}" name="STATUS" dataDxfId="5">
       <calculatedColumnFormula>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela59[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{42155D96-D90A-49EF-9ADB-3B70FF87E628}" name="LOCAL" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{42155D96-D90A-49EF-9ADB-3B70FF87E628}" name="LOCAL" dataDxfId="4">
       <calculatedColumnFormula>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A2),COUNTIF(NORTE!B:B,A2),COUNTIF(SUL!B:B,A2))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A2)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A2)&gt;0,"ESPECIAIS",""))))</calculatedColumnFormula>
     </tableColumn>
@@ -4604,32 +4593,32 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
-      <c r="B1" s="100" t="s">
+      <c r="B1" s="96" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
     </row>
     <row r="2" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="39" t="s">
         <v>228</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="40" t="s">
         <v>229</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="39" t="s">
         <v>49</v>
       </c>
     </row>
@@ -4669,7 +4658,7 @@
       <c r="D4" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="34" t="s">
         <v>193</v>
       </c>
       <c r="F4" s="7" t="s">
@@ -4715,7 +4704,7 @@
       <c r="D6" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="E6" s="55" t="s">
+      <c r="E6" s="53" t="s">
         <v>194</v>
       </c>
       <c r="F6" s="7" t="s">
@@ -4738,7 +4727,7 @@
       <c r="D7" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E7" s="55" t="s">
+      <c r="E7" s="53" t="s">
         <v>194</v>
       </c>
       <c r="F7" s="7" t="s">
@@ -4761,7 +4750,7 @@
       <c r="D8" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="34" t="s">
         <v>193</v>
       </c>
       <c r="F8" s="7" t="s">
@@ -4853,7 +4842,7 @@
       <c r="D12" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E12" s="36" t="s">
+      <c r="E12" s="34" t="s">
         <v>193</v>
       </c>
       <c r="F12" s="7" t="s">
@@ -4876,7 +4865,7 @@
       <c r="D13" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="E13" s="72" t="s">
+      <c r="E13" s="70" t="s">
         <v>254</v>
       </c>
       <c r="F13" s="7" t="s">
@@ -4899,7 +4888,7 @@
       <c r="D14" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="E14" s="36" t="s">
+      <c r="E14" s="34" t="s">
         <v>193</v>
       </c>
       <c r="F14" s="7" t="s">
@@ -4922,7 +4911,7 @@
       <c r="D15" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="E15" s="36" t="s">
+      <c r="E15" s="34" t="s">
         <v>193</v>
       </c>
       <c r="F15" s="7" t="s">
@@ -4968,7 +4957,7 @@
       <c r="D17" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="E17" s="72" t="s">
+      <c r="E17" s="70" t="s">
         <v>194</v>
       </c>
       <c r="F17" s="7" t="s">
@@ -4991,7 +4980,7 @@
       <c r="D18" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="E18" s="34" t="s">
         <v>193</v>
       </c>
       <c r="F18" s="7" t="s">
@@ -5014,7 +5003,7 @@
       <c r="D19" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="E19" s="36" t="s">
+      <c r="E19" s="34" t="s">
         <v>193</v>
       </c>
       <c r="F19" s="8" t="s">
@@ -5037,7 +5026,7 @@
       <c r="D20" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="36" t="s">
+      <c r="E20" s="34" t="s">
         <v>193</v>
       </c>
       <c r="F20" s="7" t="s">
@@ -5060,7 +5049,7 @@
       <c r="D21" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E21" s="36" t="s">
+      <c r="E21" s="34" t="s">
         <v>193</v>
       </c>
       <c r="F21" s="7" t="s">
@@ -5106,7 +5095,7 @@
       <c r="D23" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E23" s="72" t="s">
+      <c r="E23" s="70" t="s">
         <v>254</v>
       </c>
       <c r="F23" s="7" t="s">
@@ -5175,7 +5164,7 @@
       <c r="D26" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="E26" s="36" t="s">
+      <c r="E26" s="34" t="s">
         <v>193</v>
       </c>
       <c r="F26" s="7" t="s">
@@ -5221,7 +5210,7 @@
       <c r="D28" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E28" s="36" t="s">
+      <c r="E28" s="34" t="s">
         <v>193</v>
       </c>
       <c r="F28" s="7" t="s">
@@ -5336,7 +5325,7 @@
       <c r="D33" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E33" s="55" t="s">
+      <c r="E33" s="53" t="s">
         <v>125</v>
       </c>
       <c r="F33" s="7" t="s">
@@ -5359,7 +5348,7 @@
       <c r="D34" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E34" s="36" t="s">
+      <c r="E34" s="34" t="s">
         <v>194</v>
       </c>
       <c r="F34" s="7" t="s">
@@ -5451,7 +5440,7 @@
       <c r="D38" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E38" s="36" t="s">
+      <c r="E38" s="34" t="s">
         <v>193</v>
       </c>
       <c r="F38" s="23" t="s">
@@ -5540,7 +5529,7 @@
       <c r="C42" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="D42" s="53" t="s">
+      <c r="D42" s="51" t="s">
         <v>286</v>
       </c>
       <c r="E42" s="31" t="s">
@@ -5563,10 +5552,10 @@
       <c r="C43" s="23" t="s">
         <v>284</v>
       </c>
-      <c r="D43" s="54" t="s">
+      <c r="D43" s="52" t="s">
         <v>304</v>
       </c>
-      <c r="E43" s="36" t="s">
+      <c r="E43" s="34" t="s">
         <v>193</v>
       </c>
       <c r="F43" s="23" t="s">
@@ -5589,7 +5578,7 @@
       <c r="D44" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="E44" s="94" t="s">
+      <c r="E44" s="91" t="s">
         <v>64</v>
       </c>
       <c r="F44" s="23" t="s">
@@ -5672,7 +5661,7 @@
       <c r="A48" s="1">
         <v>46</v>
       </c>
-      <c r="B48" s="52" t="s">
+      <c r="B48" s="50" t="s">
         <v>30</v>
       </c>
       <c r="C48" s="7" t="s">
@@ -5684,10 +5673,10 @@
       <c r="E48" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="F48" s="56" t="s">
+      <c r="F48" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G48" s="56" t="s">
+      <c r="G48" s="54" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5739,13 +5728,13 @@
     </row>
     <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="59" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="G59" s="74"/>
+      <c r="G59" s="72"/>
     </row>
     <row r="60" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="G60" s="74"/>
+      <c r="G60" s="72"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G62" s="75"/>
+      <c r="G62" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5780,24 +5769,24 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
-      <c r="B1" s="100" t="s">
+      <c r="B1" s="96" t="s">
         <v>122</v>
       </c>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
     </row>
     <row r="2" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="42" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="41" t="s">
         <v>229</v>
       </c>
       <c r="E2" s="12" t="s">
@@ -5806,7 +5795,7 @@
       <c r="F2" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="45" t="s">
+      <c r="G2" s="43" t="s">
         <v>49</v>
       </c>
     </row>
@@ -5814,13 +5803,13 @@
       <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="55" t="s">
         <v>156</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="71" t="s">
         <v>301</v>
       </c>
-      <c r="D3" s="58" t="s">
+      <c r="D3" s="56" t="s">
         <v>305</v>
       </c>
       <c r="E3" s="8" t="s">
@@ -5829,7 +5818,7 @@
       <c r="F3" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="61" t="s">
+      <c r="G3" s="59" t="s">
         <v>57</v>
       </c>
     </row>
@@ -5837,13 +5826,13 @@
       <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="56" t="s">
         <v>324</v>
       </c>
-      <c r="D4" s="58" t="s">
+      <c r="D4" s="56" t="s">
         <v>286</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -5852,7 +5841,7 @@
       <c r="F4" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="59" t="s">
+      <c r="G4" s="57" t="s">
         <v>56</v>
       </c>
     </row>
@@ -5860,13 +5849,13 @@
       <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="C5" s="73" t="s">
+      <c r="C5" s="71" t="s">
         <v>301</v>
       </c>
-      <c r="D5" s="58" t="s">
+      <c r="D5" s="56" t="s">
         <v>305</v>
       </c>
       <c r="E5" s="8" t="s">
@@ -5875,7 +5864,7 @@
       <c r="F5" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="G5" s="59" t="s">
+      <c r="G5" s="57" t="s">
         <v>59</v>
       </c>
     </row>
@@ -5883,13 +5872,13 @@
       <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B6" s="81" t="s">
+      <c r="B6" s="79" t="s">
         <v>159</v>
       </c>
-      <c r="C6" s="73" t="s">
+      <c r="C6" s="71" t="s">
         <v>301</v>
       </c>
-      <c r="D6" s="73" t="s">
+      <c r="D6" s="71" t="s">
         <v>305</v>
       </c>
       <c r="E6" s="27" t="s">
@@ -5898,7 +5887,7 @@
       <c r="F6" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="G6" s="59" t="s">
+      <c r="G6" s="57" t="s">
         <v>60</v>
       </c>
     </row>
@@ -5906,13 +5895,13 @@
       <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="B7" s="81" t="s">
+      <c r="B7" s="79" t="s">
         <v>160</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="C7" s="71" t="s">
         <v>301</v>
       </c>
-      <c r="D7" s="73" t="s">
+      <c r="D7" s="71" t="s">
         <v>305</v>
       </c>
       <c r="E7" s="27" t="s">
@@ -5921,7 +5910,7 @@
       <c r="F7" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="61" t="s">
+      <c r="G7" s="59" t="s">
         <v>61</v>
       </c>
     </row>
@@ -5929,22 +5918,22 @@
       <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="56" t="s">
         <v>320</v>
       </c>
-      <c r="D8" s="73" t="s">
+      <c r="D8" s="71" t="s">
         <v>306</v>
       </c>
-      <c r="E8" s="88" t="s">
+      <c r="E8" s="85" t="s">
         <v>194</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="G8" s="59" t="s">
+      <c r="G8" s="57" t="s">
         <v>123</v>
       </c>
     </row>
@@ -5952,22 +5941,22 @@
       <c r="A9" s="5">
         <v>7</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="55" t="s">
         <v>164</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="56" t="s">
         <v>302</v>
       </c>
-      <c r="D9" s="58" t="s">
+      <c r="D9" s="56" t="s">
         <v>305</v>
       </c>
-      <c r="E9" s="88" t="s">
+      <c r="E9" s="85" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="60" t="s">
+      <c r="F9" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="G9" s="61" t="s">
+      <c r="G9" s="59" t="s">
         <v>74</v>
       </c>
     </row>
@@ -5975,22 +5964,22 @@
       <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="55" t="s">
         <v>151</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="56" t="s">
         <v>319</v>
       </c>
-      <c r="D10" s="58" t="s">
+      <c r="D10" s="56" t="s">
         <v>305</v>
       </c>
-      <c r="E10" s="89" t="s">
+      <c r="E10" s="86" t="s">
         <v>193</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="59" t="s">
+      <c r="G10" s="57" t="s">
         <v>127</v>
       </c>
     </row>
@@ -5998,22 +5987,22 @@
       <c r="A11" s="5">
         <v>9</v>
       </c>
-      <c r="B11" s="57" t="s">
+      <c r="B11" s="55" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="56" t="s">
         <v>319</v>
       </c>
-      <c r="D11" s="58" t="s">
+      <c r="D11" s="56" t="s">
         <v>305</v>
       </c>
-      <c r="E11" s="60" t="s">
+      <c r="E11" s="58" t="s">
         <v>193</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="G11" s="59" t="s">
+      <c r="G11" s="57" t="s">
         <v>130</v>
       </c>
     </row>
@@ -6021,13 +6010,13 @@
       <c r="A12" s="5">
         <v>10</v>
       </c>
-      <c r="B12" s="81" t="s">
+      <c r="B12" s="79" t="s">
         <v>152</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="C12" s="71" t="s">
         <v>301</v>
       </c>
-      <c r="D12" s="73" t="s">
+      <c r="D12" s="71" t="s">
         <v>305</v>
       </c>
       <c r="E12" s="27" t="s">
@@ -6036,7 +6025,7 @@
       <c r="F12" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="G12" s="59" t="s">
+      <c r="G12" s="57" t="s">
         <v>53</v>
       </c>
     </row>
@@ -6044,13 +6033,13 @@
       <c r="A13" s="5">
         <v>11</v>
       </c>
-      <c r="B13" s="81" t="s">
+      <c r="B13" s="79" t="s">
         <v>163</v>
       </c>
-      <c r="C13" s="73" t="s">
+      <c r="C13" s="71" t="s">
         <v>301</v>
       </c>
-      <c r="D13" s="73" t="s">
+      <c r="D13" s="71" t="s">
         <v>305</v>
       </c>
       <c r="E13" s="27" t="s">
@@ -6059,7 +6048,7 @@
       <c r="F13" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="G13" s="59" t="s">
+      <c r="G13" s="57" t="s">
         <v>63</v>
       </c>
     </row>
@@ -6067,13 +6056,13 @@
       <c r="A14" s="5">
         <v>12</v>
       </c>
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="55" t="s">
         <v>161</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="56" t="s">
         <v>317</v>
       </c>
-      <c r="D14" s="58" t="s">
+      <c r="D14" s="56" t="s">
         <v>286</v>
       </c>
       <c r="E14" s="8" t="s">
@@ -6082,7 +6071,7 @@
       <c r="F14" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G14" s="59" t="s">
+      <c r="G14" s="57" t="s">
         <v>62</v>
       </c>
     </row>
@@ -6090,13 +6079,13 @@
       <c r="A15" s="5">
         <v>13</v>
       </c>
-      <c r="B15" s="81" t="s">
+      <c r="B15" s="79" t="s">
         <v>154</v>
       </c>
-      <c r="C15" s="73" t="s">
+      <c r="C15" s="71" t="s">
         <v>321</v>
       </c>
-      <c r="D15" s="73" t="s">
+      <c r="D15" s="71" t="s">
         <v>306</v>
       </c>
       <c r="E15" s="27" t="s">
@@ -6105,7 +6094,7 @@
       <c r="F15" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="G15" s="59" t="s">
+      <c r="G15" s="57" t="s">
         <v>55</v>
       </c>
     </row>
@@ -6113,13 +6102,13 @@
       <c r="A16" s="5">
         <v>14</v>
       </c>
-      <c r="B16" s="81" t="s">
+      <c r="B16" s="79" t="s">
         <v>230</v>
       </c>
-      <c r="C16" s="73" t="s">
+      <c r="C16" s="71" t="s">
         <v>299</v>
       </c>
-      <c r="D16" s="73" t="s">
+      <c r="D16" s="71" t="s">
         <v>306</v>
       </c>
       <c r="E16" s="27" t="s">
@@ -6128,7 +6117,7 @@
       <c r="F16" s="27" t="s">
         <v>232</v>
       </c>
-      <c r="G16" s="59" t="s">
+      <c r="G16" s="57" t="s">
         <v>231</v>
       </c>
     </row>
@@ -6136,13 +6125,13 @@
       <c r="A17" s="5">
         <v>15</v>
       </c>
-      <c r="B17" s="81" t="s">
+      <c r="B17" s="79" t="s">
         <v>153</v>
       </c>
-      <c r="C17" s="73" t="s">
+      <c r="C17" s="71" t="s">
         <v>299</v>
       </c>
-      <c r="D17" s="73" t="s">
+      <c r="D17" s="71" t="s">
         <v>306</v>
       </c>
       <c r="E17" s="27" t="s">
@@ -6151,7 +6140,7 @@
       <c r="F17" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="G17" s="59" t="s">
+      <c r="G17" s="57" t="s">
         <v>54</v>
       </c>
     </row>
@@ -6159,22 +6148,22 @@
       <c r="A18" s="5">
         <v>16</v>
       </c>
-      <c r="B18" s="57" t="s">
+      <c r="B18" s="55" t="s">
         <v>162</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="56" t="s">
         <v>302</v>
       </c>
-      <c r="D18" s="58" t="s">
+      <c r="D18" s="56" t="s">
         <v>304</v>
       </c>
-      <c r="E18" s="88" t="s">
+      <c r="E18" s="85" t="s">
         <v>50</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="G18" s="59" t="s">
+      <c r="G18" s="57" t="s">
         <v>58</v>
       </c>
     </row>
@@ -6182,22 +6171,22 @@
       <c r="A19" s="5">
         <v>17</v>
       </c>
-      <c r="B19" s="62" t="s">
+      <c r="B19" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="56" t="s">
         <v>319</v>
       </c>
-      <c r="D19" s="58" t="s">
+      <c r="D19" s="56" t="s">
         <v>304</v>
       </c>
-      <c r="E19" s="60" t="s">
+      <c r="E19" s="58" t="s">
         <v>193</v>
       </c>
-      <c r="F19" s="63" t="s">
+      <c r="F19" s="61" t="s">
         <v>124</v>
       </c>
-      <c r="G19" s="64" t="s">
+      <c r="G19" s="62" t="s">
         <v>138</v>
       </c>
     </row>
@@ -6205,22 +6194,22 @@
       <c r="A20" s="5">
         <v>18</v>
       </c>
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="56" t="s">
         <v>299</v>
       </c>
-      <c r="D20" s="58" t="s">
+      <c r="D20" s="56" t="s">
         <v>306</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="63" t="s">
+      <c r="F20" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="G20" s="64" t="s">
+      <c r="G20" s="62" t="s">
         <v>58</v>
       </c>
     </row>
@@ -6228,13 +6217,13 @@
       <c r="A21" s="5">
         <v>19</v>
       </c>
-      <c r="B21" s="57" t="s">
+      <c r="B21" s="55" t="s">
         <v>341</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="56" t="s">
         <v>342</v>
       </c>
-      <c r="D21" s="58" t="s">
+      <c r="D21" s="56" t="s">
         <v>306</v>
       </c>
       <c r="E21" s="8" t="s">
@@ -6289,33 +6278,33 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
-      <c r="B1" s="100" t="s">
+      <c r="B1" s="96" t="s">
         <v>131</v>
       </c>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="46" t="s">
         <v>228</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="46" t="s">
         <v>227</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="F2" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="G2" s="47" t="s">
         <v>49</v>
       </c>
     </row>
@@ -6329,16 +6318,16 @@
       <c r="C3" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="35" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6355,7 +6344,7 @@
       <c r="D4" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="32" t="s">
         <v>64</v>
       </c>
       <c r="F4" s="6" t="s">
@@ -6375,10 +6364,10 @@
       <c r="C5" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="E5" s="92" t="s">
+      <c r="E5" s="89" t="s">
         <v>64</v>
       </c>
       <c r="F5" s="6" t="s">
@@ -6398,16 +6387,16 @@
       <c r="C6" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="D6" s="37" t="s">
+      <c r="D6" s="35" t="s">
         <v>286</v>
       </c>
-      <c r="E6" s="90" t="s">
+      <c r="E6" s="87" t="s">
         <v>235</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="37" t="s">
+      <c r="G6" s="35" t="s">
         <v>41</v>
       </c>
     </row>
@@ -6421,16 +6410,16 @@
       <c r="C7" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="35" t="s">
         <v>286</v>
       </c>
-      <c r="E7" s="90" t="s">
+      <c r="E7" s="87" t="s">
         <v>235</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="35" t="s">
         <v>44</v>
       </c>
     </row>
@@ -6441,19 +6430,19 @@
       <c r="B8" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="E8" s="69" t="s">
+      <c r="E8" s="67" t="s">
         <v>193</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="37" t="s">
+      <c r="G8" s="35" t="s">
         <v>44</v>
       </c>
     </row>
@@ -6464,19 +6453,19 @@
       <c r="B9" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="35" t="s">
         <v>326</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="E9" s="69" t="s">
+      <c r="E9" s="67" t="s">
         <v>193</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="37" t="s">
+      <c r="G9" s="35" t="s">
         <v>44</v>
       </c>
     </row>
@@ -6490,16 +6479,16 @@
       <c r="C10" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="E10" s="32" t="s">
         <v>235</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="37" t="s">
+      <c r="G10" s="35" t="s">
         <v>45</v>
       </c>
     </row>
@@ -6513,16 +6502,16 @@
       <c r="C11" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="D11" s="37" t="s">
+      <c r="D11" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="E11" s="69" t="s">
+      <c r="E11" s="67" t="s">
         <v>193</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="37" t="s">
+      <c r="G11" s="35" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6536,16 +6525,16 @@
       <c r="C12" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="D12" s="37" t="s">
+      <c r="D12" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="E12" s="34" t="s">
+      <c r="E12" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="37" t="s">
+      <c r="F12" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="37" t="s">
+      <c r="G12" s="35" t="s">
         <v>239</v>
       </c>
     </row>
@@ -6556,13 +6545,13 @@
       <c r="B13" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="D13" s="37" t="s">
+      <c r="D13" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="E13" s="92" t="s">
+      <c r="E13" s="89" t="s">
         <v>64</v>
       </c>
       <c r="F13" s="6" t="s">
@@ -6579,19 +6568,19 @@
       <c r="B14" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="E14" s="80" t="s">
+      <c r="E14" s="78" t="s">
         <v>193</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F14" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="G14" s="35" t="s">
         <v>40</v>
       </c>
     </row>
@@ -6602,19 +6591,19 @@
       <c r="B15" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="35" t="s">
         <v>305</v>
       </c>
-      <c r="E15" s="80" t="s">
+      <c r="E15" s="78" t="s">
         <v>193</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="G15" s="37" t="s">
+      <c r="G15" s="35" t="s">
         <v>40</v>
       </c>
     </row>
@@ -6622,22 +6611,22 @@
       <c r="A16" s="5">
         <v>14</v>
       </c>
-      <c r="B16" s="76" t="s">
+      <c r="B16" s="74" t="s">
         <v>94</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="D16" s="37" t="s">
+      <c r="D16" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="E16" s="90" t="s">
+      <c r="E16" s="87" t="s">
         <v>235</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="G16" s="37" t="s">
+      <c r="G16" s="35" t="s">
         <v>42</v>
       </c>
     </row>
@@ -6648,19 +6637,19 @@
       <c r="B17" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="35" t="s">
         <v>312</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D17" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="E17" s="80" t="s">
+      <c r="E17" s="78" t="s">
         <v>193</v>
       </c>
-      <c r="F17" s="37" t="s">
+      <c r="F17" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="G17" s="37" t="s">
+      <c r="G17" s="35" t="s">
         <v>42</v>
       </c>
     </row>
@@ -6671,19 +6660,19 @@
       <c r="B18" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="D18" s="37" t="s">
+      <c r="D18" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="E18" s="90" t="s">
+      <c r="E18" s="87" t="s">
         <v>235</v>
       </c>
-      <c r="F18" s="37" t="s">
+      <c r="F18" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="37" t="s">
+      <c r="G18" s="35" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6694,19 +6683,19 @@
       <c r="B19" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="C19" s="37" t="s">
+      <c r="C19" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="35" t="s">
         <v>286</v>
       </c>
-      <c r="E19" s="90" t="s">
+      <c r="E19" s="87" t="s">
         <v>235</v>
       </c>
-      <c r="F19" s="37" t="s">
+      <c r="F19" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="G19" s="37" t="s">
+      <c r="G19" s="35" t="s">
         <v>138</v>
       </c>
     </row>
@@ -6720,16 +6709,16 @@
       <c r="C20" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="D20" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="90" t="s">
+      <c r="E20" s="87" t="s">
         <v>125</v>
       </c>
-      <c r="F20" s="37" t="s">
+      <c r="F20" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="37" t="s">
+      <c r="G20" s="35" t="s">
         <v>39</v>
       </c>
     </row>
@@ -6743,10 +6732,10 @@
       <c r="C21" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="D21" s="37" t="s">
+      <c r="D21" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="E21" s="90" t="s">
+      <c r="E21" s="87" t="s">
         <v>235</v>
       </c>
       <c r="F21" s="6" t="s">
@@ -6763,13 +6752,13 @@
       <c r="B22" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="D22" s="37" t="s">
+      <c r="D22" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="E22" s="92" t="s">
+      <c r="E22" s="89" t="s">
         <v>64</v>
       </c>
       <c r="F22" s="6" t="s">
@@ -6786,19 +6775,19 @@
       <c r="B23" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="35" t="s">
         <v>328</v>
       </c>
-      <c r="D23" s="37" t="s">
+      <c r="D23" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="E23" s="69" t="s">
+      <c r="E23" s="67" t="s">
         <v>194</v>
       </c>
-      <c r="F23" s="37" t="s">
+      <c r="F23" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="G23" s="37" t="s">
+      <c r="G23" s="35" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6812,10 +6801,10 @@
       <c r="C24" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="D24" s="37" t="s">
+      <c r="D24" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="E24" s="95" t="s">
+      <c r="E24" s="92" t="s">
         <v>64</v>
       </c>
       <c r="F24" s="6" t="s">
@@ -6835,10 +6824,10 @@
       <c r="C25" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="D25" s="37" t="s">
+      <c r="D25" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="E25" s="95" t="s">
+      <c r="E25" s="92" t="s">
         <v>64</v>
       </c>
       <c r="F25" s="6" t="s">
@@ -6847,9 +6836,9 @@
       <c r="G25" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="67"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="65"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
@@ -6861,10 +6850,10 @@
       <c r="C26" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="D26" s="37" t="s">
+      <c r="D26" s="35" t="s">
         <v>305</v>
       </c>
-      <c r="E26" s="80" t="s">
+      <c r="E26" s="78" t="s">
         <v>193</v>
       </c>
       <c r="F26" s="6" t="s">
@@ -6878,22 +6867,22 @@
       <c r="A27" s="5">
         <v>25</v>
       </c>
-      <c r="B27" s="52" t="s">
+      <c r="B27" s="50" t="s">
         <v>14</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="D27" s="37" t="s">
+      <c r="D27" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="E27" s="34" t="s">
+      <c r="E27" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="F27" s="37" t="s">
+      <c r="F27" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="56" t="s">
+      <c r="G27" s="54" t="s">
         <v>43</v>
       </c>
     </row>
@@ -6901,22 +6890,22 @@
       <c r="A28" s="5">
         <v>26</v>
       </c>
-      <c r="B28" s="52" t="s">
+      <c r="B28" s="50" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D28" s="37" t="s">
+      <c r="D28" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="E28" s="90" t="s">
+      <c r="E28" s="87" t="s">
         <v>235</v>
       </c>
-      <c r="F28" s="37" t="s">
+      <c r="F28" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="G28" s="56" t="s">
+      <c r="G28" s="54" t="s">
         <v>65</v>
       </c>
     </row>
@@ -6924,22 +6913,22 @@
       <c r="A29" s="5">
         <v>27</v>
       </c>
-      <c r="B29" s="52" t="s">
+      <c r="B29" s="50" t="s">
         <v>2</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="D29" s="37" t="s">
+      <c r="D29" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="E29" s="39" t="s">
+      <c r="E29" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="F29" s="37" t="s">
+      <c r="F29" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="G29" s="56" t="s">
+      <c r="G29" s="54" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6947,22 +6936,22 @@
       <c r="A30" s="5">
         <v>28</v>
       </c>
-      <c r="B30" s="52" t="s">
+      <c r="B30" s="50" t="s">
         <v>251</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="D30" s="37" t="s">
+      <c r="D30" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="E30" s="39" t="s">
+      <c r="E30" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="F30" s="56" t="s">
+      <c r="F30" s="54" t="s">
         <v>253</v>
       </c>
-      <c r="G30" s="56" t="s">
+      <c r="G30" s="54" t="s">
         <v>252</v>
       </c>
     </row>
@@ -6976,10 +6965,10 @@
       <c r="C31" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="D31" s="37" t="s">
+      <c r="D31" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="E31" s="39" t="s">
+      <c r="E31" s="37" t="s">
         <v>64</v>
       </c>
       <c r="F31" s="6" t="s">
@@ -6997,24 +6986,24 @@
       <c r="F32" s="9"/>
     </row>
     <row r="33" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E33" s="35"/>
+      <c r="E33" s="33"/>
     </row>
     <row r="34" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E34" s="35"/>
+      <c r="E34" s="33"/>
     </row>
     <row r="35" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E35" s="35"/>
-      <c r="F35" s="78"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="76"/>
     </row>
     <row r="38" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E38" s="78"/>
-      <c r="F38" s="66"/>
+      <c r="E38" s="76"/>
+      <c r="F38" s="64"/>
     </row>
     <row r="39" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="F39" s="66"/>
+      <c r="F39" s="64"/>
     </row>
     <row r="40" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="F40" s="66"/>
+      <c r="F40" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7043,38 +7032,38 @@
     <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21" style="65" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" style="63" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
-      <c r="B1" s="100" t="s">
+      <c r="B1" s="96" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
     </row>
     <row r="2" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="49" t="s">
         <v>228</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="49" t="s">
         <v>229</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="49" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7082,22 +7071,22 @@
       <c r="A3" s="26">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="80" t="s">
         <v>236</v>
       </c>
-      <c r="C3" s="82" t="s">
+      <c r="C3" s="80" t="s">
         <v>326</v>
       </c>
       <c r="D3" s="27" t="s">
         <v>304</v>
       </c>
-      <c r="E3" s="90" t="s">
+      <c r="E3" s="87" t="s">
         <v>125</v>
       </c>
       <c r="F3" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="71" t="s">
+      <c r="G3" s="69" t="s">
         <v>237</v>
       </c>
     </row>
@@ -7105,22 +7094,22 @@
       <c r="A4" s="26">
         <v>2</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="80" t="s">
         <v>242</v>
       </c>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="80" t="s">
         <v>303</v>
       </c>
       <c r="D4" s="27" t="s">
         <v>304</v>
       </c>
-      <c r="E4" s="90" t="s">
+      <c r="E4" s="87" t="s">
         <v>125</v>
       </c>
       <c r="F4" s="27" t="s">
         <v>243</v>
       </c>
-      <c r="G4" s="71" t="s">
+      <c r="G4" s="69" t="s">
         <v>244</v>
       </c>
     </row>
@@ -7128,16 +7117,16 @@
       <c r="A5" s="26">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="s">
+      <c r="B5" s="93" t="s">
         <v>275</v>
       </c>
-      <c r="C5" s="96" t="s">
+      <c r="C5" s="93" t="s">
         <v>295</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>286</v>
       </c>
-      <c r="E5" s="90" t="s">
+      <c r="E5" s="87" t="s">
         <v>64</v>
       </c>
       <c r="F5" s="7" t="s">
@@ -7151,22 +7140,22 @@
       <c r="A6" s="26">
         <v>4</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C6" s="82" t="s">
+      <c r="C6" s="80" t="s">
         <v>294</v>
       </c>
       <c r="D6" s="27" t="s">
         <v>304</v>
       </c>
-      <c r="E6" s="90" t="s">
+      <c r="E6" s="87" t="s">
         <v>125</v>
       </c>
       <c r="F6" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="G6" s="71" t="s">
+      <c r="G6" s="69" t="s">
         <v>247</v>
       </c>
     </row>
@@ -7174,22 +7163,22 @@
       <c r="A7" s="26">
         <v>5</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="80" t="s">
         <v>245</v>
       </c>
-      <c r="C7" s="82" t="s">
+      <c r="C7" s="80" t="s">
         <v>300</v>
       </c>
       <c r="D7" s="27" t="s">
         <v>304</v>
       </c>
-      <c r="E7" s="34" t="s">
+      <c r="E7" s="32" t="s">
         <v>64</v>
       </c>
       <c r="F7" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="G7" s="71" t="s">
+      <c r="G7" s="69" t="s">
         <v>247</v>
       </c>
     </row>
@@ -7200,19 +7189,19 @@
       <c r="B8" s="38" t="s">
         <v>259</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="38" t="s">
         <v>300</v>
       </c>
       <c r="D8" s="27" t="s">
         <v>304</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="E8" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="40" t="s">
+      <c r="F8" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="G8" s="91" t="s">
+      <c r="G8" s="88" t="s">
         <v>260</v>
       </c>
     </row>
@@ -7229,7 +7218,7 @@
       <c r="D9" s="27" t="s">
         <v>304</v>
       </c>
-      <c r="E9" s="77" t="s">
+      <c r="E9" s="75" t="s">
         <v>64</v>
       </c>
       <c r="F9" s="23" t="s">
@@ -7243,22 +7232,22 @@
       <c r="A10" s="26">
         <v>8</v>
       </c>
-      <c r="B10" s="82" t="s">
+      <c r="B10" s="80" t="s">
         <v>281</v>
       </c>
-      <c r="C10" s="82" t="s">
+      <c r="C10" s="80" t="s">
         <v>299</v>
       </c>
       <c r="D10" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="E10" s="32" t="s">
         <v>64</v>
       </c>
       <c r="F10" s="27" t="s">
         <v>279</v>
       </c>
-      <c r="G10" s="71" t="s">
+      <c r="G10" s="69" t="s">
         <v>280</v>
       </c>
     </row>
@@ -7266,22 +7255,22 @@
       <c r="A11" s="26">
         <v>9</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="80" t="s">
         <v>345</v>
       </c>
-      <c r="C11" s="99" t="s">
+      <c r="C11" s="95" t="s">
         <v>300</v>
       </c>
       <c r="D11" s="25" t="s">
         <v>304</v>
       </c>
-      <c r="E11" s="34" t="s">
+      <c r="E11" s="32" t="s">
         <v>64</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>166</v>
       </c>
-      <c r="G11" s="71" t="s">
+      <c r="G11" s="69" t="s">
         <v>202</v>
       </c>
     </row>
@@ -7289,151 +7278,151 @@
       <c r="A12" s="26">
         <v>10</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="82" t="s">
+      <c r="B12" s="80"/>
+      <c r="C12" s="80" t="s">
         <v>282</v>
       </c>
       <c r="D12" s="25" t="s">
         <v>282</v>
       </c>
-      <c r="E12" s="34"/>
+      <c r="E12" s="32"/>
       <c r="F12" s="27"/>
-      <c r="G12" s="68"/>
+      <c r="G12" s="66"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="26">
         <v>11</v>
       </c>
-      <c r="B13" s="32"/>
-      <c r="C13" s="82" t="s">
+      <c r="B13" s="80"/>
+      <c r="C13" s="80" t="s">
         <v>282</v>
       </c>
       <c r="D13" s="25" t="s">
         <v>282</v>
       </c>
-      <c r="E13" s="34"/>
+      <c r="E13" s="32"/>
       <c r="F13" s="27"/>
-      <c r="G13" s="68"/>
+      <c r="G13" s="66"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="26">
         <v>12</v>
       </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="82" t="s">
+      <c r="B14" s="80"/>
+      <c r="C14" s="80" t="s">
         <v>282</v>
       </c>
       <c r="D14" s="25" t="s">
         <v>282</v>
       </c>
-      <c r="E14" s="34"/>
+      <c r="E14" s="32"/>
       <c r="F14" s="27"/>
-      <c r="G14" s="68"/>
+      <c r="G14" s="66"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="26">
         <v>13</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="82" t="s">
+      <c r="B15" s="80"/>
+      <c r="C15" s="80" t="s">
         <v>282</v>
       </c>
       <c r="D15" s="25" t="s">
         <v>282</v>
       </c>
-      <c r="E15" s="34"/>
+      <c r="E15" s="32"/>
       <c r="F15" s="27"/>
-      <c r="G15" s="68"/>
+      <c r="G15" s="66"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="26">
         <v>14</v>
       </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="82" t="s">
+      <c r="B16" s="80"/>
+      <c r="C16" s="80" t="s">
         <v>282</v>
       </c>
       <c r="D16" s="25" t="s">
         <v>282</v>
       </c>
-      <c r="E16" s="34"/>
+      <c r="E16" s="32"/>
       <c r="F16" s="27"/>
-      <c r="G16" s="68"/>
+      <c r="G16" s="66"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="26">
         <v>15</v>
       </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="82" t="s">
+      <c r="B17" s="80"/>
+      <c r="C17" s="80" t="s">
         <v>282</v>
       </c>
       <c r="D17" s="25" t="s">
         <v>282</v>
       </c>
-      <c r="E17" s="34"/>
+      <c r="E17" s="32"/>
       <c r="F17" s="27"/>
-      <c r="G17" s="68"/>
+      <c r="G17" s="66"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="26">
         <v>16</v>
       </c>
-      <c r="B18" s="32"/>
-      <c r="C18" s="82" t="s">
+      <c r="B18" s="80"/>
+      <c r="C18" s="80" t="s">
         <v>282</v>
       </c>
       <c r="D18" s="25" t="s">
         <v>282</v>
       </c>
-      <c r="E18" s="34"/>
+      <c r="E18" s="32"/>
       <c r="F18" s="27"/>
-      <c r="G18" s="68"/>
+      <c r="G18" s="66"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="24">
         <v>17</v>
       </c>
-      <c r="B19" s="33"/>
-      <c r="C19" s="87" t="s">
+      <c r="B19" s="84"/>
+      <c r="C19" s="84" t="s">
         <v>282</v>
       </c>
-      <c r="D19" s="38" t="s">
+      <c r="D19" s="36" t="s">
         <v>282</v>
       </c>
-      <c r="E19" s="39"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="70"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="68"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>18</v>
       </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="87" t="s">
+      <c r="B20" s="84"/>
+      <c r="C20" s="84" t="s">
         <v>282</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="36" t="s">
         <v>282</v>
       </c>
-      <c r="E20" s="39"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="70"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="68"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>19</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="82" t="s">
+      <c r="B21" s="80"/>
+      <c r="C21" s="80" t="s">
         <v>282</v>
       </c>
       <c r="D21" s="25" t="s">
         <v>282</v>
       </c>
-      <c r="E21" s="34"/>
+      <c r="E21" s="32"/>
       <c r="F21" s="27"/>
-      <c r="G21" s="68"/>
+      <c r="G21" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7465,33 +7454,33 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
-      <c r="B1" s="100" t="s">
+      <c r="B1" s="96" t="s">
         <v>208</v>
       </c>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
     </row>
     <row r="2" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="49" t="s">
         <v>228</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="49" t="s">
         <v>229</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="49" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7499,7 +7488,7 @@
       <c r="A3" s="26">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="80" t="s">
         <v>226</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -7508,7 +7497,7 @@
       <c r="D3" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="32" t="s">
         <v>125</v>
       </c>
       <c r="F3" s="27" t="s">
@@ -7522,7 +7511,7 @@
       <c r="A4" s="26">
         <v>2</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="80" t="s">
         <v>180</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -7531,7 +7520,7 @@
       <c r="D4" s="27" t="s">
         <v>283</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="32" t="s">
         <v>193</v>
       </c>
       <c r="F4" s="27" t="s">
@@ -7545,7 +7534,7 @@
       <c r="A5" s="26">
         <v>3</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="80" t="s">
         <v>215</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -7554,7 +7543,7 @@
       <c r="D5" s="27" t="s">
         <v>336</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="32" t="s">
         <v>125</v>
       </c>
       <c r="F5" s="27" t="s">
@@ -7568,7 +7557,7 @@
       <c r="A6" s="26">
         <v>4</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="79" t="s">
         <v>256</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -7577,7 +7566,7 @@
       <c r="D6" s="30" t="s">
         <v>273</v>
       </c>
-      <c r="E6" s="79" t="s">
+      <c r="E6" s="77" t="s">
         <v>193</v>
       </c>
       <c r="F6" s="30" t="s">
@@ -7591,7 +7580,7 @@
       <c r="A7" s="26">
         <v>5</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="80" t="s">
         <v>233</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -7600,7 +7589,7 @@
       <c r="D7" s="27" t="s">
         <v>336</v>
       </c>
-      <c r="E7" s="34" t="s">
+      <c r="E7" s="32" t="s">
         <v>64</v>
       </c>
       <c r="F7" s="27" t="s">
@@ -7614,7 +7603,7 @@
       <c r="A8" s="26">
         <v>6</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="80" t="s">
         <v>182</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -7623,7 +7612,7 @@
       <c r="D8" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="32" t="s">
         <v>235</v>
       </c>
       <c r="F8" s="27" t="s">
@@ -7637,7 +7626,7 @@
       <c r="A9" s="26">
         <v>7</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="80" t="s">
         <v>183</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -7646,7 +7635,7 @@
       <c r="D9" s="27" t="s">
         <v>337</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="E9" s="32" t="s">
         <v>125</v>
       </c>
       <c r="F9" s="27" t="s">
@@ -7660,7 +7649,7 @@
       <c r="A10" s="26">
         <v>8</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="80" t="s">
         <v>257</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -7669,13 +7658,13 @@
       <c r="D10" s="27" t="s">
         <v>336</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="E10" s="32" t="s">
         <v>64</v>
       </c>
       <c r="F10" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="G10" s="71" t="s">
+      <c r="G10" s="69" t="s">
         <v>258</v>
       </c>
     </row>
@@ -7683,7 +7672,7 @@
       <c r="A11" s="26">
         <v>9</v>
       </c>
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="79" t="s">
         <v>269</v>
       </c>
       <c r="C11" s="7" t="s">
@@ -7692,7 +7681,7 @@
       <c r="D11" s="30" t="s">
         <v>336</v>
       </c>
-      <c r="E11" s="79" t="s">
+      <c r="E11" s="77" t="s">
         <v>64</v>
       </c>
       <c r="F11" s="30" t="s">
@@ -7706,7 +7695,7 @@
       <c r="A12" s="26">
         <v>10</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="79" t="s">
         <v>274</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -7715,7 +7704,7 @@
       <c r="D12" s="30" t="s">
         <v>336</v>
       </c>
-      <c r="E12" s="79" t="s">
+      <c r="E12" s="77" t="s">
         <v>64</v>
       </c>
       <c r="F12" s="30" t="s">
@@ -7729,7 +7718,7 @@
       <c r="A13" s="26">
         <v>11</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="80" t="s">
         <v>184</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -7738,7 +7727,7 @@
       <c r="D13" s="27" t="s">
         <v>283</v>
       </c>
-      <c r="E13" s="34" t="s">
+      <c r="E13" s="32" t="s">
         <v>193</v>
       </c>
       <c r="F13" s="27" t="s">
@@ -7752,7 +7741,7 @@
       <c r="A14" s="26">
         <v>12</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="80" t="s">
         <v>185</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -7761,7 +7750,7 @@
       <c r="D14" s="27" t="s">
         <v>283</v>
       </c>
-      <c r="E14" s="34" t="s">
+      <c r="E14" s="32" t="s">
         <v>193</v>
       </c>
       <c r="F14" s="27" t="s">
@@ -7775,7 +7764,7 @@
       <c r="A15" s="26">
         <v>13</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="80" t="s">
         <v>186</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -7784,7 +7773,7 @@
       <c r="D15" s="27" t="s">
         <v>336</v>
       </c>
-      <c r="E15" s="34" t="s">
+      <c r="E15" s="32" t="s">
         <v>50</v>
       </c>
       <c r="F15" s="27" t="s">
@@ -7798,7 +7787,7 @@
       <c r="A16" s="26">
         <v>14</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="80" t="s">
         <v>255</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -7807,7 +7796,7 @@
       <c r="D16" s="27" t="s">
         <v>283</v>
       </c>
-      <c r="E16" s="34" t="s">
+      <c r="E16" s="32" t="s">
         <v>194</v>
       </c>
       <c r="F16" s="27" t="s">
@@ -7821,7 +7810,7 @@
       <c r="A17" s="26">
         <v>15</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="80" t="s">
         <v>189</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -7830,7 +7819,7 @@
       <c r="D17" s="27" t="s">
         <v>336</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E17" s="32" t="s">
         <v>64</v>
       </c>
       <c r="F17" s="27" t="s">
@@ -7844,7 +7833,7 @@
       <c r="A18" s="26">
         <v>16</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="80" t="s">
         <v>187</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -7853,7 +7842,7 @@
       <c r="D18" s="27" t="s">
         <v>336</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="32" t="s">
         <v>194</v>
       </c>
       <c r="F18" s="27" t="s">
@@ -7867,22 +7856,22 @@
       <c r="A19" s="24">
         <v>17</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="84" t="s">
         <v>188</v>
       </c>
       <c r="C19" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="D19" s="40" t="s">
+      <c r="D19" s="38" t="s">
         <v>336</v>
       </c>
-      <c r="E19" s="39" t="s">
+      <c r="E19" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="F19" s="40" t="s">
+      <c r="F19" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="G19" s="40" t="s">
+      <c r="G19" s="38" t="s">
         <v>204</v>
       </c>
     </row>
@@ -7890,22 +7879,22 @@
       <c r="A20" s="26">
         <v>18</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="84" t="s">
         <v>181</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D20" s="40" t="s">
+      <c r="D20" s="38" t="s">
         <v>338</v>
       </c>
-      <c r="E20" s="39" t="s">
+      <c r="E20" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="40" t="s">
+      <c r="F20" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="G20" s="40" t="s">
+      <c r="G20" s="38" t="s">
         <v>200</v>
       </c>
     </row>
@@ -7913,7 +7902,7 @@
       <c r="A21" s="26">
         <v>19</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="80" t="s">
         <v>240</v>
       </c>
       <c r="C21" s="3" t="s">
@@ -7922,7 +7911,7 @@
       <c r="D21" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="E21" s="34" t="s">
+      <c r="E21" s="32" t="s">
         <v>64</v>
       </c>
       <c r="F21" s="27" t="s">
@@ -7936,22 +7925,22 @@
       <c r="A22" s="3">
         <v>20</v>
       </c>
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="84" t="s">
         <v>144</v>
       </c>
       <c r="C22" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="D22" s="40" t="s">
+      <c r="D22" s="38" t="s">
         <v>304</v>
       </c>
-      <c r="E22" s="34" t="s">
+      <c r="E22" s="32" t="s">
         <v>125</v>
       </c>
       <c r="F22" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="G22" s="40" t="s">
+      <c r="G22" s="38" t="s">
         <v>127</v>
       </c>
     </row>
@@ -7959,7 +7948,7 @@
       <c r="A23" s="3">
         <v>21</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="27" t="s">
         <v>191</v>
       </c>
       <c r="C23" s="3" t="s">
@@ -7968,7 +7957,7 @@
       <c r="D23" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="E23" s="34" t="s">
+      <c r="E23" s="32" t="s">
         <v>64</v>
       </c>
       <c r="F23" s="27" t="s">
@@ -7982,22 +7971,22 @@
       <c r="A24" s="3">
         <v>22</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="27" t="s">
         <v>190</v>
       </c>
       <c r="C24" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="D24" s="40" t="s">
+      <c r="D24" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="E24" s="39" t="s">
+      <c r="E24" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="F24" s="40" t="s">
+      <c r="F24" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="G24" s="40" t="s">
+      <c r="G24" s="38" t="s">
         <v>150</v>
       </c>
     </row>
@@ -8005,7 +7994,7 @@
       <c r="A25" s="3">
         <v>23</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="27" t="s">
         <v>192</v>
       </c>
       <c r="C25" s="3" t="s">
@@ -8014,7 +8003,7 @@
       <c r="D25" s="27" t="s">
         <v>336</v>
       </c>
-      <c r="E25" s="34" t="s">
+      <c r="E25" s="32" t="s">
         <v>50</v>
       </c>
       <c r="F25" s="27" t="s">
@@ -8028,7 +8017,7 @@
       <c r="A26" s="3">
         <v>24</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="27" t="s">
         <v>224</v>
       </c>
       <c r="C26" s="3" t="s">
@@ -8037,7 +8026,7 @@
       <c r="D26" s="27" t="s">
         <v>337</v>
       </c>
-      <c r="E26" s="34" t="s">
+      <c r="E26" s="32" t="s">
         <v>194</v>
       </c>
       <c r="F26" s="27" t="s">
@@ -8051,14 +8040,14 @@
       <c r="A27" s="3">
         <v>25</v>
       </c>
-      <c r="B27" s="97" t="s">
+      <c r="B27" s="98" t="s">
         <v>343</v>
       </c>
       <c r="C27" s="23"/>
       <c r="D27" s="31" t="s">
         <v>336</v>
       </c>
-      <c r="E27" s="98" t="s">
+      <c r="E27" s="94" t="s">
         <v>64</v>
       </c>
       <c r="F27" s="31" t="s">
@@ -8121,7 +8110,7 @@
       <c r="A2" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B2" s="84" t="str">
+      <c r="B2" s="81" t="str">
         <f t="shared" ref="B2:B33" ca="1" si="0">UPPER(TRIM(UPPER(IFERROR(VLOOKUP(A2,INDIRECT("'BAIXADA'!$B$3:$I$51"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'NORTE'!$B$3:$I$21"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'SUL'!$B$3:$I$31"),3,FALSE),
@@ -8129,15 +8118,15 @@
 IFERROR(VLOOKUP(A2,INDIRECT("'ESPECIAIS'!$B$3:$I$27"),3,FALSE),""))))))))</f>
         <v>ERICK HYLARIO</v>
       </c>
-      <c r="C2" s="84" t="str">
+      <c r="C2" s="81" t="str">
         <f t="shared" ref="C2:C33" ca="1" si="1">IF(OR(B2="CARLOS FERNANDES", B2="GISELLE G. FONSECA"), "BAIXADA",
  IF(OR(B2="ISADORA ROSALINO", B2="JEHNIFFER PIRES"), "NORTE",
  IF(OR(B2="LUIZ FILHO", B2="MARCUS", B2="JAQUELINE PASTÓRIO"), "SUL",
  IF(OR(B2="AIMAR FILHO", B2="ERICK HYLARIO", B2="IGOR CARNEIRO", B2="CESAR", B2="DANRLEI"), "ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85" t="str">
+      <c r="D2" s="82"/>
+      <c r="E2" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8145,7 +8134,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F2" s="85" t="str">
+      <c r="F2" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A2),COUNTIF(NORTE!B:B,A2),COUNTIF(SUL!B:B,A2))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A2)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A2)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -8155,16 +8144,16 @@
       <c r="A3" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="84" t="str">
+      <c r="B3" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C3" s="84" t="str">
+      <c r="C3" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85" t="str">
+      <c r="D3" s="82"/>
+      <c r="E3" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8172,7 +8161,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F3" s="85" t="str">
+      <c r="F3" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A3),COUNTIF(NORTE!B:B,A3),COUNTIF(SUL!B:B,A3))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A3)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A3)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8182,16 +8171,16 @@
       <c r="A4" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="84" t="str">
+      <c r="B4" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>LUIZ FILHO</v>
       </c>
-      <c r="C4" s="84" t="str">
+      <c r="C4" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>SUL</v>
       </c>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85" t="str">
+      <c r="D4" s="82"/>
+      <c r="E4" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8199,7 +8188,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE PROVISORIO</v>
       </c>
-      <c r="F4" s="85" t="str">
+      <c r="F4" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A4),COUNTIF(NORTE!B:B,A4),COUNTIF(SUL!B:B,A4))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A4)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A4)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8209,16 +8198,16 @@
       <c r="A5" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="84" t="str">
+      <c r="B5" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C5" s="84" t="str">
+      <c r="C5" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85" t="str">
+      <c r="D5" s="82"/>
+      <c r="E5" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8226,7 +8215,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>DISTRATO</v>
       </c>
-      <c r="F5" s="85" t="str">
+      <c r="F5" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A5),COUNTIF(NORTE!B:B,A5),COUNTIF(SUL!B:B,A5))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A5)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A5)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8236,16 +8225,16 @@
       <c r="A6" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B6" s="84" t="str">
+      <c r="B6" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C6" s="84" t="str">
+      <c r="C6" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85" t="str">
+      <c r="D6" s="82"/>
+      <c r="E6" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8253,7 +8242,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>DISTRATO</v>
       </c>
-      <c r="F6" s="85" t="str">
+      <c r="F6" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A6),COUNTIF(NORTE!B:B,A6),COUNTIF(SUL!B:B,A6))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A6)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A6)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8263,16 +8252,16 @@
       <c r="A7" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B7" s="84" t="str">
+      <c r="B7" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C7" s="84" t="str">
+      <c r="C7" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85" t="str">
+      <c r="D7" s="82"/>
+      <c r="E7" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8280,7 +8269,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F7" s="85" t="str">
+      <c r="F7" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A7),COUNTIF(NORTE!B:B,A7),COUNTIF(SUL!B:B,A7))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A7)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A7)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8290,16 +8279,16 @@
       <c r="A8" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="84" t="str">
+      <c r="B8" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>IGOR CARNEIRO</v>
       </c>
-      <c r="C8" s="84" t="str">
+      <c r="C8" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D8" s="85"/>
-      <c r="E8" s="85" t="str">
+      <c r="D8" s="82"/>
+      <c r="E8" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8307,7 +8296,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F8" s="85" t="str">
+      <c r="F8" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A8),COUNTIF(NORTE!B:B,A8),COUNTIF(SUL!B:B,A8))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A8)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A8)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -8317,16 +8306,16 @@
       <c r="A9" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B9" s="84" t="str">
+      <c r="B9" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C9" s="84" t="str">
+      <c r="C9" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85" t="str">
+      <c r="D9" s="82"/>
+      <c r="E9" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8334,7 +8323,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>DISTRATO</v>
       </c>
-      <c r="F9" s="85" t="str">
+      <c r="F9" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A9),COUNTIF(NORTE!B:B,A9),COUNTIF(SUL!B:B,A9))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A9)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A9)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8344,16 +8333,16 @@
       <c r="A10" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B10" s="84" t="str">
+      <c r="B10" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C10" s="84" t="str">
+      <c r="C10" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85" t="str">
+      <c r="D10" s="82"/>
+      <c r="E10" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8361,7 +8350,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>#CONCLUIDA</v>
       </c>
-      <c r="F10" s="85" t="str">
+      <c r="F10" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A10),COUNTIF(NORTE!B:B,A10),COUNTIF(SUL!B:B,A10))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A10)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A10)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8371,16 +8360,16 @@
       <c r="A11" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B11" s="84" t="str">
+      <c r="B11" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>IGOR CARNEIRO</v>
       </c>
-      <c r="C11" s="84" t="str">
+      <c r="C11" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D11" s="85"/>
-      <c r="E11" s="85" t="str">
+      <c r="D11" s="82"/>
+      <c r="E11" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8388,7 +8377,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>#CONCLUIDA</v>
       </c>
-      <c r="F11" s="85" t="str">
+      <c r="F11" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A11),COUNTIF(NORTE!B:B,A11),COUNTIF(SUL!B:B,A11))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A11)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A11)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -8398,16 +8387,16 @@
       <c r="A12" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B12" s="84" t="str">
+      <c r="B12" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C12" s="84" t="str">
+      <c r="C12" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D12" s="85"/>
-      <c r="E12" s="85" t="str">
+      <c r="D12" s="82"/>
+      <c r="E12" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8415,7 +8404,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F12" s="85" t="str">
+      <c r="F12" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A12),COUNTIF(NORTE!B:B,A12),COUNTIF(SUL!B:B,A12))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A12)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A12)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8425,16 +8414,16 @@
       <c r="A13" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B13" s="84" t="str">
+      <c r="B13" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C13" s="84" t="str">
+      <c r="C13" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D13" s="85"/>
-      <c r="E13" s="85" t="str">
+      <c r="D13" s="82"/>
+      <c r="E13" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8442,7 +8431,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>SUSPENSA</v>
       </c>
-      <c r="F13" s="85" t="str">
+      <c r="F13" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A13),COUNTIF(NORTE!B:B,A13),COUNTIF(SUL!B:B,A13))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A13)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A13)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8452,16 +8441,16 @@
       <c r="A14" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B14" s="84" t="str">
+      <c r="B14" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C14" s="84" t="str">
+      <c r="C14" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D14" s="85"/>
-      <c r="E14" s="85" t="str">
+      <c r="D14" s="82"/>
+      <c r="E14" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8469,7 +8458,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F14" s="85" t="str">
+      <c r="F14" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A14),COUNTIF(NORTE!B:B,A14),COUNTIF(SUL!B:B,A14))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A14)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A14)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8479,16 +8468,16 @@
       <c r="A15" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B15" s="84" t="str">
+      <c r="B15" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C15" s="84" t="str">
+      <c r="C15" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D15" s="85"/>
-      <c r="E15" s="85" t="str">
+      <c r="D15" s="82"/>
+      <c r="E15" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8496,7 +8485,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F15" s="85" t="str">
+      <c r="F15" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A15),COUNTIF(NORTE!B:B,A15),COUNTIF(SUL!B:B,A15))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A15)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A15)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8506,16 +8495,16 @@
       <c r="A16" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="84" t="str">
+      <c r="B16" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C16" s="84" t="str">
+      <c r="C16" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D16" s="85"/>
-      <c r="E16" s="85" t="str">
+      <c r="D16" s="82"/>
+      <c r="E16" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8523,7 +8512,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>DISTRATO</v>
       </c>
-      <c r="F16" s="85" t="str">
+      <c r="F16" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A16),COUNTIF(NORTE!B:B,A16),COUNTIF(SUL!B:B,A16))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A16)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A16)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8533,16 +8522,16 @@
       <c r="A17" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B17" s="84" t="str">
+      <c r="B17" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C17" s="84" t="str">
+      <c r="C17" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D17" s="85"/>
-      <c r="E17" s="85" t="str">
+      <c r="D17" s="82"/>
+      <c r="E17" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8550,7 +8539,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>DISTRATO</v>
       </c>
-      <c r="F17" s="85" t="str">
+      <c r="F17" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A17),COUNTIF(NORTE!B:B,A17),COUNTIF(SUL!B:B,A17))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A17)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A17)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8560,16 +8549,16 @@
       <c r="A18" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B18" s="84" t="str">
+      <c r="B18" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C18" s="84" t="str">
+      <c r="C18" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85" t="str">
+      <c r="D18" s="82"/>
+      <c r="E18" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8577,7 +8566,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F18" s="85" t="str">
+      <c r="F18" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A18),COUNTIF(NORTE!B:B,A18),COUNTIF(SUL!B:B,A18))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A18)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A18)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8587,16 +8576,16 @@
       <c r="A19" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B19" s="84" t="str">
+      <c r="B19" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C19" s="84" t="str">
+      <c r="C19" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D19" s="85"/>
-      <c r="E19" s="85" t="str">
+      <c r="D19" s="82"/>
+      <c r="E19" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8604,7 +8593,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F19" s="85" t="str">
+      <c r="F19" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A19),COUNTIF(NORTE!B:B,A19),COUNTIF(SUL!B:B,A19))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A19)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A19)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8614,16 +8603,16 @@
       <c r="A20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="84" t="str">
+      <c r="B20" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C20" s="84" t="str">
+      <c r="C20" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D20" s="85"/>
-      <c r="E20" s="85" t="str">
+      <c r="D20" s="82"/>
+      <c r="E20" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8631,7 +8620,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F20" s="85" t="str">
+      <c r="F20" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A20),COUNTIF(NORTE!B:B,A20),COUNTIF(SUL!B:B,A20))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A20)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A20)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8641,16 +8630,16 @@
       <c r="A21" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B21" s="84" t="str">
+      <c r="B21" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C21" s="84" t="str">
+      <c r="C21" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D21" s="85"/>
-      <c r="E21" s="85" t="str">
+      <c r="D21" s="82"/>
+      <c r="E21" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8658,7 +8647,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE DEFINITIVO</v>
       </c>
-      <c r="F21" s="85" t="str">
+      <c r="F21" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A21),COUNTIF(NORTE!B:B,A21),COUNTIF(SUL!B:B,A21))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A21)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A21)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8668,16 +8657,16 @@
       <c r="A22" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B22" s="84" t="str">
+      <c r="B22" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C22" s="84" t="str">
+      <c r="C22" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D22" s="85"/>
-      <c r="E22" s="85" t="str">
+      <c r="D22" s="82"/>
+      <c r="E22" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8685,7 +8674,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>SUSPENSA</v>
       </c>
-      <c r="F22" s="85" t="str">
+      <c r="F22" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A22),COUNTIF(NORTE!B:B,A22),COUNTIF(SUL!B:B,A22))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A22)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A22)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8695,16 +8684,16 @@
       <c r="A23" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B23" s="84" t="str">
+      <c r="B23" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>ISADORA ROSALINO</v>
       </c>
-      <c r="C23" s="84" t="str">
+      <c r="C23" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>NORTE</v>
       </c>
-      <c r="D23" s="85"/>
-      <c r="E23" s="85" t="str">
+      <c r="D23" s="82"/>
+      <c r="E23" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8712,7 +8701,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F23" s="85" t="str">
+      <c r="F23" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A23),COUNTIF(NORTE!B:B,A23),COUNTIF(SUL!B:B,A23))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A23)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A23)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8722,16 +8711,16 @@
       <c r="A24" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B24" s="84" t="str">
+      <c r="B24" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C24" s="84" t="str">
+      <c r="C24" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D24" s="85"/>
-      <c r="E24" s="85" t="str">
+      <c r="D24" s="82"/>
+      <c r="E24" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8739,7 +8728,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>#CONCLUIDA</v>
       </c>
-      <c r="F24" s="85" t="str">
+      <c r="F24" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A24),COUNTIF(NORTE!B:B,A24),COUNTIF(SUL!B:B,A24))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A24)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A24)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8749,16 +8738,16 @@
       <c r="A25" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B25" s="84" t="str">
+      <c r="B25" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C25" s="84" t="str">
+      <c r="C25" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D25" s="85"/>
-      <c r="E25" s="85" t="str">
+      <c r="D25" s="82"/>
+      <c r="E25" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8766,7 +8755,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F25" s="85" t="str">
+      <c r="F25" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A25),COUNTIF(NORTE!B:B,A25),COUNTIF(SUL!B:B,A25))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A25)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A25)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8776,16 +8765,16 @@
       <c r="A26" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="84" t="str">
+      <c r="B26" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C26" s="84" t="str">
+      <c r="C26" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D26" s="85"/>
-      <c r="E26" s="85" t="str">
+      <c r="D26" s="82"/>
+      <c r="E26" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8793,7 +8782,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE PROVISORIO</v>
       </c>
-      <c r="F26" s="85" t="str">
+      <c r="F26" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A26),COUNTIF(NORTE!B:B,A26),COUNTIF(SUL!B:B,A26))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A26)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A26)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8803,16 +8792,16 @@
       <c r="A27" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B27" s="84" t="str">
+      <c r="B27" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C27" s="84" t="str">
+      <c r="C27" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D27" s="85"/>
-      <c r="E27" s="85" t="str">
+      <c r="D27" s="82"/>
+      <c r="E27" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8820,7 +8809,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F27" s="85" t="str">
+      <c r="F27" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A27),COUNTIF(NORTE!B:B,A27),COUNTIF(SUL!B:B,A27))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A27)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A27)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8830,16 +8819,16 @@
       <c r="A28" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B28" s="84" t="str">
+      <c r="B28" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C28" s="84" t="str">
+      <c r="C28" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D28" s="85"/>
-      <c r="E28" s="85" t="str">
+      <c r="D28" s="82"/>
+      <c r="E28" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8847,7 +8836,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE PROVISORIO</v>
       </c>
-      <c r="F28" s="85" t="str">
+      <c r="F28" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A28),COUNTIF(NORTE!B:B,A28),COUNTIF(SUL!B:B,A28))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A28)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A28)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8857,16 +8846,16 @@
       <c r="A29" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="84" t="str">
+      <c r="B29" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C29" s="84" t="str">
+      <c r="C29" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>SUL</v>
       </c>
-      <c r="D29" s="85"/>
-      <c r="E29" s="85" t="str">
+      <c r="D29" s="82"/>
+      <c r="E29" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8874,7 +8863,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>#CONCLUIDA</v>
       </c>
-      <c r="F29" s="85" t="str">
+      <c r="F29" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A29),COUNTIF(NORTE!B:B,A29),COUNTIF(SUL!B:B,A29))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A29)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A29)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8884,16 +8873,16 @@
       <c r="A30" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B30" s="84" t="str">
+      <c r="B30" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C30" s="84" t="str">
+      <c r="C30" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D30" s="85"/>
-      <c r="E30" s="85" t="str">
+      <c r="D30" s="82"/>
+      <c r="E30" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8901,7 +8890,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE DEFINITIVO</v>
       </c>
-      <c r="F30" s="85" t="str">
+      <c r="F30" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A30),COUNTIF(NORTE!B:B,A30),COUNTIF(SUL!B:B,A30))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A30)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A30)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8911,16 +8900,16 @@
       <c r="A31" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="84" t="str">
+      <c r="B31" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C31" s="84" t="str">
+      <c r="C31" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D31" s="85"/>
-      <c r="E31" s="85" t="str">
+      <c r="D31" s="82"/>
+      <c r="E31" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8928,7 +8917,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>DISTRATO</v>
       </c>
-      <c r="F31" s="85" t="str">
+      <c r="F31" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A31),COUNTIF(NORTE!B:B,A31),COUNTIF(SUL!B:B,A31))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A31)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A31)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -8938,16 +8927,16 @@
       <c r="A32" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B32" s="84" t="str">
+      <c r="B32" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>IGOR CARNEIRO</v>
       </c>
-      <c r="C32" s="84" t="str">
+      <c r="C32" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D32" s="85"/>
-      <c r="E32" s="85" t="str">
+      <c r="D32" s="82"/>
+      <c r="E32" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8955,7 +8944,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F32" s="85" t="str">
+      <c r="F32" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A32),COUNTIF(NORTE!B:B,A32),COUNTIF(SUL!B:B,A32))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A32)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A32)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -8965,16 +8954,16 @@
       <c r="A33" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B33" s="84" t="str">
+      <c r="B33" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>ERICK HYLARIO</v>
       </c>
-      <c r="C33" s="84" t="str">
+      <c r="C33" s="81" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D33" s="85"/>
-      <c r="E33" s="85" t="str">
+      <c r="D33" s="82"/>
+      <c r="E33" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -8982,7 +8971,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F33" s="85" t="str">
+      <c r="F33" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A33),COUNTIF(NORTE!B:B,A33),COUNTIF(SUL!B:B,A33))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A33)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A33)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -8992,7 +8981,7 @@
       <c r="A34" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B34" s="84" t="str">
+      <c r="B34" s="81" t="str">
         <f t="shared" ref="B34:B65" ca="1" si="2">UPPER(TRIM(UPPER(IFERROR(VLOOKUP(A34,INDIRECT("'BAIXADA'!$B$3:$I$51"),3,FALSE),
 IFERROR(VLOOKUP(A34,INDIRECT("'NORTE'!$B$3:$I$21"),3,FALSE),
 IFERROR(VLOOKUP(A34,INDIRECT("'SUL'!$B$3:$I$31"),3,FALSE),
@@ -9000,15 +8989,15 @@
 IFERROR(VLOOKUP(A34,INDIRECT("'ESPECIAIS'!$B$3:$I$27"),3,FALSE),""))))))))</f>
         <v>ERICK HYLARIO</v>
       </c>
-      <c r="C34" s="84" t="str">
+      <c r="C34" s="81" t="str">
         <f t="shared" ref="C34:C65" ca="1" si="3">IF(OR(B34="CARLOS FERNANDES", B34="GISELLE G. FONSECA"), "BAIXADA",
  IF(OR(B34="ISADORA ROSALINO", B34="JEHNIFFER PIRES"), "NORTE",
  IF(OR(B34="LUIZ FILHO", B34="MARCUS", B34="JAQUELINE PASTÓRIO"), "SUL",
  IF(OR(B34="AIMAR FILHO", B34="ERICK HYLARIO", B34="IGOR CARNEIRO", B34="CESAR", B34="DANRLEI"), "ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="85" t="str">
+      <c r="D34" s="82"/>
+      <c r="E34" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9016,7 +9005,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F34" s="85" t="str">
+      <c r="F34" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A34),COUNTIF(NORTE!B:B,A34),COUNTIF(SUL!B:B,A34))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A34)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A34)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -9026,16 +9015,16 @@
       <c r="A35" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B35" s="84" t="str">
+      <c r="B35" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C35" s="84" t="str">
+      <c r="C35" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D35" s="85"/>
-      <c r="E35" s="85" t="str">
+      <c r="D35" s="82"/>
+      <c r="E35" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9043,7 +9032,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F35" s="85" t="str">
+      <c r="F35" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A35),COUNTIF(NORTE!B:B,A35),COUNTIF(SUL!B:B,A35))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A35)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A35)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9053,16 +9042,16 @@
       <c r="A36" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B36" s="84" t="str">
+      <c r="B36" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>ERICK HYLARIO</v>
       </c>
-      <c r="C36" s="84" t="str">
+      <c r="C36" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D36" s="85"/>
-      <c r="E36" s="85" t="str">
+      <c r="D36" s="82"/>
+      <c r="E36" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9070,7 +9059,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F36" s="85" t="str">
+      <c r="F36" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A36),COUNTIF(NORTE!B:B,A36),COUNTIF(SUL!B:B,A36))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A36)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A36)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -9080,16 +9069,16 @@
       <c r="A37" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B37" s="84" t="str">
+      <c r="B37" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C37" s="84" t="str">
+      <c r="C37" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>SUL</v>
       </c>
-      <c r="D37" s="85"/>
-      <c r="E37" s="85" t="str">
+      <c r="D37" s="82"/>
+      <c r="E37" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9097,7 +9086,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F37" s="85" t="str">
+      <c r="F37" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A37),COUNTIF(NORTE!B:B,A37),COUNTIF(SUL!B:B,A37))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A37)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A37)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9107,16 +9096,16 @@
       <c r="A38" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B38" s="84" t="str">
+      <c r="B38" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C38" s="84" t="str">
+      <c r="C38" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>SUL</v>
       </c>
-      <c r="D38" s="85"/>
-      <c r="E38" s="85" t="str">
+      <c r="D38" s="82"/>
+      <c r="E38" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9124,7 +9113,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F38" s="85" t="str">
+      <c r="F38" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A38),COUNTIF(NORTE!B:B,A38),COUNTIF(SUL!B:B,A38))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A38)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A38)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9134,16 +9123,16 @@
       <c r="A39" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B39" s="84" t="str">
+      <c r="B39" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C39" s="84" t="str">
+      <c r="C39" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D39" s="85"/>
-      <c r="E39" s="85" t="str">
+      <c r="D39" s="82"/>
+      <c r="E39" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9151,7 +9140,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>DISTRATO</v>
       </c>
-      <c r="F39" s="85" t="str">
+      <c r="F39" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A39),COUNTIF(NORTE!B:B,A39),COUNTIF(SUL!B:B,A39))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A39)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A39)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9161,16 +9150,16 @@
       <c r="A40" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B40" s="84" t="str">
+      <c r="B40" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C40" s="84" t="str">
+      <c r="C40" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D40" s="85"/>
-      <c r="E40" s="85" t="str">
+      <c r="D40" s="82"/>
+      <c r="E40" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9178,7 +9167,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F40" s="85" t="str">
+      <c r="F40" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A40),COUNTIF(NORTE!B:B,A40),COUNTIF(SUL!B:B,A40))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A40)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A40)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9188,16 +9177,16 @@
       <c r="A41" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B41" s="84" t="str">
+      <c r="B41" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C41" s="84" t="str">
+      <c r="C41" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D41" s="85"/>
-      <c r="E41" s="85" t="str">
+      <c r="D41" s="82"/>
+      <c r="E41" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9205,7 +9194,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F41" s="85" t="str">
+      <c r="F41" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A41),COUNTIF(NORTE!B:B,A41),COUNTIF(SUL!B:B,A41))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A41)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A41)&gt;0,"ESPECIAIS",""))))</f>
         <v>CONTINGENCIA</v>
@@ -9215,16 +9204,16 @@
       <c r="A42" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B42" s="84" t="str">
+      <c r="B42" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C42" s="84" t="str">
+      <c r="C42" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D42" s="85"/>
-      <c r="E42" s="85" t="str">
+      <c r="D42" s="82"/>
+      <c r="E42" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9232,7 +9221,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F42" s="85" t="str">
+      <c r="F42" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A42),COUNTIF(NORTE!B:B,A42),COUNTIF(SUL!B:B,A42))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A42)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A42)&gt;0,"ESPECIAIS",""))))</f>
         <v>CONTINGENCIA</v>
@@ -9242,16 +9231,16 @@
       <c r="A43" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B43" s="84" t="str">
+      <c r="B43" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C43" s="84" t="str">
+      <c r="C43" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D43" s="85"/>
-      <c r="E43" s="85" t="str">
+      <c r="D43" s="82"/>
+      <c r="E43" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9259,7 +9248,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F43" s="85" t="str">
+      <c r="F43" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A43),COUNTIF(NORTE!B:B,A43),COUNTIF(SUL!B:B,A43))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A43)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A43)&gt;0,"ESPECIAIS",""))))</f>
         <v>CONTINGENCIA</v>
@@ -9269,16 +9258,16 @@
       <c r="A44" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B44" s="84" t="str">
+      <c r="B44" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C44" s="84" t="str">
+      <c r="C44" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D44" s="85"/>
-      <c r="E44" s="85" t="str">
+      <c r="D44" s="82"/>
+      <c r="E44" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9286,7 +9275,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F44" s="85" t="str">
+      <c r="F44" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A44),COUNTIF(NORTE!B:B,A44),COUNTIF(SUL!B:B,A44))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A44)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A44)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9296,16 +9285,16 @@
       <c r="A45" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B45" s="84" t="str">
+      <c r="B45" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C45" s="84" t="str">
+      <c r="C45" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D45" s="85"/>
-      <c r="E45" s="85" t="str">
+      <c r="D45" s="82"/>
+      <c r="E45" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9313,7 +9302,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F45" s="85" t="str">
+      <c r="F45" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A45),COUNTIF(NORTE!B:B,A45),COUNTIF(SUL!B:B,A45))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A45)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A45)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9323,16 +9312,16 @@
       <c r="A46" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B46" s="84" t="str">
+      <c r="B46" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C46" s="84" t="str">
+      <c r="C46" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D46" s="85"/>
-      <c r="E46" s="85" t="str">
+      <c r="D46" s="82"/>
+      <c r="E46" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9340,7 +9329,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>DISTRATO</v>
       </c>
-      <c r="F46" s="85" t="str">
+      <c r="F46" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A46),COUNTIF(NORTE!B:B,A46),COUNTIF(SUL!B:B,A46))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A46)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A46)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9350,16 +9339,16 @@
       <c r="A47" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B47" s="84" t="str">
+      <c r="B47" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C47" s="84" t="str">
+      <c r="C47" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>SUL</v>
       </c>
-      <c r="D47" s="85"/>
-      <c r="E47" s="85" t="str">
+      <c r="D47" s="82"/>
+      <c r="E47" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9367,7 +9356,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F47" s="85" t="str">
+      <c r="F47" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A47),COUNTIF(NORTE!B:B,A47),COUNTIF(SUL!B:B,A47))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A47)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A47)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9377,16 +9366,16 @@
       <c r="A48" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B48" s="84" t="str">
+      <c r="B48" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C48" s="84" t="str">
+      <c r="C48" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D48" s="85"/>
-      <c r="E48" s="85" t="str">
+      <c r="D48" s="82"/>
+      <c r="E48" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9394,7 +9383,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE DEFINITIVO</v>
       </c>
-      <c r="F48" s="85" t="str">
+      <c r="F48" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A48),COUNTIF(NORTE!B:B,A48),COUNTIF(SUL!B:B,A48))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A48)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A48)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9404,16 +9393,16 @@
       <c r="A49" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B49" s="84" t="str">
+      <c r="B49" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>JEHNIFFER PIRES</v>
       </c>
-      <c r="C49" s="84" t="str">
+      <c r="C49" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>NORTE</v>
       </c>
-      <c r="D49" s="85"/>
-      <c r="E49" s="85" t="str">
+      <c r="D49" s="82"/>
+      <c r="E49" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9421,7 +9410,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F49" s="85" t="str">
+      <c r="F49" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A49),COUNTIF(NORTE!B:B,A49),COUNTIF(SUL!B:B,A49))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A49)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A49)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9431,16 +9420,16 @@
       <c r="A50" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B50" s="84" t="str">
+      <c r="B50" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C50" s="84" t="str">
+      <c r="C50" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D50" s="85"/>
-      <c r="E50" s="85" t="str">
+      <c r="D50" s="82"/>
+      <c r="E50" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9448,7 +9437,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F50" s="85" t="str">
+      <c r="F50" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A50),COUNTIF(NORTE!B:B,A50),COUNTIF(SUL!B:B,A50))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A50)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A50)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9458,16 +9447,16 @@
       <c r="A51" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B51" s="84" t="str">
+      <c r="B51" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>JEHNIFFER PIRES</v>
       </c>
-      <c r="C51" s="84" t="str">
+      <c r="C51" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>NORTE</v>
       </c>
-      <c r="D51" s="85"/>
-      <c r="E51" s="85" t="str">
+      <c r="D51" s="82"/>
+      <c r="E51" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9475,7 +9464,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>#CONCLUIDA</v>
       </c>
-      <c r="F51" s="85" t="str">
+      <c r="F51" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A51),COUNTIF(NORTE!B:B,A51),COUNTIF(SUL!B:B,A51))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A51)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A51)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9485,16 +9474,16 @@
       <c r="A52" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B52" s="84" t="str">
+      <c r="B52" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>JEHNIFFER PIRES</v>
       </c>
-      <c r="C52" s="84" t="str">
+      <c r="C52" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>NORTE</v>
       </c>
-      <c r="D52" s="85"/>
-      <c r="E52" s="85" t="str">
+      <c r="D52" s="82"/>
+      <c r="E52" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9502,7 +9491,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>DISTRATO</v>
       </c>
-      <c r="F52" s="85" t="str">
+      <c r="F52" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A52),COUNTIF(NORTE!B:B,A52),COUNTIF(SUL!B:B,A52))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A52)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A52)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9512,16 +9501,16 @@
       <c r="A53" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B53" s="84" t="str">
+      <c r="B53" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>ISADORA ROSALINO</v>
       </c>
-      <c r="C53" s="84" t="str">
+      <c r="C53" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>NORTE</v>
       </c>
-      <c r="D53" s="85"/>
-      <c r="E53" s="85" t="str">
+      <c r="D53" s="82"/>
+      <c r="E53" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9529,7 +9518,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE PROVISORIO</v>
       </c>
-      <c r="F53" s="85" t="str">
+      <c r="F53" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A53),COUNTIF(NORTE!B:B,A53),COUNTIF(SUL!B:B,A53))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A53)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A53)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9539,16 +9528,16 @@
       <c r="A54" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B54" s="84" t="str">
+      <c r="B54" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>ISADORA ROSALINO</v>
       </c>
-      <c r="C54" s="84" t="str">
+      <c r="C54" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>NORTE</v>
       </c>
-      <c r="D54" s="85"/>
-      <c r="E54" s="85" t="str">
+      <c r="D54" s="82"/>
+      <c r="E54" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9556,7 +9545,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F54" s="85" t="str">
+      <c r="F54" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A54),COUNTIF(NORTE!B:B,A54),COUNTIF(SUL!B:B,A54))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A54)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A54)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9566,16 +9555,16 @@
       <c r="A55" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B55" s="84" t="str">
+      <c r="B55" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>ISADORA ROSALINO</v>
       </c>
-      <c r="C55" s="84" t="str">
+      <c r="C55" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>NORTE</v>
       </c>
-      <c r="D55" s="85"/>
-      <c r="E55" s="85" t="str">
+      <c r="D55" s="82"/>
+      <c r="E55" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9583,7 +9572,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F55" s="85" t="str">
+      <c r="F55" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A55),COUNTIF(NORTE!B:B,A55),COUNTIF(SUL!B:B,A55))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A55)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A55)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9593,16 +9582,16 @@
       <c r="A56" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B56" s="84" t="str">
+      <c r="B56" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C56" s="84" t="str">
+      <c r="C56" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D56" s="85"/>
-      <c r="E56" s="85" t="str">
+      <c r="D56" s="82"/>
+      <c r="E56" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9610,7 +9599,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F56" s="85" t="str">
+      <c r="F56" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A56),COUNTIF(NORTE!B:B,A56),COUNTIF(SUL!B:B,A56))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A56)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A56)&gt;0,"ESPECIAIS",""))))</f>
         <v>CONTINGENCIA</v>
@@ -9620,16 +9609,16 @@
       <c r="A57" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B57" s="84" t="str">
+      <c r="B57" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C57" s="84" t="str">
+      <c r="C57" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D57" s="85"/>
-      <c r="E57" s="85" t="str">
+      <c r="D57" s="82"/>
+      <c r="E57" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9637,7 +9626,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F57" s="85" t="str">
+      <c r="F57" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A57),COUNTIF(NORTE!B:B,A57),COUNTIF(SUL!B:B,A57))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A57)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A57)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9647,16 +9636,16 @@
       <c r="A58" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B58" s="84" t="str">
+      <c r="B58" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C58" s="84" t="str">
+      <c r="C58" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D58" s="85"/>
-      <c r="E58" s="85" t="str">
+      <c r="D58" s="82"/>
+      <c r="E58" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9664,7 +9653,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE DEFINITIVO</v>
       </c>
-      <c r="F58" s="85" t="str">
+      <c r="F58" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A58),COUNTIF(NORTE!B:B,A58),COUNTIF(SUL!B:B,A58))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A58)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A58)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9674,16 +9663,16 @@
       <c r="A59" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B59" s="84" t="str">
+      <c r="B59" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C59" s="84" t="str">
+      <c r="C59" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D59" s="85"/>
-      <c r="E59" s="85" t="str">
+      <c r="D59" s="82"/>
+      <c r="E59" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9691,7 +9680,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F59" s="85" t="str">
+      <c r="F59" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A59),COUNTIF(NORTE!B:B,A59),COUNTIF(SUL!B:B,A59))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A59)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A59)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9701,16 +9690,16 @@
       <c r="A60" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B60" s="84" t="str">
+      <c r="B60" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C60" s="84" t="str">
+      <c r="C60" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D60" s="85"/>
-      <c r="E60" s="85" t="str">
+      <c r="D60" s="82"/>
+      <c r="E60" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9718,7 +9707,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F60" s="85" t="str">
+      <c r="F60" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A60),COUNTIF(NORTE!B:B,A60),COUNTIF(SUL!B:B,A60))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A60)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A60)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9728,16 +9717,16 @@
       <c r="A61" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B61" s="84" t="str">
+      <c r="B61" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C61" s="84" t="str">
+      <c r="C61" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>SUL</v>
       </c>
-      <c r="D61" s="85"/>
-      <c r="E61" s="85" t="str">
+      <c r="D61" s="82"/>
+      <c r="E61" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9745,7 +9734,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F61" s="85" t="str">
+      <c r="F61" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A61),COUNTIF(NORTE!B:B,A61),COUNTIF(SUL!B:B,A61))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A61)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A61)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9755,16 +9744,16 @@
       <c r="A62" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B62" s="84" t="str">
+      <c r="B62" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C62" s="84" t="str">
+      <c r="C62" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D62" s="85"/>
-      <c r="E62" s="85" t="str">
+      <c r="D62" s="82"/>
+      <c r="E62" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9772,7 +9761,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE PROVISORIO</v>
       </c>
-      <c r="F62" s="85" t="str">
+      <c r="F62" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A62),COUNTIF(NORTE!B:B,A62),COUNTIF(SUL!B:B,A62))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A62)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A62)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9782,16 +9771,16 @@
       <c r="A63" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B63" s="84" t="str">
+      <c r="B63" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C63" s="84" t="str">
+      <c r="C63" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D63" s="85"/>
-      <c r="E63" s="85" t="str">
+      <c r="D63" s="82"/>
+      <c r="E63" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9799,7 +9788,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F63" s="85" t="str">
+      <c r="F63" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A63),COUNTIF(NORTE!B:B,A63),COUNTIF(SUL!B:B,A63))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A63)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A63)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9809,16 +9798,16 @@
       <c r="A64" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B64" s="84" t="str">
+      <c r="B64" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>ISADORA ROSALINO</v>
       </c>
-      <c r="C64" s="84" t="str">
+      <c r="C64" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>NORTE</v>
       </c>
-      <c r="D64" s="85"/>
-      <c r="E64" s="85" t="str">
+      <c r="D64" s="82"/>
+      <c r="E64" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9826,7 +9815,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>#CONCLUIDA</v>
       </c>
-      <c r="F64" s="85" t="str">
+      <c r="F64" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A64),COUNTIF(NORTE!B:B,A64),COUNTIF(SUL!B:B,A64))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A64)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A64)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9836,16 +9825,16 @@
       <c r="A65" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B65" s="84" t="str">
+      <c r="B65" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C65" s="84" t="str">
+      <c r="C65" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>SUL</v>
       </c>
-      <c r="D65" s="85"/>
-      <c r="E65" s="85" t="str">
+      <c r="D65" s="82"/>
+      <c r="E65" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9853,7 +9842,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F65" s="85" t="str">
+      <c r="F65" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A65),COUNTIF(NORTE!B:B,A65),COUNTIF(SUL!B:B,A65))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A65)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A65)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9863,7 +9852,7 @@
       <c r="A66" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B66" s="84" t="str">
+      <c r="B66" s="81" t="str">
         <f t="shared" ref="B66:B97" ca="1" si="4">UPPER(TRIM(UPPER(IFERROR(VLOOKUP(A66,INDIRECT("'BAIXADA'!$B$3:$I$51"),3,FALSE),
 IFERROR(VLOOKUP(A66,INDIRECT("'NORTE'!$B$3:$I$21"),3,FALSE),
 IFERROR(VLOOKUP(A66,INDIRECT("'SUL'!$B$3:$I$31"),3,FALSE),
@@ -9871,15 +9860,15 @@
 IFERROR(VLOOKUP(A66,INDIRECT("'ESPECIAIS'!$B$3:$I$27"),3,FALSE),""))))))))</f>
         <v>JEHNIFFER PIRES</v>
       </c>
-      <c r="C66" s="84" t="str">
+      <c r="C66" s="81" t="str">
         <f t="shared" ref="C66:C97" ca="1" si="5">IF(OR(B66="CARLOS FERNANDES", B66="GISELLE G. FONSECA"), "BAIXADA",
  IF(OR(B66="ISADORA ROSALINO", B66="JEHNIFFER PIRES"), "NORTE",
  IF(OR(B66="LUIZ FILHO", B66="MARCUS", B66="JAQUELINE PASTÓRIO"), "SUL",
  IF(OR(B66="AIMAR FILHO", B66="ERICK HYLARIO", B66="IGOR CARNEIRO", B66="CESAR", B66="DANRLEI"), "ESPECIAIS",""))))</f>
         <v>NORTE</v>
       </c>
-      <c r="D66" s="85"/>
-      <c r="E66" s="85" t="str">
+      <c r="D66" s="82"/>
+      <c r="E66" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9887,7 +9876,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F66" s="85" t="str">
+      <c r="F66" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A66),COUNTIF(NORTE!B:B,A66),COUNTIF(SUL!B:B,A66))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A66)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A66)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9897,16 +9886,16 @@
       <c r="A67" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B67" s="84" t="str">
+      <c r="B67" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C67" s="84" t="str">
+      <c r="C67" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D67" s="85"/>
-      <c r="E67" s="85" t="str">
+      <c r="D67" s="82"/>
+      <c r="E67" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9914,7 +9903,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F67" s="85" t="str">
+      <c r="F67" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A67),COUNTIF(NORTE!B:B,A67),COUNTIF(SUL!B:B,A67))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A67)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A67)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9924,16 +9913,16 @@
       <c r="A68" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B68" s="84" t="str">
+      <c r="B68" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C68" s="84" t="str">
+      <c r="C68" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D68" s="85"/>
-      <c r="E68" s="85" t="str">
+      <c r="D68" s="82"/>
+      <c r="E68" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9941,7 +9930,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>#CONCLUIDA</v>
       </c>
-      <c r="F68" s="85" t="str">
+      <c r="F68" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A68),COUNTIF(NORTE!B:B,A68),COUNTIF(SUL!B:B,A68))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A68)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A68)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9951,16 +9940,16 @@
       <c r="A69" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B69" s="84" t="str">
+      <c r="B69" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C69" s="84" t="str">
+      <c r="C69" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D69" s="85"/>
-      <c r="E69" s="85" t="str">
+      <c r="D69" s="82"/>
+      <c r="E69" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9968,7 +9957,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>#CONCLUIDA</v>
       </c>
-      <c r="F69" s="85" t="str">
+      <c r="F69" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A69),COUNTIF(NORTE!B:B,A69),COUNTIF(SUL!B:B,A69))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A69)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A69)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -9978,16 +9967,16 @@
       <c r="A70" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B70" s="84" t="str">
+      <c r="B70" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C70" s="84" t="str">
+      <c r="C70" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D70" s="85"/>
-      <c r="E70" s="85" t="str">
+      <c r="D70" s="82"/>
+      <c r="E70" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -9995,7 +9984,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F70" s="85" t="str">
+      <c r="F70" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A70),COUNTIF(NORTE!B:B,A70),COUNTIF(SUL!B:B,A70))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A70)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A70)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10005,16 +9994,16 @@
       <c r="A71" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B71" s="84" t="str">
+      <c r="B71" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>LUIZ FILHO</v>
       </c>
-      <c r="C71" s="84" t="str">
+      <c r="C71" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>SUL</v>
       </c>
-      <c r="D71" s="85"/>
-      <c r="E71" s="85" t="str">
+      <c r="D71" s="82"/>
+      <c r="E71" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10022,7 +10011,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F71" s="85" t="str">
+      <c r="F71" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A71),COUNTIF(NORTE!B:B,A71),COUNTIF(SUL!B:B,A71))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A71)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A71)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10032,16 +10021,16 @@
       <c r="A72" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B72" s="84" t="str">
+      <c r="B72" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C72" s="84" t="str">
+      <c r="C72" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>SUL</v>
       </c>
-      <c r="D72" s="85"/>
-      <c r="E72" s="85" t="str">
+      <c r="D72" s="82"/>
+      <c r="E72" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10049,7 +10038,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F72" s="85" t="str">
+      <c r="F72" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A72),COUNTIF(NORTE!B:B,A72),COUNTIF(SUL!B:B,A72))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A72)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A72)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10059,16 +10048,16 @@
       <c r="A73" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B73" s="84" t="str">
+      <c r="B73" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>ISADORA ROSALINO</v>
       </c>
-      <c r="C73" s="84" t="str">
+      <c r="C73" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>NORTE</v>
       </c>
-      <c r="D73" s="85"/>
-      <c r="E73" s="85" t="str">
+      <c r="D73" s="82"/>
+      <c r="E73" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10076,7 +10065,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F73" s="85" t="str">
+      <c r="F73" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A73),COUNTIF(NORTE!B:B,A73),COUNTIF(SUL!B:B,A73))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A73)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A73)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10086,16 +10075,16 @@
       <c r="A74" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B74" s="84" t="str">
+      <c r="B74" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>ISADORA ROSALINO</v>
       </c>
-      <c r="C74" s="84" t="str">
+      <c r="C74" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>NORTE</v>
       </c>
-      <c r="D74" s="85"/>
-      <c r="E74" s="85" t="str">
+      <c r="D74" s="82"/>
+      <c r="E74" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10103,7 +10092,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F74" s="85" t="str">
+      <c r="F74" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A74),COUNTIF(NORTE!B:B,A74),COUNTIF(SUL!B:B,A74))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A74)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A74)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10113,16 +10102,16 @@
       <c r="A75" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B75" s="84" t="str">
+      <c r="B75" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>ISADORA ROSALINO</v>
       </c>
-      <c r="C75" s="84" t="str">
+      <c r="C75" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>NORTE</v>
       </c>
-      <c r="D75" s="85"/>
-      <c r="E75" s="85" t="str">
+      <c r="D75" s="82"/>
+      <c r="E75" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10130,7 +10119,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F75" s="85" t="str">
+      <c r="F75" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A75),COUNTIF(NORTE!B:B,A75),COUNTIF(SUL!B:B,A75))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A75)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A75)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10140,16 +10129,16 @@
       <c r="A76" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B76" s="84" t="str">
+      <c r="B76" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>LUIZ FILHO</v>
       </c>
-      <c r="C76" s="84" t="str">
+      <c r="C76" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>SUL</v>
       </c>
-      <c r="D76" s="85"/>
-      <c r="E76" s="85" t="str">
+      <c r="D76" s="82"/>
+      <c r="E76" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10157,7 +10146,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F76" s="85" t="str">
+      <c r="F76" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A76),COUNTIF(NORTE!B:B,A76),COUNTIF(SUL!B:B,A76))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A76)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A76)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10167,16 +10156,16 @@
       <c r="A77" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B77" s="84" t="str">
+      <c r="B77" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>ISADORA ROSALINO</v>
       </c>
-      <c r="C77" s="84" t="str">
+      <c r="C77" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>NORTE</v>
       </c>
-      <c r="D77" s="85"/>
-      <c r="E77" s="85" t="str">
+      <c r="D77" s="82"/>
+      <c r="E77" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10184,7 +10173,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F77" s="85" t="str">
+      <c r="F77" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A77),COUNTIF(NORTE!B:B,A77),COUNTIF(SUL!B:B,A77))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A77)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A77)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10194,16 +10183,16 @@
       <c r="A78" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B78" s="84" t="str">
+      <c r="B78" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C78" s="84" t="str">
+      <c r="C78" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>SUL</v>
       </c>
-      <c r="D78" s="85"/>
-      <c r="E78" s="85" t="str">
+      <c r="D78" s="82"/>
+      <c r="E78" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10211,7 +10200,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>#CONCLUIDA</v>
       </c>
-      <c r="F78" s="85" t="str">
+      <c r="F78" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A78),COUNTIF(NORTE!B:B,A78),COUNTIF(SUL!B:B,A78))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A78)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A78)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10221,16 +10210,16 @@
       <c r="A79" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B79" s="84" t="str">
+      <c r="B79" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C79" s="84" t="str">
+      <c r="C79" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D79" s="85"/>
-      <c r="E79" s="85" t="str">
+      <c r="D79" s="82"/>
+      <c r="E79" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10238,7 +10227,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F79" s="85" t="str">
+      <c r="F79" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A79),COUNTIF(NORTE!B:B,A79),COUNTIF(SUL!B:B,A79))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A79)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A79)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10248,16 +10237,16 @@
       <c r="A80" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B80" s="84" t="str">
+      <c r="B80" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C80" s="84" t="str">
+      <c r="C80" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D80" s="85"/>
-      <c r="E80" s="85" t="str">
+      <c r="D80" s="82"/>
+      <c r="E80" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10265,7 +10254,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>#CONCLUIDA</v>
       </c>
-      <c r="F80" s="85" t="str">
+      <c r="F80" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A80),COUNTIF(NORTE!B:B,A80),COUNTIF(SUL!B:B,A80))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A80)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A80)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10275,16 +10264,16 @@
       <c r="A81" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B81" s="84" t="str">
+      <c r="B81" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C81" s="84" t="str">
+      <c r="C81" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D81" s="85"/>
-      <c r="E81" s="85" t="str">
+      <c r="D81" s="82"/>
+      <c r="E81" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10292,7 +10281,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>#CONCLUIDA</v>
       </c>
-      <c r="F81" s="85" t="str">
+      <c r="F81" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A81),COUNTIF(NORTE!B:B,A81),COUNTIF(SUL!B:B,A81))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A81)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A81)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10302,16 +10291,16 @@
       <c r="A82" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B82" s="84" t="str">
+      <c r="B82" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C82" s="84" t="str">
+      <c r="C82" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D82" s="85"/>
-      <c r="E82" s="85" t="str">
+      <c r="D82" s="82"/>
+      <c r="E82" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10319,7 +10308,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE DEFINITIVO</v>
       </c>
-      <c r="F82" s="85" t="str">
+      <c r="F82" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A82),COUNTIF(NORTE!B:B,A82),COUNTIF(SUL!B:B,A82))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A82)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A82)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10329,16 +10318,16 @@
       <c r="A83" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B83" s="84" t="str">
+      <c r="B83" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C83" s="84" t="str">
+      <c r="C83" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>SUL</v>
       </c>
-      <c r="D83" s="85"/>
-      <c r="E83" s="85" t="str">
+      <c r="D83" s="82"/>
+      <c r="E83" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10346,7 +10335,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>#CONCLUIDA</v>
       </c>
-      <c r="F83" s="85" t="str">
+      <c r="F83" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A83),COUNTIF(NORTE!B:B,A83),COUNTIF(SUL!B:B,A83))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A83)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A83)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10356,16 +10345,16 @@
       <c r="A84" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B84" s="84" t="str">
+      <c r="B84" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C84" s="84" t="str">
+      <c r="C84" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>SUL</v>
       </c>
-      <c r="D84" s="85"/>
-      <c r="E84" s="85" t="str">
+      <c r="D84" s="82"/>
+      <c r="E84" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10373,7 +10362,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F84" s="85" t="str">
+      <c r="F84" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A84),COUNTIF(NORTE!B:B,A84),COUNTIF(SUL!B:B,A84))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A84)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A84)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10383,16 +10372,16 @@
       <c r="A85" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B85" s="84" t="str">
+      <c r="B85" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>LUIZ FILHO</v>
       </c>
-      <c r="C85" s="84" t="str">
+      <c r="C85" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>SUL</v>
       </c>
-      <c r="D85" s="85"/>
-      <c r="E85" s="85" t="str">
+      <c r="D85" s="82"/>
+      <c r="E85" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10400,7 +10389,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>DISTRATO</v>
       </c>
-      <c r="F85" s="85" t="str">
+      <c r="F85" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A85),COUNTIF(NORTE!B:B,A85),COUNTIF(SUL!B:B,A85))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A85)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A85)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10410,16 +10399,16 @@
       <c r="A86" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B86" s="84" t="str">
+      <c r="B86" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C86" s="84" t="str">
+      <c r="C86" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>SUL</v>
       </c>
-      <c r="D86" s="85"/>
-      <c r="E86" s="85" t="str">
+      <c r="D86" s="82"/>
+      <c r="E86" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10427,7 +10416,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F86" s="85" t="str">
+      <c r="F86" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A86),COUNTIF(NORTE!B:B,A86),COUNTIF(SUL!B:B,A86))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A86)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A86)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10437,16 +10426,16 @@
       <c r="A87" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B87" s="84" t="str">
+      <c r="B87" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C87" s="84" t="str">
+      <c r="C87" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D87" s="85"/>
-      <c r="E87" s="85" t="str">
+      <c r="D87" s="82"/>
+      <c r="E87" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10454,7 +10443,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F87" s="85" t="str">
+      <c r="F87" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A87),COUNTIF(NORTE!B:B,A87),COUNTIF(SUL!B:B,A87))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A87)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A87)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10464,16 +10453,16 @@
       <c r="A88" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B88" s="84" t="str">
+      <c r="B88" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>ISADORA ROSALINO</v>
       </c>
-      <c r="C88" s="84" t="str">
+      <c r="C88" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>NORTE</v>
       </c>
-      <c r="D88" s="85"/>
-      <c r="E88" s="85" t="str">
+      <c r="D88" s="82"/>
+      <c r="E88" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10481,7 +10470,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F88" s="85" t="str">
+      <c r="F88" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A88),COUNTIF(NORTE!B:B,A88),COUNTIF(SUL!B:B,A88))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A88)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A88)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10491,16 +10480,16 @@
       <c r="A89" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B89" s="84" t="str">
+      <c r="B89" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C89" s="84" t="str">
+      <c r="C89" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D89" s="85"/>
-      <c r="E89" s="85" t="str">
+      <c r="D89" s="82"/>
+      <c r="E89" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10508,7 +10497,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE DEFINITIVO</v>
       </c>
-      <c r="F89" s="85" t="str">
+      <c r="F89" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A89),COUNTIF(NORTE!B:B,A89),COUNTIF(SUL!B:B,A89))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A89)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A89)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10518,16 +10507,16 @@
       <c r="A90" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B90" s="84" t="str">
+      <c r="B90" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C90" s="84" t="str">
+      <c r="C90" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D90" s="85"/>
-      <c r="E90" s="85" t="str">
+      <c r="D90" s="82"/>
+      <c r="E90" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10535,7 +10524,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>#CONCLUIDA</v>
       </c>
-      <c r="F90" s="85" t="str">
+      <c r="F90" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A90),COUNTIF(NORTE!B:B,A90),COUNTIF(SUL!B:B,A90))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A90)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A90)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10545,16 +10534,16 @@
       <c r="A91" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B91" s="84" t="str">
+      <c r="B91" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C91" s="84" t="str">
+      <c r="C91" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D91" s="85"/>
-      <c r="E91" s="85" t="str">
+      <c r="D91" s="82"/>
+      <c r="E91" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10562,7 +10551,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F91" s="85" t="str">
+      <c r="F91" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A91),COUNTIF(NORTE!B:B,A91),COUNTIF(SUL!B:B,A91))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A91)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A91)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10572,16 +10561,16 @@
       <c r="A92" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B92" s="84" t="str">
+      <c r="B92" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C92" s="84" t="str">
+      <c r="C92" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D92" s="85"/>
-      <c r="E92" s="85" t="str">
+      <c r="D92" s="82"/>
+      <c r="E92" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10589,7 +10578,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F92" s="85" t="str">
+      <c r="F92" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A92),COUNTIF(NORTE!B:B,A92),COUNTIF(SUL!B:B,A92))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A92)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A92)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10599,16 +10588,16 @@
       <c r="A93" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B93" s="84" t="str">
+      <c r="B93" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C93" s="84" t="str">
+      <c r="C93" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D93" s="85"/>
-      <c r="E93" s="85" t="str">
+      <c r="D93" s="82"/>
+      <c r="E93" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10616,7 +10605,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE DEFINITIVO</v>
       </c>
-      <c r="F93" s="85" t="str">
+      <c r="F93" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A93),COUNTIF(NORTE!B:B,A93),COUNTIF(SUL!B:B,A93))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A93)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A93)&gt;0,"ESPECIAIS",""))))</f>
         <v>CONTINGENCIA</v>
@@ -10626,16 +10615,16 @@
       <c r="A94" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B94" s="84" t="str">
+      <c r="B94" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C94" s="84" t="str">
+      <c r="C94" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D94" s="85"/>
-      <c r="E94" s="85" t="str">
+      <c r="D94" s="82"/>
+      <c r="E94" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10643,7 +10632,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE DEFINITIVO</v>
       </c>
-      <c r="F94" s="85" t="str">
+      <c r="F94" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A94),COUNTIF(NORTE!B:B,A94),COUNTIF(SUL!B:B,A94))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A94)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A94)&gt;0,"ESPECIAIS",""))))</f>
         <v>CONTINGENCIA</v>
@@ -10653,16 +10642,16 @@
       <c r="A95" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B95" s="84" t="str">
+      <c r="B95" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C95" s="84" t="str">
+      <c r="C95" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>SUL</v>
       </c>
-      <c r="D95" s="85"/>
-      <c r="E95" s="85" t="str">
+      <c r="D95" s="82"/>
+      <c r="E95" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10670,7 +10659,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F95" s="85" t="str">
+      <c r="F95" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A95),COUNTIF(NORTE!B:B,A95),COUNTIF(SUL!B:B,A95))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A95)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A95)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10680,16 +10669,16 @@
       <c r="A96" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B96" s="84" t="str">
+      <c r="B96" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C96" s="84" t="str">
+      <c r="C96" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D96" s="85"/>
-      <c r="E96" s="85" t="str">
+      <c r="D96" s="82"/>
+      <c r="E96" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10697,7 +10686,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE DEFINITIVO</v>
       </c>
-      <c r="F96" s="85" t="str">
+      <c r="F96" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A96),COUNTIF(NORTE!B:B,A96),COUNTIF(SUL!B:B,A96))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A96)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A96)&gt;0,"ESPECIAIS",""))))</f>
         <v>CONTINGENCIA</v>
@@ -10707,16 +10696,16 @@
       <c r="A97" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B97" s="84" t="str">
+      <c r="B97" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C97" s="84" t="str">
+      <c r="C97" s="81" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>SUL</v>
       </c>
-      <c r="D97" s="85"/>
-      <c r="E97" s="85" t="str">
+      <c r="D97" s="82"/>
+      <c r="E97" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10724,7 +10713,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F97" s="85" t="str">
+      <c r="F97" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A97),COUNTIF(NORTE!B:B,A97),COUNTIF(SUL!B:B,A97))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A97)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A97)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10734,7 +10723,7 @@
       <c r="A98" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B98" s="84" t="str">
+      <c r="B98" s="81" t="str">
         <f t="shared" ref="B98:B129" ca="1" si="6">UPPER(TRIM(UPPER(IFERROR(VLOOKUP(A98,INDIRECT("'BAIXADA'!$B$3:$I$51"),3,FALSE),
 IFERROR(VLOOKUP(A98,INDIRECT("'NORTE'!$B$3:$I$21"),3,FALSE),
 IFERROR(VLOOKUP(A98,INDIRECT("'SUL'!$B$3:$I$31"),3,FALSE),
@@ -10742,15 +10731,15 @@
 IFERROR(VLOOKUP(A98,INDIRECT("'ESPECIAIS'!$B$3:$I$27"),3,FALSE),""))))))))</f>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C98" s="84" t="str">
+      <c r="C98" s="81" t="str">
         <f t="shared" ref="C98:C129" ca="1" si="7">IF(OR(B98="CARLOS FERNANDES", B98="GISELLE G. FONSECA"), "BAIXADA",
  IF(OR(B98="ISADORA ROSALINO", B98="JEHNIFFER PIRES"), "NORTE",
  IF(OR(B98="LUIZ FILHO", B98="MARCUS", B98="JAQUELINE PASTÓRIO"), "SUL",
  IF(OR(B98="AIMAR FILHO", B98="ERICK HYLARIO", B98="IGOR CARNEIRO", B98="CESAR", B98="DANRLEI"), "ESPECIAIS",""))))</f>
         <v>BAIXADA</v>
       </c>
-      <c r="D98" s="85"/>
-      <c r="E98" s="85" t="str">
+      <c r="D98" s="82"/>
+      <c r="E98" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10758,7 +10747,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F98" s="85" t="str">
+      <c r="F98" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A98),COUNTIF(NORTE!B:B,A98),COUNTIF(SUL!B:B,A98))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A98)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A98)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10768,16 +10757,16 @@
       <c r="A99" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B99" s="84" t="str">
+      <c r="B99" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C99" s="84" t="str">
+      <c r="C99" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D99" s="85"/>
-      <c r="E99" s="85" t="str">
+      <c r="D99" s="82"/>
+      <c r="E99" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10785,7 +10774,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>#CONCLUIDA</v>
       </c>
-      <c r="F99" s="85" t="str">
+      <c r="F99" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A99),COUNTIF(NORTE!B:B,A99),COUNTIF(SUL!B:B,A99))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A99)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A99)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10795,16 +10784,16 @@
       <c r="A100" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B100" s="84" t="str">
+      <c r="B100" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C100" s="84" t="str">
+      <c r="C100" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D100" s="85"/>
-      <c r="E100" s="85" t="str">
+      <c r="D100" s="82"/>
+      <c r="E100" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10812,7 +10801,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F100" s="85" t="str">
+      <c r="F100" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A100),COUNTIF(NORTE!B:B,A100),COUNTIF(SUL!B:B,A100))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A100)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A100)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10822,16 +10811,16 @@
       <c r="A101" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B101" s="84" t="str">
+      <c r="B101" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>MARCUS</v>
       </c>
-      <c r="C101" s="84" t="str">
+      <c r="C101" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>SUL</v>
       </c>
-      <c r="D101" s="86"/>
-      <c r="E101" s="86" t="str">
+      <c r="D101" s="83"/>
+      <c r="E101" s="83" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10839,7 +10828,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE DEFINITIVO</v>
       </c>
-      <c r="F101" s="85" t="str">
+      <c r="F101" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A101),COUNTIF(NORTE!B:B,A101),COUNTIF(SUL!B:B,A101))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A101)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A101)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -10849,16 +10838,16 @@
       <c r="A102" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B102" s="84" t="str">
+      <c r="B102" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C102" s="84" t="str">
+      <c r="C102" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>SUL</v>
       </c>
-      <c r="D102" s="86"/>
-      <c r="E102" s="86" t="str">
+      <c r="D102" s="83"/>
+      <c r="E102" s="83" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10866,7 +10855,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F102" s="85" t="str">
+      <c r="F102" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A102),COUNTIF(NORTE!B:B,A102),COUNTIF(SUL!B:B,A102))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A102)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A102)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -10876,16 +10865,16 @@
       <c r="A103" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B103" s="84" t="str">
+      <c r="B103" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>ERICK HYLARIO</v>
       </c>
-      <c r="C103" s="84" t="str">
+      <c r="C103" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D103" s="85"/>
-      <c r="E103" s="85" t="str">
+      <c r="D103" s="82"/>
+      <c r="E103" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10893,7 +10882,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE DEFINITIVO</v>
       </c>
-      <c r="F103" s="85" t="str">
+      <c r="F103" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A103),COUNTIF(NORTE!B:B,A103),COUNTIF(SUL!B:B,A103))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A103)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A103)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -10903,16 +10892,16 @@
       <c r="A104" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B104" s="84" t="str">
+      <c r="B104" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>CESAR</v>
       </c>
-      <c r="C104" s="84" t="str">
+      <c r="C104" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D104" s="85"/>
-      <c r="E104" s="85" t="str">
+      <c r="D104" s="82"/>
+      <c r="E104" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10920,7 +10909,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F104" s="85" t="str">
+      <c r="F104" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A104),COUNTIF(NORTE!B:B,A104),COUNTIF(SUL!B:B,A104))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A104)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A104)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -10930,16 +10919,16 @@
       <c r="A105" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B105" s="84" t="str">
+      <c r="B105" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>ISADORA ROSALINO</v>
       </c>
-      <c r="C105" s="84" t="str">
+      <c r="C105" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>NORTE</v>
       </c>
-      <c r="D105" s="86"/>
-      <c r="E105" s="85" t="str">
+      <c r="D105" s="83"/>
+      <c r="E105" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10947,7 +10936,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>#CONCLUIDA</v>
       </c>
-      <c r="F105" s="85" t="str">
+      <c r="F105" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A105),COUNTIF(NORTE!B:B,A105),COUNTIF(SUL!B:B,A105))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A105)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A105)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10957,16 +10946,16 @@
       <c r="A106" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B106" s="84" t="str">
+      <c r="B106" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C106" s="84" t="str">
+      <c r="C106" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D106" s="86"/>
-      <c r="E106" s="85" t="str">
+      <c r="D106" s="83"/>
+      <c r="E106" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -10974,7 +10963,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F106" s="85" t="str">
+      <c r="F106" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A106),COUNTIF(NORTE!B:B,A106),COUNTIF(SUL!B:B,A106))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A106)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A106)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -10984,16 +10973,16 @@
       <c r="A107" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B107" s="84" t="str">
+      <c r="B107" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>AIMAR FILHO</v>
       </c>
-      <c r="C107" s="84" t="str">
+      <c r="C107" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D107" s="86"/>
-      <c r="E107" s="85" t="str">
+      <c r="D107" s="83"/>
+      <c r="E107" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11001,7 +10990,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE DEFINITIVO</v>
       </c>
-      <c r="F107" s="85" t="str">
+      <c r="F107" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A107),COUNTIF(NORTE!B:B,A107),COUNTIF(SUL!B:B,A107))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A107)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A107)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -11011,16 +11000,16 @@
       <c r="A108" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B108" s="84" t="str">
+      <c r="B108" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>IGOR CARNEIRO</v>
       </c>
-      <c r="C108" s="84" t="str">
+      <c r="C108" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D108" s="86"/>
-      <c r="E108" s="86" t="str">
+      <c r="D108" s="83"/>
+      <c r="E108" s="83" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11028,7 +11017,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F108" s="85" t="str">
+      <c r="F108" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A108),COUNTIF(NORTE!B:B,A108),COUNTIF(SUL!B:B,A108))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A108)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A108)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -11038,16 +11027,16 @@
       <c r="A109" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B109" s="84" t="str">
+      <c r="B109" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C109" s="84" t="str">
+      <c r="C109" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D109" s="86"/>
-      <c r="E109" s="86" t="str">
+      <c r="D109" s="83"/>
+      <c r="E109" s="83" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11055,7 +11044,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>#CONCLUIDA</v>
       </c>
-      <c r="F109" s="85" t="str">
+      <c r="F109" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A109),COUNTIF(NORTE!B:B,A109),COUNTIF(SUL!B:B,A109))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A109)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A109)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -11065,16 +11054,16 @@
       <c r="A110" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B110" s="84" t="str">
+      <c r="B110" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C110" s="84" t="str">
+      <c r="C110" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D110" s="85"/>
-      <c r="E110" s="85" t="str">
+      <c r="D110" s="82"/>
+      <c r="E110" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11082,7 +11071,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>#CONCLUIDA</v>
       </c>
-      <c r="F110" s="85" t="str">
+      <c r="F110" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A110),COUNTIF(NORTE!B:B,A110),COUNTIF(SUL!B:B,A110))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A110)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A110)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -11092,16 +11081,16 @@
       <c r="A111" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B111" s="84" t="str">
+      <c r="B111" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C111" s="84" t="str">
+      <c r="C111" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>SUL</v>
       </c>
-      <c r="D111" s="86"/>
-      <c r="E111" s="85" t="str">
+      <c r="D111" s="83"/>
+      <c r="E111" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11109,7 +11098,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F111" s="85" t="str">
+      <c r="F111" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A111),COUNTIF(NORTE!B:B,A111),COUNTIF(SUL!B:B,A111))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A111)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A111)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -11119,16 +11108,16 @@
       <c r="A112" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B112" s="84" t="str">
+      <c r="B112" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C112" s="84" t="str">
+      <c r="C112" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>SUL</v>
       </c>
-      <c r="D112" s="85"/>
-      <c r="E112" s="85" t="str">
+      <c r="D112" s="82"/>
+      <c r="E112" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11136,7 +11125,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F112" s="85" t="str">
+      <c r="F112" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A112),COUNTIF(NORTE!B:B,A112),COUNTIF(SUL!B:B,A112))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A112)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A112)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -11146,16 +11135,16 @@
       <c r="A113" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B113" s="84" t="str">
+      <c r="B113" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>ERICK HYLARIO</v>
       </c>
-      <c r="C113" s="84" t="str">
+      <c r="C113" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D113" s="85"/>
-      <c r="E113" s="85" t="str">
+      <c r="D113" s="82"/>
+      <c r="E113" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11163,7 +11152,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE PROVISORIO</v>
       </c>
-      <c r="F113" s="85" t="str">
+      <c r="F113" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A113),COUNTIF(NORTE!B:B,A113),COUNTIF(SUL!B:B,A113))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A113)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A113)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -11173,16 +11162,16 @@
       <c r="A114" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B114" s="84" t="str">
+      <c r="B114" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C114" s="84" t="str">
+      <c r="C114" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>SUL</v>
       </c>
-      <c r="D114" s="85"/>
-      <c r="E114" s="85" t="str">
+      <c r="D114" s="82"/>
+      <c r="E114" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11190,7 +11179,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>DISTRATO</v>
       </c>
-      <c r="F114" s="85" t="str">
+      <c r="F114" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A114),COUNTIF(NORTE!B:B,A114),COUNTIF(SUL!B:B,A114))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A114)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A114)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -11200,16 +11189,16 @@
       <c r="A115" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B115" s="84" t="str">
+      <c r="B115" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>ERICK HYLARIO</v>
       </c>
-      <c r="C115" s="84" t="str">
+      <c r="C115" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D115" s="85"/>
-      <c r="E115" s="85" t="str">
+      <c r="D115" s="82"/>
+      <c r="E115" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11217,7 +11206,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F115" s="85" t="str">
+      <c r="F115" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A115),COUNTIF(NORTE!B:B,A115),COUNTIF(SUL!B:B,A115))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A115)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A115)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -11227,16 +11216,16 @@
       <c r="A116" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B116" s="84" t="str">
+      <c r="B116" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>ERICK HYLARIO</v>
       </c>
-      <c r="C116" s="84" t="str">
+      <c r="C116" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D116" s="86"/>
-      <c r="E116" s="85" t="str">
+      <c r="D116" s="83"/>
+      <c r="E116" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11244,7 +11233,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>DISTRATO</v>
       </c>
-      <c r="F116" s="85" t="str">
+      <c r="F116" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A116),COUNTIF(NORTE!B:B,A116),COUNTIF(SUL!B:B,A116))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A116)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A116)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -11254,16 +11243,16 @@
       <c r="A117" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B117" s="84" t="str">
+      <c r="B117" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>ERICK HYLARIO</v>
       </c>
-      <c r="C117" s="84" t="str">
+      <c r="C117" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D117" s="85"/>
-      <c r="E117" s="85" t="str">
+      <c r="D117" s="82"/>
+      <c r="E117" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11271,7 +11260,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>DISTRATO</v>
       </c>
-      <c r="F117" s="85" t="str">
+      <c r="F117" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A117),COUNTIF(NORTE!B:B,A117),COUNTIF(SUL!B:B,A117))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A117)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A117)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -11281,16 +11270,16 @@
       <c r="A118" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B118" s="84" t="str">
+      <c r="B118" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>JEHNIFFER PIRES</v>
       </c>
-      <c r="C118" s="84" t="str">
+      <c r="C118" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>NORTE</v>
       </c>
-      <c r="D118" s="85"/>
-      <c r="E118" s="85" t="str">
+      <c r="D118" s="82"/>
+      <c r="E118" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11298,7 +11287,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F118" s="85" t="str">
+      <c r="F118" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A118),COUNTIF(NORTE!B:B,A118),COUNTIF(SUL!B:B,A118))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A118)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A118)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -11308,16 +11297,16 @@
       <c r="A119" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B119" s="84" t="str">
+      <c r="B119" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C119" s="84" t="str">
+      <c r="C119" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>SUL</v>
       </c>
-      <c r="D119" s="86"/>
-      <c r="E119" s="85" t="str">
+      <c r="D119" s="83"/>
+      <c r="E119" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11325,7 +11314,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F119" s="85" t="str">
+      <c r="F119" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A119),COUNTIF(NORTE!B:B,A119),COUNTIF(SUL!B:B,A119))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A119)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A119)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -11335,16 +11324,16 @@
       <c r="A120" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B120" s="84" t="str">
+      <c r="B120" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C120" s="84" t="str">
+      <c r="C120" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D120" s="85"/>
-      <c r="E120" s="85" t="str">
+      <c r="D120" s="82"/>
+      <c r="E120" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11352,7 +11341,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE DEFINITIVO</v>
       </c>
-      <c r="F120" s="85" t="str">
+      <c r="F120" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A120),COUNTIF(NORTE!B:B,A120),COUNTIF(SUL!B:B,A120))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A120)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A120)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -11362,16 +11351,16 @@
       <c r="A121" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B121" s="84" t="str">
+      <c r="B121" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>JEHNIFFER PIRES</v>
       </c>
-      <c r="C121" s="84" t="str">
+      <c r="C121" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>NORTE</v>
       </c>
-      <c r="D121" s="85"/>
-      <c r="E121" s="85" t="str">
+      <c r="D121" s="82"/>
+      <c r="E121" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11379,7 +11368,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F121" s="85" t="str">
+      <c r="F121" s="82" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A121),COUNTIF(NORTE!B:B,A121),COUNTIF(SUL!B:B,A121))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A121)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A121)&gt;0,"ESPECIAIS",""))))</f>
         <v>CONTINGENCIA</v>
@@ -11389,16 +11378,16 @@
       <c r="A122" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B122" s="84" t="str">
+      <c r="B122" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>JAQUELINE PASTÓRIO</v>
       </c>
-      <c r="C122" s="84" t="str">
+      <c r="C122" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>SUL</v>
       </c>
-      <c r="D122" s="86"/>
-      <c r="E122" s="85" t="str">
+      <c r="D122" s="83"/>
+      <c r="E122" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11406,7 +11395,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F122" s="86" t="str">
+      <c r="F122" s="83" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A122),COUNTIF(NORTE!B:B,A122),COUNTIF(SUL!B:B,A122))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A122)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A122)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -11416,16 +11405,16 @@
       <c r="A123" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B123" s="84" t="str">
+      <c r="B123" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>ERICK HYLARIO</v>
       </c>
-      <c r="C123" s="84" t="str">
+      <c r="C123" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D123" s="86"/>
-      <c r="E123" s="85" t="str">
+      <c r="D123" s="83"/>
+      <c r="E123" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11433,7 +11422,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>ACEITE PROVISORIO</v>
       </c>
-      <c r="F123" s="86" t="str">
+      <c r="F123" s="83" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A123),COUNTIF(NORTE!B:B,A123),COUNTIF(SUL!B:B,A123))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A123)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A123)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -11443,16 +11432,16 @@
       <c r="A124" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B124" s="84" t="str">
+      <c r="B124" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>AIMAR FILHO</v>
       </c>
-      <c r="C124" s="84" t="str">
+      <c r="C124" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D124" s="86"/>
-      <c r="E124" s="85" t="str">
+      <c r="D124" s="83"/>
+      <c r="E124" s="82" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11460,7 +11449,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>DISTRATO</v>
       </c>
-      <c r="F124" s="86" t="str">
+      <c r="F124" s="83" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A124),COUNTIF(NORTE!B:B,A124),COUNTIF(SUL!B:B,A124))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A124)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A124)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -11470,16 +11459,16 @@
       <c r="A125" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="B125" s="93" t="str">
+      <c r="B125" s="90" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C125" s="93" t="str">
+      <c r="C125" s="90" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D125" s="86"/>
-      <c r="E125" s="86" t="str">
+      <c r="D125" s="83"/>
+      <c r="E125" s="83" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11487,7 +11476,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F125" s="86" t="str">
+      <c r="F125" s="83" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A125),COUNTIF(NORTE!B:B,A125),COUNTIF(SUL!B:B,A125))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A125)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A125)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -11497,16 +11486,16 @@
       <c r="A126" s="24" t="s">
         <v>289</v>
       </c>
-      <c r="B126" s="93" t="str">
+      <c r="B126" s="90" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>CARLOS FERNANDES</v>
       </c>
-      <c r="C126" s="93" t="str">
+      <c r="C126" s="90" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D126" s="86"/>
-      <c r="E126" s="86" t="str">
+      <c r="D126" s="83"/>
+      <c r="E126" s="83" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11514,7 +11503,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F126" s="86" t="str">
+      <c r="F126" s="83" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A126),COUNTIF(NORTE!B:B,A126),COUNTIF(SUL!B:B,A126))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A126)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A126)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -11524,16 +11513,16 @@
       <c r="A127" s="24" t="s">
         <v>339</v>
       </c>
-      <c r="B127" s="93" t="str">
+      <c r="B127" s="90" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C127" s="93" t="str">
+      <c r="C127" s="90" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>BAIXADA</v>
       </c>
-      <c r="D127" s="86"/>
-      <c r="E127" s="86" t="str">
+      <c r="D127" s="83"/>
+      <c r="E127" s="83" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11541,7 +11530,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>CONCLUIDA</v>
       </c>
-      <c r="F127" s="86" t="str">
+      <c r="F127" s="83" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A127),COUNTIF(NORTE!B:B,A127),COUNTIF(SUL!B:B,A127))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A127)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A127)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -11551,16 +11540,16 @@
       <c r="A128" s="24" t="s">
         <v>341</v>
       </c>
-      <c r="B128" s="93" t="str">
+      <c r="B128" s="90" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>JEHNIFFER PIRES</v>
       </c>
-      <c r="C128" s="93" t="str">
+      <c r="C128" s="90" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>NORTE</v>
       </c>
-      <c r="D128" s="86"/>
-      <c r="E128" s="86" t="str">
+      <c r="D128" s="83"/>
+      <c r="E128" s="83" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11568,7 +11557,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F128" s="86" t="str">
+      <c r="F128" s="83" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A128),COUNTIF(NORTE!B:B,A128),COUNTIF(SUL!B:B,A128))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A128)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A128)&gt;0,"ESPECIAIS",""))))</f>
         <v>CIVIS</v>
@@ -11578,16 +11567,16 @@
       <c r="A129" s="24" t="s">
         <v>343</v>
       </c>
-      <c r="B129" s="93" t="str">
+      <c r="B129" s="90" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>ERICK HYLARIO</v>
       </c>
-      <c r="C129" s="93" t="str">
+      <c r="C129" s="90" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>ESPECIAIS</v>
       </c>
-      <c r="D129" s="86"/>
-      <c r="E129" s="86" t="str">
+      <c r="D129" s="83"/>
+      <c r="E129" s="83" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11595,7 +11584,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F129" s="86" t="str">
+      <c r="F129" s="83" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A129),COUNTIF(NORTE!B:B,A129),COUNTIF(SUL!B:B,A129))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A129)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A129)&gt;0,"ESPECIAIS",""))))</f>
         <v>ESPECIAIS</v>
@@ -11605,7 +11594,7 @@
       <c r="A130" s="24" t="s">
         <v>345</v>
       </c>
-      <c r="B130" s="93" t="str">
+      <c r="B130" s="90" t="str">
         <f ca="1">UPPER(TRIM(UPPER(IFERROR(VLOOKUP(A130,INDIRECT("'BAIXADA'!$B$3:$I$51"),3,FALSE),
 IFERROR(VLOOKUP(A130,INDIRECT("'NORTE'!$B$3:$I$21"),3,FALSE),
 IFERROR(VLOOKUP(A130,INDIRECT("'SUL'!$B$3:$I$31"),3,FALSE),
@@ -11613,15 +11602,15 @@
 IFERROR(VLOOKUP(A130,INDIRECT("'ESPECIAIS'!$B$3:$I$27"),3,FALSE),""))))))))</f>
         <v>GISELLE G. FONSECA</v>
       </c>
-      <c r="C130" s="93" t="str">
+      <c r="C130" s="90" t="str">
         <f ca="1">IF(OR(B130="CARLOS FERNANDES", B130="GISELLE G. FONSECA"), "BAIXADA",
  IF(OR(B130="ISADORA ROSALINO", B130="JEHNIFFER PIRES"), "NORTE",
  IF(OR(B130="LUIZ FILHO", B130="MARCUS", B130="JAQUELINE PASTÓRIO"), "SUL",
  IF(OR(B130="AIMAR FILHO", B130="ERICK HYLARIO", B130="IGOR CARNEIRO", B130="CESAR", B130="DANRLEI"), "ESPECIAIS",""))))</f>
         <v>BAIXADA</v>
       </c>
-      <c r="D130" s="86"/>
-      <c r="E130" s="86" t="str">
+      <c r="D130" s="83"/>
+      <c r="E130" s="83" t="str">
         <f>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
@@ -11629,7 +11618,7 @@
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</f>
         <v>EXECUÇÃO</v>
       </c>
-      <c r="F130" s="86" t="str">
+      <c r="F130" s="83" t="str">
         <f>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A130),COUNTIF(NORTE!B:B,A130),COUNTIF(SUL!B:B,A130))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A130)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A130)&gt;0,"ESPECIAIS",""))))</f>
         <v>CONTINGENCIA</v>

--- a/COMISSÕES POR REGIAO.xlsx
+++ b/COMISSÕES POR REGIAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APRENDIZADO APP\MEDICOES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BC49D8-30B8-4930-84CC-31AD6CF13773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE726F02-5BA8-41B7-8C88-2C90EE20E855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" activeTab="2" xr2:uid="{8E7E61FA-AA35-49DA-A0A0-B5261C3AB08E}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" activeTab="5" xr2:uid="{8E7E61FA-AA35-49DA-A0A0-B5261C3AB08E}"/>
   </bookViews>
   <sheets>
     <sheet name="BAIXADA" sheetId="1" r:id="rId1"/>
@@ -1048,9 +1048,6 @@
     <t>E-17/026/1514/2019</t>
   </si>
   <si>
-    <t>MARCUS</t>
-  </si>
-  <si>
     <t>390005/000096/2021</t>
   </si>
   <si>
@@ -1410,6 +1407,9 @@
   </si>
   <si>
     <t>330001/001337/2025</t>
+  </si>
+  <si>
+    <t>MARCUS PAULO</t>
   </si>
 </sst>
 </file>
@@ -2529,14 +2529,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="25" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="62">
@@ -2605,6 +2605,231 @@
   </cellStyles>
   <dxfs count="61">
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -2623,7 +2848,9 @@
       </font>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -2637,8 +2864,20 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
         <sz val="10"/>
         <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -2651,7 +2890,91 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2686,192 +3009,6 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="thin">
           <color indexed="64"/>
@@ -2895,18 +3032,6 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
@@ -2914,7 +3039,29 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3047,6 +3194,56 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+        <color auto="1"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -3140,6 +3337,504 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3398,701 +4093,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -4147,7 +4147,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}" name="TBL_BAIXADA" displayName="TBL_BAIXADA" ref="B2:G51" totalsRowShown="0" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}" name="TBL_BAIXADA" displayName="TBL_BAIXADA" ref="B2:G51" totalsRowShown="0" headerRowDxfId="50" dataDxfId="48" headerRowBorderDxfId="49" tableBorderDxfId="47" totalsRowBorderDxfId="46">
   <autoFilter ref="B2:G51" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}">
     <filterColumn colId="2">
       <filters>
@@ -4159,119 +4159,119 @@
     <sortCondition ref="D2:D50"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="2" xr3:uid="{019F32D2-C233-43C9-9576-4AE595F1C1BA}" name="SEI" dataDxfId="46"/>
-    <tableColumn id="1" xr3:uid="{AEDA410C-7924-46EC-AEAB-7AE262BECCD2}" name="FISCAL NOMEADO" dataDxfId="45"/>
-    <tableColumn id="7" xr3:uid="{19466E79-BFE7-4E2E-A742-DD97531E2EF3}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{7880C9F9-C6BC-479F-9DA9-E17F6116251F}" name="STATUS" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{DA47CCE5-2317-4B1E-8640-27A34A02D8B9}" name="MUNICIPIO" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{DCC92333-101D-46D3-9AB3-309FAD98BBFB}" name="EMPRESA" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{019F32D2-C233-43C9-9576-4AE595F1C1BA}" name="SEI" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{AEDA410C-7924-46EC-AEAB-7AE262BECCD2}" name="FISCAL NOMEADO" dataDxfId="44"/>
+    <tableColumn id="7" xr3:uid="{19466E79-BFE7-4E2E-A742-DD97531E2EF3}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{7880C9F9-C6BC-479F-9DA9-E17F6116251F}" name="STATUS" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{DA47CCE5-2317-4B1E-8640-27A34A02D8B9}" name="MUNICIPIO" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{DCC92333-101D-46D3-9AB3-309FAD98BBFB}" name="EMPRESA" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}" name="Tabela2" displayName="Tabela2" ref="B2:G21" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" tableBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}" name="Tabela2" displayName="Tabela2" ref="B2:G21" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38" tableBorderDxfId="37">
   <autoFilter ref="B2:G21" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G20">
     <sortCondition ref="D2:D20"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{16E9EBD3-F35D-4598-A9F2-0A4D20432CE9}" name="SEI" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{E30337A4-09C3-4048-9E77-97431DB2FF42}" name="FISCAL NOMEADO" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{E188BB43-7D82-4633-A725-9027F38B6D00}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{8E3CCA43-C0CA-43A2-BFF6-C18CE15835DE}" name="STATUS" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{4BDB1FC4-3FA9-4D47-842C-749A9777B396}" name="MUNICIPIO" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{080468F4-AE50-4958-86EA-366972343A8C}" name="EMPRESA" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{16E9EBD3-F35D-4598-A9F2-0A4D20432CE9}" name="SEI" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{E30337A4-09C3-4048-9E77-97431DB2FF42}" name="FISCAL NOMEADO" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{E188BB43-7D82-4633-A725-9027F38B6D00}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{8E3CCA43-C0CA-43A2-BFF6-C18CE15835DE}" name="STATUS" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{4BDB1FC4-3FA9-4D47-842C-749A9777B396}" name="MUNICIPIO" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{080468F4-AE50-4958-86EA-366972343A8C}" name="EMPRESA" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B825E509-0D21-4897-AEA1-45396A5B8904}" name="Tabela3" displayName="Tabela3" ref="B2:G31" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30" tableBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B825E509-0D21-4897-AEA1-45396A5B8904}" name="Tabela3" displayName="Tabela3" ref="B2:G31" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58" tableBorderDxfId="57">
   <autoFilter ref="B2:G31" xr:uid="{B825E509-0D21-4897-AEA1-45396A5B8904}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G31">
     <sortCondition ref="D2:D31"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{AF3D376D-5669-42C7-85B7-D133DE0C7C9F}" name="SEI" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{51805C44-CC05-4045-9BCE-C493679844E5}" name="FISCAL NOMEADO" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{5E18CB63-80F1-40CE-AC25-4FF6D6C56801}" name="GESTOR(A) ATUANTE" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{8A899838-F31E-4B62-AD60-CACBA61F7301}" name="STATUS" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{A189C6A4-301D-4BC4-893D-C571D3C65C4F}" name="MUNICIPIO" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{1FE96F05-55E0-47E2-950A-C4FE6590F71E}" name="EMPRESA" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{AF3D376D-5669-42C7-85B7-D133DE0C7C9F}" name="SEI" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{51805C44-CC05-4045-9BCE-C493679844E5}" name="FISCAL NOMEADO" dataDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{5E18CB63-80F1-40CE-AC25-4FF6D6C56801}" name="GESTOR(A) ATUANTE" dataDxfId="54"/>
+    <tableColumn id="4" xr3:uid="{8A899838-F31E-4B62-AD60-CACBA61F7301}" name="STATUS" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{A189C6A4-301D-4BC4-893D-C571D3C65C4F}" name="MUNICIPIO" dataDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{1FE96F05-55E0-47E2-950A-C4FE6590F71E}" name="EMPRESA" dataDxfId="51"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{07EEB8F3-2A08-4F77-A71A-F14F310E745B}" name="Tabela59" displayName="Tabela59" ref="B2:G21" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{07EEB8F3-2A08-4F77-A71A-F14F310E745B}" name="Tabela59" displayName="Tabela59" ref="B2:G21" totalsRowShown="0" headerRowDxfId="30" headerRowBorderDxfId="29" tableBorderDxfId="28" totalsRowBorderDxfId="27">
   <autoFilter ref="B2:G21" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:G10">
     <sortCondition ref="D2:D21"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{1B0B707C-42D7-439C-BC86-F2074086CDFA}" name="SEI" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{E4E4A98E-5F6A-4D1A-BF5C-90DB3AF4D029}" name="FISCAL NOMEADO" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{3F530A0F-746C-40A5-87E4-3EF4BC754B35}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{6289C995-291C-4CD2-9F38-F7B7C1C4C572}" name="STATUS" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{C32C9B37-692D-406F-BC6A-231C43E51674}" name="MUNICIPIO" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{AEFC288F-DB80-4821-8DAC-8848204495B7}" name="EMPRESA" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{1B0B707C-42D7-439C-BC86-F2074086CDFA}" name="SEI" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{E4E4A98E-5F6A-4D1A-BF5C-90DB3AF4D029}" name="FISCAL NOMEADO" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{3F530A0F-746C-40A5-87E4-3EF4BC754B35}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{6289C995-291C-4CD2-9F38-F7B7C1C4C572}" name="STATUS" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{C32C9B37-692D-406F-BC6A-231C43E51674}" name="MUNICIPIO" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{AEFC288F-DB80-4821-8DAC-8848204495B7}" name="EMPRESA" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}" name="Tabela5" displayName="Tabela5" ref="B2:G27" totalsRowShown="0" headerRowDxfId="59" headerRowBorderDxfId="58" tableBorderDxfId="57" totalsRowBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}" name="Tabela5" displayName="Tabela5" ref="B2:G27" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
   <autoFilter ref="B2:G27" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:G23">
     <sortCondition ref="D2:D26"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8FECF49A-25BA-405F-A561-286D71FB284B}" name="SEI" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{88A1DC3F-1E69-48FA-B7AB-F895C771F55E}" name="FISCAL NOMEADO" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{B977B564-9125-4E72-A174-DD668115187D}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{6A4D0185-1909-4BA9-A2C1-58CDBA8CD45C}" name="STATUS" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{539417AD-B8A4-4898-AB74-66F05A603AF4}" name="MUNICIPIO" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{235BE65E-B850-4BB7-8E87-322FA0E9FAE2}" name="EMPRESA" dataDxfId="52"/>
+    <tableColumn id="1" xr3:uid="{8FECF49A-25BA-405F-A561-286D71FB284B}" name="SEI" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{88A1DC3F-1E69-48FA-B7AB-F895C771F55E}" name="FISCAL NOMEADO" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{B977B564-9125-4E72-A174-DD668115187D}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{6A4D0185-1909-4BA9-A2C1-58CDBA8CD45C}" name="STATUS" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{539417AD-B8A4-4898-AB74-66F05A603AF4}" name="MUNICIPIO" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{235BE65E-B850-4BB7-8E87-322FA0E9FAE2}" name="EMPRESA" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}" name="TBL_AUX_COMISSAO" displayName="TBL_AUX_COMISSAO" ref="A1:F130" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}" name="TBL_AUX_COMISSAO" displayName="TBL_AUX_COMISSAO" ref="A1:F130" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="A1:F130" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F121">
     <sortCondition ref="A1:A124"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6940CE63-D3EF-4410-99DC-5338DACC9347}" name="SEI" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{BC273B88-930A-4795-B862-FBC8E6F6BDFE}" name="GESTOR" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{6940CE63-D3EF-4410-99DC-5338DACC9347}" name="SEI" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{BC273B88-930A-4795-B862-FBC8E6F6BDFE}" name="GESTOR" dataDxfId="4">
       <calculatedColumnFormula>UPPER(TRIM(UPPER(IFERROR(VLOOKUP(A2,INDIRECT("'BAIXADA'!$B$3:$I$51"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'NORTE'!$B$3:$I$21"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'SUL'!$B$3:$I$31"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'CONTIGENCIA'!$B$3:$I$22"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'ESPECIAIS'!$B$3:$I$27"),3,FALSE),""))))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2DD541AF-D366-4FA1-934F-2D706DEB3424}" name="REGIAO" dataDxfId="7">
+    <tableColumn id="3" xr3:uid="{2DD541AF-D366-4FA1-934F-2D706DEB3424}" name="REGIAO" dataDxfId="3">
       <calculatedColumnFormula>IF(OR(B2="CARLOS FERNANDES", B2="GISELLE G. FONSECA"), "BAIXADA",
  IF(OR(B2="ISADORA ROSALINO", B2="JEHNIFFER PIRES"), "NORTE",
  IF(OR(B2="LUIZ FILHO", B2="MARCUS", B2="JAQUELINE PASTÓRIO"), "SUL",
  IF(OR(B2="AIMAR FILHO", B2="ERICK HYLARIO", B2="IGOR CARNEIRO", B2="CESAR", B2="DANRLEI"), "ESPECIAIS",""))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{48CC14BF-DA39-4E7A-9D30-3BF4E557740A}" name="Coluna1" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{73F6C358-23B2-4118-8542-3EF0D7731680}" name="STATUS" dataDxfId="5">
+    <tableColumn id="4" xr3:uid="{48CC14BF-DA39-4E7A-9D30-3BF4E557740A}" name="Coluna1" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{73F6C358-23B2-4118-8542-3EF0D7731680}" name="STATUS" dataDxfId="1">
       <calculatedColumnFormula>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela59[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{42155D96-D90A-49EF-9ADB-3B70FF87E628}" name="LOCAL" dataDxfId="4">
+    <tableColumn id="6" xr3:uid="{42155D96-D90A-49EF-9ADB-3B70FF87E628}" name="LOCAL" dataDxfId="0">
       <calculatedColumnFormula>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A2),COUNTIF(NORTE!B:B,A2),COUNTIF(SUL!B:B,A2))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A2)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A2)&gt;0,"ESPECIAIS",""))))</calculatedColumnFormula>
     </tableColumn>
@@ -4593,24 +4593,24 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="97" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
     </row>
     <row r="2" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B2" s="39" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2" s="40" t="s">
         <v>228</v>
-      </c>
-      <c r="D2" s="40" t="s">
-        <v>229</v>
       </c>
       <c r="E2" s="39" t="s">
         <v>36</v>
@@ -4630,10 +4630,10 @@
         <v>111</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E3" s="30" t="s">
         <v>64</v>
@@ -4653,10 +4653,10 @@
         <v>106</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E4" s="34" t="s">
         <v>193</v>
@@ -4676,10 +4676,10 @@
         <v>52</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E5" s="30" t="s">
         <v>50</v>
@@ -4699,10 +4699,10 @@
         <v>102</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E6" s="53" t="s">
         <v>194</v>
@@ -4722,10 +4722,10 @@
         <v>213</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E7" s="53" t="s">
         <v>194</v>
@@ -4745,10 +4745,10 @@
         <v>176</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E8" s="34" t="s">
         <v>193</v>
@@ -4765,13 +4765,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E9" s="30" t="s">
         <v>64</v>
@@ -4780,7 +4780,7 @@
         <v>149</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -4791,10 +4791,10 @@
         <v>209</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>285</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>286</v>
       </c>
       <c r="E10" s="30" t="s">
         <v>194</v>
@@ -4814,13 +4814,13 @@
         <v>168</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>91</v>
@@ -4837,10 +4837,10 @@
         <v>212</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E12" s="34" t="s">
         <v>193</v>
@@ -4849,7 +4849,7 @@
         <v>137</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -4860,13 +4860,13 @@
         <v>119</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E13" s="70" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>117</v>
@@ -4883,10 +4883,10 @@
         <v>175</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E14" s="34" t="s">
         <v>193</v>
@@ -4906,10 +4906,10 @@
         <v>172</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E15" s="34" t="s">
         <v>193</v>
@@ -4929,10 +4929,10 @@
         <v>80</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E16" s="30" t="s">
         <v>194</v>
@@ -4949,13 +4949,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E17" s="70" t="s">
         <v>194</v>
@@ -4964,7 +4964,7 @@
         <v>137</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -4975,10 +4975,10 @@
         <v>113</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E18" s="34" t="s">
         <v>193</v>
@@ -5001,7 +5001,7 @@
         <v>95</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E19" s="34" t="s">
         <v>193</v>
@@ -5021,10 +5021,10 @@
         <v>10</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E20" s="34" t="s">
         <v>193</v>
@@ -5041,13 +5041,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E21" s="34" t="s">
         <v>193</v>
@@ -5056,7 +5056,7 @@
         <v>11</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -5067,10 +5067,10 @@
         <v>79</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E22" s="30" t="s">
         <v>125</v>
@@ -5090,13 +5090,13 @@
         <v>132</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E23" s="70" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>137</v>
@@ -5113,13 +5113,13 @@
         <v>218</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>92</v>
@@ -5133,13 +5133,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E25" s="30" t="s">
         <v>64</v>
@@ -5159,10 +5159,10 @@
         <v>169</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E26" s="34" t="s">
         <v>193</v>
@@ -5182,10 +5182,10 @@
         <v>116</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E27" s="30" t="s">
         <v>50</v>
@@ -5205,10 +5205,10 @@
         <v>78</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E28" s="34" t="s">
         <v>193</v>
@@ -5228,10 +5228,10 @@
         <v>146</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E29" s="30" t="s">
         <v>64</v>
@@ -5251,10 +5251,10 @@
         <v>145</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E30" s="30" t="s">
         <v>50</v>
@@ -5274,13 +5274,13 @@
         <v>217</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>92</v>
@@ -5297,10 +5297,10 @@
         <v>104</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E32" s="30" t="s">
         <v>64</v>
@@ -5320,10 +5320,10 @@
         <v>170</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E33" s="53" t="s">
         <v>125</v>
@@ -5343,10 +5343,10 @@
         <v>51</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E34" s="34" t="s">
         <v>194</v>
@@ -5366,13 +5366,13 @@
         <v>115</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E35" s="30" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>109</v>
@@ -5389,13 +5389,13 @@
         <v>219</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E36" s="30" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>148</v>
@@ -5412,10 +5412,10 @@
         <v>173</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E37" s="30" t="s">
         <v>64</v>
@@ -5435,10 +5435,10 @@
         <v>171</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E38" s="34" t="s">
         <v>193</v>
@@ -5455,13 +5455,13 @@
         <v>37</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E39" s="30" t="s">
         <v>64</v>
@@ -5470,7 +5470,7 @@
         <v>196</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -5481,10 +5481,10 @@
         <v>147</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E40" s="30" t="s">
         <v>193</v>
@@ -5504,10 +5504,10 @@
         <v>143</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E41" s="30" t="s">
         <v>64</v>
@@ -5527,10 +5527,10 @@
         <v>174</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D42" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E42" s="31" t="s">
         <v>194</v>
@@ -5550,10 +5550,10 @@
         <v>96</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D43" s="52" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E43" s="34" t="s">
         <v>193</v>
@@ -5570,13 +5570,13 @@
         <v>42</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E44" s="91" t="s">
         <v>64</v>
@@ -5585,7 +5585,7 @@
         <v>90</v>
       </c>
       <c r="G44" s="23" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -5596,10 +5596,10 @@
         <v>83</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E45" s="30" t="s">
         <v>64</v>
@@ -5619,10 +5619,10 @@
         <v>82</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E46" s="30" t="s">
         <v>64</v>
@@ -5639,13 +5639,13 @@
         <v>45</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E47" s="31" t="s">
         <v>64</v>
@@ -5654,7 +5654,7 @@
         <v>23</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -5665,10 +5665,10 @@
         <v>30</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E48" s="31" t="s">
         <v>64</v>
@@ -5688,10 +5688,10 @@
         <v>211</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E49" s="30" t="s">
         <v>194</v>
@@ -5711,10 +5711,10 @@
         <v>81</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E50" s="30" t="s">
         <v>64</v>
@@ -5769,14 +5769,14 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="97" t="s">
         <v>122</v>
       </c>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
     </row>
     <row r="2" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
@@ -5784,10 +5784,10 @@
         <v>35</v>
       </c>
       <c r="C2" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2" s="41" t="s">
         <v>228</v>
-      </c>
-      <c r="D2" s="41" t="s">
-        <v>229</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>36</v>
@@ -5807,13 +5807,13 @@
         <v>156</v>
       </c>
       <c r="C3" s="71" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F3" s="27" t="s">
         <v>68</v>
@@ -5830,10 +5830,10 @@
         <v>155</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>125</v>
@@ -5853,10 +5853,10 @@
         <v>158</v>
       </c>
       <c r="C5" s="71" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>64</v>
@@ -5876,10 +5876,10 @@
         <v>159</v>
       </c>
       <c r="C6" s="71" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D6" s="71" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E6" s="27" t="s">
         <v>64</v>
@@ -5899,10 +5899,10 @@
         <v>160</v>
       </c>
       <c r="C7" s="71" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D7" s="71" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E7" s="27" t="s">
         <v>64</v>
@@ -5922,10 +5922,10 @@
         <v>120</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D8" s="71" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E8" s="85" t="s">
         <v>194</v>
@@ -5945,10 +5945,10 @@
         <v>164</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E9" s="85" t="s">
         <v>50</v>
@@ -5968,10 +5968,10 @@
         <v>151</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E10" s="86" t="s">
         <v>193</v>
@@ -5991,10 +5991,10 @@
         <v>128</v>
       </c>
       <c r="C11" s="56" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>305</v>
+        <v>345</v>
       </c>
       <c r="E11" s="58" t="s">
         <v>193</v>
@@ -6014,10 +6014,10 @@
         <v>152</v>
       </c>
       <c r="C12" s="71" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D12" s="71" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E12" s="27" t="s">
         <v>64</v>
@@ -6037,13 +6037,13 @@
         <v>163</v>
       </c>
       <c r="C13" s="71" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D13" s="71" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>73</v>
@@ -6060,10 +6060,10 @@
         <v>161</v>
       </c>
       <c r="C14" s="56" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>125</v>
@@ -6083,13 +6083,13 @@
         <v>154</v>
       </c>
       <c r="C15" s="71" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D15" s="71" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>68</v>
@@ -6103,22 +6103,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="79" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C16" s="71" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D16" s="71" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E16" s="27" t="s">
         <v>64</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G16" s="57" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -6129,10 +6129,10 @@
         <v>153</v>
       </c>
       <c r="C17" s="71" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D17" s="71" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E17" s="27" t="s">
         <v>64</v>
@@ -6152,10 +6152,10 @@
         <v>162</v>
       </c>
       <c r="C18" s="56" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E18" s="85" t="s">
         <v>50</v>
@@ -6175,10 +6175,10 @@
         <v>121</v>
       </c>
       <c r="C19" s="56" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D19" s="56" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E19" s="58" t="s">
         <v>193</v>
@@ -6198,10 +6198,10 @@
         <v>157</v>
       </c>
       <c r="C20" s="56" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D20" s="56" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>64</v>
@@ -6218,13 +6218,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="55" t="s">
+        <v>340</v>
+      </c>
+      <c r="C21" s="56" t="s">
         <v>341</v>
       </c>
-      <c r="C21" s="56" t="s">
-        <v>342</v>
-      </c>
       <c r="D21" s="56" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>64</v>
@@ -6233,7 +6233,7 @@
         <v>197</v>
       </c>
       <c r="G21" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -6278,14 +6278,14 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="97" t="s">
         <v>131</v>
       </c>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
@@ -6293,10 +6293,10 @@
         <v>35</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E2" s="45" t="s">
         <v>36</v>
@@ -6316,10 +6316,10 @@
         <v>4</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E3" s="32" t="s">
         <v>64</v>
@@ -6336,22 +6336,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>64</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>292</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -6362,10 +6362,10 @@
         <v>223</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E5" s="89" t="s">
         <v>64</v>
@@ -6385,13 +6385,13 @@
         <v>8</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E6" s="87" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F6" s="35" t="s">
         <v>9</v>
@@ -6408,13 +6408,13 @@
         <v>16</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E7" s="87" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F7" s="35" t="s">
         <v>15</v>
@@ -6431,10 +6431,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E8" s="67" t="s">
         <v>193</v>
@@ -6454,10 +6454,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E9" s="67" t="s">
         <v>193</v>
@@ -6477,13 +6477,13 @@
         <v>21</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F10" s="35" t="s">
         <v>20</v>
@@ -6500,10 +6500,10 @@
         <v>34</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E11" s="67" t="s">
         <v>193</v>
@@ -6523,10 +6523,10 @@
         <v>32</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E12" s="32" t="s">
         <v>64</v>
@@ -6535,7 +6535,7 @@
         <v>33</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -6546,10 +6546,10 @@
         <v>134</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E13" s="89" t="s">
         <v>64</v>
@@ -6569,10 +6569,10 @@
         <v>7</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E14" s="78" t="s">
         <v>193</v>
@@ -6592,10 +6592,10 @@
         <v>24</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E15" s="78" t="s">
         <v>193</v>
@@ -6615,13 +6615,13 @@
         <v>94</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E16" s="87" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F16" s="35" t="s">
         <v>3</v>
@@ -6638,10 +6638,10 @@
         <v>26</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E17" s="78" t="s">
         <v>193</v>
@@ -6661,13 +6661,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E18" s="87" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F18" s="35" t="s">
         <v>23</v>
@@ -6684,13 +6684,13 @@
         <v>133</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E19" s="87" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F19" s="35" t="s">
         <v>3</v>
@@ -6707,10 +6707,10 @@
         <v>5</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D20" s="35" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E20" s="87" t="s">
         <v>125</v>
@@ -6730,13 +6730,13 @@
         <v>27</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D21" s="35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E21" s="87" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>28</v>
@@ -6753,10 +6753,10 @@
         <v>135</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E22" s="89" t="s">
         <v>64</v>
@@ -6776,10 +6776,10 @@
         <v>0</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D23" s="35" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E23" s="67" t="s">
         <v>194</v>
@@ -6799,10 +6799,10 @@
         <v>136</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D24" s="35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E24" s="92" t="s">
         <v>64</v>
@@ -6822,10 +6822,10 @@
         <v>221</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D25" s="35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E25" s="92" t="s">
         <v>64</v>
@@ -6848,10 +6848,10 @@
         <v>29</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D26" s="35" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E26" s="78" t="s">
         <v>193</v>
@@ -6871,10 +6871,10 @@
         <v>14</v>
       </c>
       <c r="C27" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="D27" s="35" t="s">
         <v>303</v>
-      </c>
-      <c r="D27" s="35" t="s">
-        <v>304</v>
       </c>
       <c r="E27" s="32" t="s">
         <v>125</v>
@@ -6894,13 +6894,13 @@
         <v>12</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D28" s="35" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E28" s="87" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F28" s="35" t="s">
         <v>13</v>
@@ -6917,10 +6917,10 @@
         <v>2</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D29" s="35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E29" s="37" t="s">
         <v>64</v>
@@ -6937,22 +6937,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="50" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D30" s="35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>64</v>
       </c>
       <c r="F30" s="54" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G30" s="54" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -6960,13 +6960,13 @@
         <v>29</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D31" s="35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E31" s="37" t="s">
         <v>64</v>
@@ -6975,7 +6975,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -7037,14 +7037,14 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
-      <c r="B1" s="96" t="s">
-        <v>271</v>
-      </c>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
+      <c r="B1" s="97" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
     </row>
     <row r="2" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
@@ -7052,10 +7052,10 @@
         <v>35</v>
       </c>
       <c r="C2" s="49" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2" s="49" t="s">
         <v>228</v>
-      </c>
-      <c r="D2" s="49" t="s">
-        <v>229</v>
       </c>
       <c r="E2" s="49" t="s">
         <v>36</v>
@@ -7072,13 +7072,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="80" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C3" s="80" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E3" s="87" t="s">
         <v>125</v>
@@ -7087,7 +7087,7 @@
         <v>9</v>
       </c>
       <c r="G3" s="69" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7095,22 +7095,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="80" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C4" s="80" t="s">
+        <v>302</v>
+      </c>
+      <c r="D4" s="27" t="s">
         <v>303</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>304</v>
       </c>
       <c r="E4" s="87" t="s">
         <v>125</v>
       </c>
       <c r="F4" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="G4" s="69" t="s">
         <v>243</v>
-      </c>
-      <c r="G4" s="69" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -7118,13 +7118,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="93" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C5" s="93" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E5" s="87" t="s">
         <v>64</v>
@@ -7133,7 +7133,7 @@
         <v>196</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7141,22 +7141,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="80" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C6" s="80" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E6" s="87" t="s">
         <v>125</v>
       </c>
       <c r="F6" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="G6" s="69" t="s">
         <v>246</v>
-      </c>
-      <c r="G6" s="69" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7164,22 +7164,22 @@
         <v>5</v>
       </c>
       <c r="B7" s="80" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C7" s="80" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E7" s="32" t="s">
         <v>64</v>
       </c>
       <c r="F7" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="G7" s="69" t="s">
         <v>246</v>
-      </c>
-      <c r="G7" s="69" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7187,13 +7187,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E8" s="37" t="s">
         <v>64</v>
@@ -7202,7 +7202,7 @@
         <v>166</v>
       </c>
       <c r="G8" s="88" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7210,13 +7210,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E9" s="75" t="s">
         <v>64</v>
@@ -7225,7 +7225,7 @@
         <v>90</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -7233,22 +7233,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="80" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C10" s="80" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E10" s="32" t="s">
         <v>64</v>
       </c>
       <c r="F10" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="G10" s="69" t="s">
         <v>279</v>
-      </c>
-      <c r="G10" s="69" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -7256,13 +7256,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="80" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C11" s="95" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E11" s="32" t="s">
         <v>64</v>
@@ -7280,10 +7280,10 @@
       </c>
       <c r="B12" s="80"/>
       <c r="C12" s="80" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="27"/>
@@ -7295,10 +7295,10 @@
       </c>
       <c r="B13" s="80"/>
       <c r="C13" s="80" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="27"/>
@@ -7310,10 +7310,10 @@
       </c>
       <c r="B14" s="80"/>
       <c r="C14" s="80" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="27"/>
@@ -7325,10 +7325,10 @@
       </c>
       <c r="B15" s="80"/>
       <c r="C15" s="80" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="27"/>
@@ -7340,10 +7340,10 @@
       </c>
       <c r="B16" s="80"/>
       <c r="C16" s="80" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="27"/>
@@ -7355,10 +7355,10 @@
       </c>
       <c r="B17" s="80"/>
       <c r="C17" s="80" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="27"/>
@@ -7370,10 +7370,10 @@
       </c>
       <c r="B18" s="80"/>
       <c r="C18" s="80" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="27"/>
@@ -7385,10 +7385,10 @@
       </c>
       <c r="B19" s="84"/>
       <c r="C19" s="84" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E19" s="37"/>
       <c r="F19" s="38"/>
@@ -7400,10 +7400,10 @@
       </c>
       <c r="B20" s="84"/>
       <c r="C20" s="84" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E20" s="37"/>
       <c r="F20" s="38"/>
@@ -7415,10 +7415,10 @@
       </c>
       <c r="B21" s="80"/>
       <c r="C21" s="80" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E21" s="32"/>
       <c r="F21" s="27"/>
@@ -7454,14 +7454,14 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="97" t="s">
         <v>208</v>
       </c>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
     </row>
     <row r="2" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
@@ -7469,10 +7469,10 @@
         <v>35</v>
       </c>
       <c r="C2" s="49" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2" s="49" t="s">
         <v>228</v>
-      </c>
-      <c r="D2" s="49" t="s">
-        <v>229</v>
       </c>
       <c r="E2" s="49" t="s">
         <v>36</v>
@@ -7489,13 +7489,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="80" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>225</v>
+        <v>345</v>
       </c>
       <c r="E3" s="32" t="s">
         <v>125</v>
@@ -7504,7 +7504,7 @@
         <v>196</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7515,10 +7515,10 @@
         <v>180</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D4" s="27" t="s">
         <v>282</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>283</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>193</v>
@@ -7538,10 +7538,10 @@
         <v>215</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E5" s="32" t="s">
         <v>125</v>
@@ -7558,13 +7558,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="79" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E6" s="77" t="s">
         <v>193</v>
@@ -7581,13 +7581,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="80" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E7" s="32" t="s">
         <v>64</v>
@@ -7596,7 +7596,7 @@
         <v>196</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7607,13 +7607,13 @@
         <v>182</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F8" s="27" t="s">
         <v>196</v>
@@ -7630,10 +7630,10 @@
         <v>183</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E9" s="32" t="s">
         <v>125</v>
@@ -7650,13 +7650,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="80" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E10" s="32" t="s">
         <v>64</v>
@@ -7665,7 +7665,7 @@
         <v>196</v>
       </c>
       <c r="G10" s="69" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -7673,13 +7673,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="79" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E11" s="77" t="s">
         <v>64</v>
@@ -7688,7 +7688,7 @@
         <v>196</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -7696,13 +7696,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="79" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E12" s="77" t="s">
         <v>64</v>
@@ -7722,10 +7722,10 @@
         <v>184</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D13" s="27" t="s">
         <v>282</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>283</v>
       </c>
       <c r="E13" s="32" t="s">
         <v>193</v>
@@ -7745,10 +7745,10 @@
         <v>185</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D14" s="27" t="s">
         <v>282</v>
-      </c>
-      <c r="D14" s="27" t="s">
-        <v>283</v>
       </c>
       <c r="E14" s="32" t="s">
         <v>193</v>
@@ -7768,10 +7768,10 @@
         <v>186</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E15" s="32" t="s">
         <v>50</v>
@@ -7788,13 +7788,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="80" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D16" s="27" t="s">
         <v>282</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>283</v>
       </c>
       <c r="E16" s="32" t="s">
         <v>194</v>
@@ -7814,10 +7814,10 @@
         <v>189</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E17" s="32" t="s">
         <v>64</v>
@@ -7837,10 +7837,10 @@
         <v>187</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E18" s="32" t="s">
         <v>194</v>
@@ -7860,10 +7860,10 @@
         <v>188</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E19" s="37" t="s">
         <v>194</v>
@@ -7883,10 +7883,10 @@
         <v>181</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E20" s="37" t="s">
         <v>64</v>
@@ -7903,13 +7903,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="80" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E21" s="32" t="s">
         <v>64</v>
@@ -7918,7 +7918,7 @@
         <v>196</v>
       </c>
       <c r="G21" s="27" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -7929,10 +7929,10 @@
         <v>144</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E22" s="32" t="s">
         <v>125</v>
@@ -7952,10 +7952,10 @@
         <v>191</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E23" s="32" t="s">
         <v>64</v>
@@ -7975,10 +7975,10 @@
         <v>190</v>
       </c>
       <c r="C24" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="D24" s="38" t="s">
         <v>282</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>283</v>
       </c>
       <c r="E24" s="37" t="s">
         <v>193</v>
@@ -7998,10 +7998,10 @@
         <v>192</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E25" s="32" t="s">
         <v>50</v>
@@ -8021,10 +8021,10 @@
         <v>224</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E26" s="32" t="s">
         <v>194</v>
@@ -8040,12 +8040,12 @@
       <c r="A27" s="3">
         <v>25</v>
       </c>
-      <c r="B27" s="98" t="s">
-        <v>343</v>
+      <c r="B27" s="96" t="s">
+        <v>342</v>
       </c>
       <c r="C27" s="23"/>
       <c r="D27" s="31" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E27" s="94" t="s">
         <v>64</v>
@@ -8054,7 +8054,7 @@
         <v>196</v>
       </c>
       <c r="G27" s="31" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H27" s="2"/>
     </row>
@@ -8103,7 +8103,7 @@
         <v>36</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -8439,7 +8439,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B14" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8520,7 +8520,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B17" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8925,7 +8925,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B32" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8952,7 +8952,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B33" s="81" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8979,7 +8979,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B34" s="81" t="str">
         <f t="shared" ref="B34:B65" ca="1" si="2">UPPER(TRIM(UPPER(IFERROR(VLOOKUP(A34,INDIRECT("'BAIXADA'!$B$3:$I$51"),3,FALSE),
@@ -9040,7 +9040,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B36" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9094,7 +9094,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B38" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9175,7 +9175,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B41" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9202,7 +9202,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B42" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9229,7 +9229,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B43" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9256,7 +9256,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B44" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9283,7 +9283,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B45" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9557,11 +9557,11 @@
       </c>
       <c r="B55" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>ISADORA ROSALINO</v>
+        <v>MARCUS PAULO</v>
       </c>
       <c r="C55" s="81" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>NORTE</v>
+        <v/>
       </c>
       <c r="D55" s="82"/>
       <c r="E55" s="82" t="str">
@@ -9580,7 +9580,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B56" s="81" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10586,7 +10586,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B93" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -10613,7 +10613,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B94" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -10667,7 +10667,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B96" s="81" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -10809,15 +10809,15 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B101" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>MARCUS</v>
+        <v>MARCUS PAULO</v>
       </c>
       <c r="C101" s="81" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>SUL</v>
+        <v/>
       </c>
       <c r="D101" s="83"/>
       <c r="E101" s="83" t="str">
@@ -10890,7 +10890,7 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B104" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -11160,7 +11160,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B114" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -11187,7 +11187,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B115" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -11268,7 +11268,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B118" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -11295,7 +11295,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B119" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -11349,7 +11349,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B121" s="81" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -11457,7 +11457,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B125" s="90" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -11484,7 +11484,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B126" s="90" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -11511,7 +11511,7 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="24" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B127" s="90" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -11538,7 +11538,7 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="24" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B128" s="90" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -11565,7 +11565,7 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="24" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B129" s="90" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -11592,7 +11592,7 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="24" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B130" s="90" t="str">
         <f ca="1">UPPER(TRIM(UPPER(IFERROR(VLOOKUP(A130,INDIRECT("'BAIXADA'!$B$3:$I$51"),3,FALSE),

--- a/COMISSÕES POR REGIAO.xlsx
+++ b/COMISSÕES POR REGIAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APRENDIZADO APP\MEDICOES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE726F02-5BA8-41B7-8C88-2C90EE20E855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DA6965-B007-4887-9F66-C37BBF2766C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" activeTab="5" xr2:uid="{8E7E61FA-AA35-49DA-A0A0-B5261C3AB08E}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" xr2:uid="{8E7E61FA-AA35-49DA-A0A0-B5261C3AB08E}"/>
   </bookViews>
   <sheets>
     <sheet name="BAIXADA" sheetId="1" r:id="rId1"/>
@@ -2605,231 +2605,6 @@
   </cellStyles>
   <dxfs count="61">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -3337,504 +3112,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -4092,6 +3369,729 @@
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -4147,7 +4147,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}" name="TBL_BAIXADA" displayName="TBL_BAIXADA" ref="B2:G51" totalsRowShown="0" headerRowDxfId="50" dataDxfId="48" headerRowBorderDxfId="49" tableBorderDxfId="47" totalsRowBorderDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}" name="TBL_BAIXADA" displayName="TBL_BAIXADA" ref="B2:G51" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45" totalsRowBorderDxfId="44">
   <autoFilter ref="B2:G51" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}">
     <filterColumn colId="2">
       <filters>
@@ -4159,119 +4159,119 @@
     <sortCondition ref="D2:D50"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="2" xr3:uid="{019F32D2-C233-43C9-9576-4AE595F1C1BA}" name="SEI" dataDxfId="45"/>
-    <tableColumn id="1" xr3:uid="{AEDA410C-7924-46EC-AEAB-7AE262BECCD2}" name="FISCAL NOMEADO" dataDxfId="44"/>
-    <tableColumn id="7" xr3:uid="{19466E79-BFE7-4E2E-A742-DD97531E2EF3}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{7880C9F9-C6BC-479F-9DA9-E17F6116251F}" name="STATUS" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{DA47CCE5-2317-4B1E-8640-27A34A02D8B9}" name="MUNICIPIO" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{DCC92333-101D-46D3-9AB3-309FAD98BBFB}" name="EMPRESA" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{019F32D2-C233-43C9-9576-4AE595F1C1BA}" name="SEI" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{AEDA410C-7924-46EC-AEAB-7AE262BECCD2}" name="FISCAL NOMEADO" dataDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{19466E79-BFE7-4E2E-A742-DD97531E2EF3}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{7880C9F9-C6BC-479F-9DA9-E17F6116251F}" name="STATUS" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{DA47CCE5-2317-4B1E-8640-27A34A02D8B9}" name="MUNICIPIO" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{DCC92333-101D-46D3-9AB3-309FAD98BBFB}" name="EMPRESA" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}" name="Tabela2" displayName="Tabela2" ref="B2:G21" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38" tableBorderDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}" name="Tabela2" displayName="Tabela2" ref="B2:G21" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36" tableBorderDxfId="35">
   <autoFilter ref="B2:G21" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G20">
     <sortCondition ref="D2:D20"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{16E9EBD3-F35D-4598-A9F2-0A4D20432CE9}" name="SEI" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{E30337A4-09C3-4048-9E77-97431DB2FF42}" name="FISCAL NOMEADO" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{E188BB43-7D82-4633-A725-9027F38B6D00}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{8E3CCA43-C0CA-43A2-BFF6-C18CE15835DE}" name="STATUS" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{4BDB1FC4-3FA9-4D47-842C-749A9777B396}" name="MUNICIPIO" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{080468F4-AE50-4958-86EA-366972343A8C}" name="EMPRESA" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{16E9EBD3-F35D-4598-A9F2-0A4D20432CE9}" name="SEI" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{E30337A4-09C3-4048-9E77-97431DB2FF42}" name="FISCAL NOMEADO" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{E188BB43-7D82-4633-A725-9027F38B6D00}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{8E3CCA43-C0CA-43A2-BFF6-C18CE15835DE}" name="STATUS" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{4BDB1FC4-3FA9-4D47-842C-749A9777B396}" name="MUNICIPIO" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{080468F4-AE50-4958-86EA-366972343A8C}" name="EMPRESA" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B825E509-0D21-4897-AEA1-45396A5B8904}" name="Tabela3" displayName="Tabela3" ref="B2:G31" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58" tableBorderDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B825E509-0D21-4897-AEA1-45396A5B8904}" name="Tabela3" displayName="Tabela3" ref="B2:G31" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27" tableBorderDxfId="26">
   <autoFilter ref="B2:G31" xr:uid="{B825E509-0D21-4897-AEA1-45396A5B8904}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G31">
     <sortCondition ref="D2:D31"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{AF3D376D-5669-42C7-85B7-D133DE0C7C9F}" name="SEI" dataDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{51805C44-CC05-4045-9BCE-C493679844E5}" name="FISCAL NOMEADO" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{5E18CB63-80F1-40CE-AC25-4FF6D6C56801}" name="GESTOR(A) ATUANTE" dataDxfId="54"/>
-    <tableColumn id="4" xr3:uid="{8A899838-F31E-4B62-AD60-CACBA61F7301}" name="STATUS" dataDxfId="53"/>
-    <tableColumn id="5" xr3:uid="{A189C6A4-301D-4BC4-893D-C571D3C65C4F}" name="MUNICIPIO" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{1FE96F05-55E0-47E2-950A-C4FE6590F71E}" name="EMPRESA" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{AF3D376D-5669-42C7-85B7-D133DE0C7C9F}" name="SEI" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{51805C44-CC05-4045-9BCE-C493679844E5}" name="FISCAL NOMEADO" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{5E18CB63-80F1-40CE-AC25-4FF6D6C56801}" name="GESTOR(A) ATUANTE" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{8A899838-F31E-4B62-AD60-CACBA61F7301}" name="STATUS" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{A189C6A4-301D-4BC4-893D-C571D3C65C4F}" name="MUNICIPIO" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{1FE96F05-55E0-47E2-950A-C4FE6590F71E}" name="EMPRESA" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{07EEB8F3-2A08-4F77-A71A-F14F310E745B}" name="Tabela59" displayName="Tabela59" ref="B2:G21" totalsRowShown="0" headerRowDxfId="30" headerRowBorderDxfId="29" tableBorderDxfId="28" totalsRowBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{07EEB8F3-2A08-4F77-A71A-F14F310E745B}" name="Tabela59" displayName="Tabela59" ref="B2:G21" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
   <autoFilter ref="B2:G21" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:G10">
     <sortCondition ref="D2:D21"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{1B0B707C-42D7-439C-BC86-F2074086CDFA}" name="SEI" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{E4E4A98E-5F6A-4D1A-BF5C-90DB3AF4D029}" name="FISCAL NOMEADO" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{3F530A0F-746C-40A5-87E4-3EF4BC754B35}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{6289C995-291C-4CD2-9F38-F7B7C1C4C572}" name="STATUS" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{C32C9B37-692D-406F-BC6A-231C43E51674}" name="MUNICIPIO" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{AEFC288F-DB80-4821-8DAC-8848204495B7}" name="EMPRESA" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{1B0B707C-42D7-439C-BC86-F2074086CDFA}" name="SEI" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{E4E4A98E-5F6A-4D1A-BF5C-90DB3AF4D029}" name="FISCAL NOMEADO" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{3F530A0F-746C-40A5-87E4-3EF4BC754B35}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{6289C995-291C-4CD2-9F38-F7B7C1C4C572}" name="STATUS" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{C32C9B37-692D-406F-BC6A-231C43E51674}" name="MUNICIPIO" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{AEFC288F-DB80-4821-8DAC-8848204495B7}" name="EMPRESA" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}" name="Tabela5" displayName="Tabela5" ref="B2:G27" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}" name="Tabela5" displayName="Tabela5" ref="B2:G27" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="B2:G27" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:G23">
     <sortCondition ref="D2:D26"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8FECF49A-25BA-405F-A561-286D71FB284B}" name="SEI" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{88A1DC3F-1E69-48FA-B7AB-F895C771F55E}" name="FISCAL NOMEADO" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{B977B564-9125-4E72-A174-DD668115187D}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{6A4D0185-1909-4BA9-A2C1-58CDBA8CD45C}" name="STATUS" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{539417AD-B8A4-4898-AB74-66F05A603AF4}" name="MUNICIPIO" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{235BE65E-B850-4BB7-8E87-322FA0E9FAE2}" name="EMPRESA" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{8FECF49A-25BA-405F-A561-286D71FB284B}" name="SEI" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{88A1DC3F-1E69-48FA-B7AB-F895C771F55E}" name="FISCAL NOMEADO" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{B977B564-9125-4E72-A174-DD668115187D}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{6A4D0185-1909-4BA9-A2C1-58CDBA8CD45C}" name="STATUS" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{539417AD-B8A4-4898-AB74-66F05A603AF4}" name="MUNICIPIO" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{235BE65E-B850-4BB7-8E87-322FA0E9FAE2}" name="EMPRESA" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}" name="TBL_AUX_COMISSAO" displayName="TBL_AUX_COMISSAO" ref="A1:F130" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}" name="TBL_AUX_COMISSAO" displayName="TBL_AUX_COMISSAO" ref="A1:F130" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
   <autoFilter ref="A1:F130" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F121">
     <sortCondition ref="A1:A124"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6940CE63-D3EF-4410-99DC-5338DACC9347}" name="SEI" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{BC273B88-930A-4795-B862-FBC8E6F6BDFE}" name="GESTOR" dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{6940CE63-D3EF-4410-99DC-5338DACC9347}" name="SEI" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{BC273B88-930A-4795-B862-FBC8E6F6BDFE}" name="GESTOR" dataDxfId="53">
       <calculatedColumnFormula>UPPER(TRIM(UPPER(IFERROR(VLOOKUP(A2,INDIRECT("'BAIXADA'!$B$3:$I$51"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'NORTE'!$B$3:$I$21"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'SUL'!$B$3:$I$31"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'CONTIGENCIA'!$B$3:$I$22"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'ESPECIAIS'!$B$3:$I$27"),3,FALSE),""))))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2DD541AF-D366-4FA1-934F-2D706DEB3424}" name="REGIAO" dataDxfId="3">
+    <tableColumn id="3" xr3:uid="{2DD541AF-D366-4FA1-934F-2D706DEB3424}" name="REGIAO" dataDxfId="52">
       <calculatedColumnFormula>IF(OR(B2="CARLOS FERNANDES", B2="GISELLE G. FONSECA"), "BAIXADA",
  IF(OR(B2="ISADORA ROSALINO", B2="JEHNIFFER PIRES"), "NORTE",
  IF(OR(B2="LUIZ FILHO", B2="MARCUS", B2="JAQUELINE PASTÓRIO"), "SUL",
  IF(OR(B2="AIMAR FILHO", B2="ERICK HYLARIO", B2="IGOR CARNEIRO", B2="CESAR", B2="DANRLEI"), "ESPECIAIS",""))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{48CC14BF-DA39-4E7A-9D30-3BF4E557740A}" name="Coluna1" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{73F6C358-23B2-4118-8542-3EF0D7731680}" name="STATUS" dataDxfId="1">
+    <tableColumn id="4" xr3:uid="{48CC14BF-DA39-4E7A-9D30-3BF4E557740A}" name="Coluna1" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{73F6C358-23B2-4118-8542-3EF0D7731680}" name="STATUS" dataDxfId="50">
       <calculatedColumnFormula>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela59[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{42155D96-D90A-49EF-9ADB-3B70FF87E628}" name="LOCAL" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{42155D96-D90A-49EF-9ADB-3B70FF87E628}" name="LOCAL" dataDxfId="49">
       <calculatedColumnFormula>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A2),COUNTIF(NORTE!B:B,A2),COUNTIF(SUL!B:B,A2))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A2)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A2)&gt;0,"ESPECIAIS",""))))</calculatedColumnFormula>
     </tableColumn>

--- a/COMISSÕES POR REGIAO.xlsx
+++ b/COMISSÕES POR REGIAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APRENDIZADO APP\MEDICOES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DA6965-B007-4887-9F66-C37BBF2766C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5795CA9D-B525-4ADE-BCB8-D3ABFF8BB97C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" xr2:uid="{8E7E61FA-AA35-49DA-A0A0-B5261C3AB08E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" activeTab="5" xr2:uid="{8E7E61FA-AA35-49DA-A0A0-B5261C3AB08E}"/>
   </bookViews>
   <sheets>
     <sheet name="BAIXADA" sheetId="1" r:id="rId1"/>
@@ -2605,6 +2605,231 @@
   </cellStyles>
   <dxfs count="61">
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -3880,231 +4105,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -4147,131 +4147,125 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}" name="TBL_BAIXADA" displayName="TBL_BAIXADA" ref="B2:G51" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45" totalsRowBorderDxfId="44">
-  <autoFilter ref="B2:G51" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="CARLOS FERNANDES"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}" name="TBL_BAIXADA" displayName="TBL_BAIXADA" ref="B2:G51" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
+  <autoFilter ref="B2:G51" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G50">
     <sortCondition ref="D2:D50"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="2" xr3:uid="{019F32D2-C233-43C9-9576-4AE595F1C1BA}" name="SEI" dataDxfId="43"/>
-    <tableColumn id="1" xr3:uid="{AEDA410C-7924-46EC-AEAB-7AE262BECCD2}" name="FISCAL NOMEADO" dataDxfId="42"/>
-    <tableColumn id="7" xr3:uid="{19466E79-BFE7-4E2E-A742-DD97531E2EF3}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="41"/>
-    <tableColumn id="3" xr3:uid="{7880C9F9-C6BC-479F-9DA9-E17F6116251F}" name="STATUS" dataDxfId="40"/>
-    <tableColumn id="4" xr3:uid="{DA47CCE5-2317-4B1E-8640-27A34A02D8B9}" name="MUNICIPIO" dataDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{DCC92333-101D-46D3-9AB3-309FAD98BBFB}" name="EMPRESA" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{019F32D2-C233-43C9-9576-4AE595F1C1BA}" name="SEI" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{AEDA410C-7924-46EC-AEAB-7AE262BECCD2}" name="FISCAL NOMEADO" dataDxfId="53"/>
+    <tableColumn id="7" xr3:uid="{19466E79-BFE7-4E2E-A742-DD97531E2EF3}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{7880C9F9-C6BC-479F-9DA9-E17F6116251F}" name="STATUS" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{DA47CCE5-2317-4B1E-8640-27A34A02D8B9}" name="MUNICIPIO" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{DCC92333-101D-46D3-9AB3-309FAD98BBFB}" name="EMPRESA" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}" name="Tabela2" displayName="Tabela2" ref="B2:G21" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36" tableBorderDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}" name="Tabela2" displayName="Tabela2" ref="B2:G21" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47" tableBorderDxfId="46">
   <autoFilter ref="B2:G21" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G20">
     <sortCondition ref="D2:D20"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{16E9EBD3-F35D-4598-A9F2-0A4D20432CE9}" name="SEI" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{E30337A4-09C3-4048-9E77-97431DB2FF42}" name="FISCAL NOMEADO" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{E188BB43-7D82-4633-A725-9027F38B6D00}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="32"/>
-    <tableColumn id="4" xr3:uid="{8E3CCA43-C0CA-43A2-BFF6-C18CE15835DE}" name="STATUS" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{4BDB1FC4-3FA9-4D47-842C-749A9777B396}" name="MUNICIPIO" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{080468F4-AE50-4958-86EA-366972343A8C}" name="EMPRESA" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{16E9EBD3-F35D-4598-A9F2-0A4D20432CE9}" name="SEI" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{E30337A4-09C3-4048-9E77-97431DB2FF42}" name="FISCAL NOMEADO" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{E188BB43-7D82-4633-A725-9027F38B6D00}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{8E3CCA43-C0CA-43A2-BFF6-C18CE15835DE}" name="STATUS" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{4BDB1FC4-3FA9-4D47-842C-749A9777B396}" name="MUNICIPIO" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{080468F4-AE50-4958-86EA-366972343A8C}" name="EMPRESA" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B825E509-0D21-4897-AEA1-45396A5B8904}" name="Tabela3" displayName="Tabela3" ref="B2:G31" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27" tableBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B825E509-0D21-4897-AEA1-45396A5B8904}" name="Tabela3" displayName="Tabela3" ref="B2:G31" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38" tableBorderDxfId="37">
   <autoFilter ref="B2:G31" xr:uid="{B825E509-0D21-4897-AEA1-45396A5B8904}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G31">
     <sortCondition ref="D2:D31"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{AF3D376D-5669-42C7-85B7-D133DE0C7C9F}" name="SEI" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{51805C44-CC05-4045-9BCE-C493679844E5}" name="FISCAL NOMEADO" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{5E18CB63-80F1-40CE-AC25-4FF6D6C56801}" name="GESTOR(A) ATUANTE" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{8A899838-F31E-4B62-AD60-CACBA61F7301}" name="STATUS" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{A189C6A4-301D-4BC4-893D-C571D3C65C4F}" name="MUNICIPIO" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{1FE96F05-55E0-47E2-950A-C4FE6590F71E}" name="EMPRESA" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{AF3D376D-5669-42C7-85B7-D133DE0C7C9F}" name="SEI" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{51805C44-CC05-4045-9BCE-C493679844E5}" name="FISCAL NOMEADO" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{5E18CB63-80F1-40CE-AC25-4FF6D6C56801}" name="GESTOR(A) ATUANTE" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{8A899838-F31E-4B62-AD60-CACBA61F7301}" name="STATUS" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{A189C6A4-301D-4BC4-893D-C571D3C65C4F}" name="MUNICIPIO" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{1FE96F05-55E0-47E2-950A-C4FE6590F71E}" name="EMPRESA" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{07EEB8F3-2A08-4F77-A71A-F14F310E745B}" name="Tabela59" displayName="Tabela59" ref="B2:G21" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{07EEB8F3-2A08-4F77-A71A-F14F310E745B}" name="Tabela59" displayName="Tabela59" ref="B2:G21" totalsRowShown="0" headerRowDxfId="30" headerRowBorderDxfId="29" tableBorderDxfId="28" totalsRowBorderDxfId="27">
   <autoFilter ref="B2:G21" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:G10">
     <sortCondition ref="D2:D21"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{1B0B707C-42D7-439C-BC86-F2074086CDFA}" name="SEI" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{E4E4A98E-5F6A-4D1A-BF5C-90DB3AF4D029}" name="FISCAL NOMEADO" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{3F530A0F-746C-40A5-87E4-3EF4BC754B35}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{6289C995-291C-4CD2-9F38-F7B7C1C4C572}" name="STATUS" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{C32C9B37-692D-406F-BC6A-231C43E51674}" name="MUNICIPIO" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{AEFC288F-DB80-4821-8DAC-8848204495B7}" name="EMPRESA" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{1B0B707C-42D7-439C-BC86-F2074086CDFA}" name="SEI" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{E4E4A98E-5F6A-4D1A-BF5C-90DB3AF4D029}" name="FISCAL NOMEADO" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{3F530A0F-746C-40A5-87E4-3EF4BC754B35}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{6289C995-291C-4CD2-9F38-F7B7C1C4C572}" name="STATUS" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{C32C9B37-692D-406F-BC6A-231C43E51674}" name="MUNICIPIO" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{AEFC288F-DB80-4821-8DAC-8848204495B7}" name="EMPRESA" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}" name="Tabela5" displayName="Tabela5" ref="B2:G27" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}" name="Tabela5" displayName="Tabela5" ref="B2:G27" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
   <autoFilter ref="B2:G27" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:G23">
     <sortCondition ref="D2:D26"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8FECF49A-25BA-405F-A561-286D71FB284B}" name="SEI" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{88A1DC3F-1E69-48FA-B7AB-F895C771F55E}" name="FISCAL NOMEADO" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{B977B564-9125-4E72-A174-DD668115187D}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{6A4D0185-1909-4BA9-A2C1-58CDBA8CD45C}" name="STATUS" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{539417AD-B8A4-4898-AB74-66F05A603AF4}" name="MUNICIPIO" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{235BE65E-B850-4BB7-8E87-322FA0E9FAE2}" name="EMPRESA" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{8FECF49A-25BA-405F-A561-286D71FB284B}" name="SEI" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{88A1DC3F-1E69-48FA-B7AB-F895C771F55E}" name="FISCAL NOMEADO" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{B977B564-9125-4E72-A174-DD668115187D}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{6A4D0185-1909-4BA9-A2C1-58CDBA8CD45C}" name="STATUS" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{539417AD-B8A4-4898-AB74-66F05A603AF4}" name="MUNICIPIO" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{235BE65E-B850-4BB7-8E87-322FA0E9FAE2}" name="EMPRESA" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}" name="TBL_AUX_COMISSAO" displayName="TBL_AUX_COMISSAO" ref="A1:F130" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}" name="TBL_AUX_COMISSAO" displayName="TBL_AUX_COMISSAO" ref="A1:F130" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="A1:F130" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F121">
     <sortCondition ref="A1:A124"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6940CE63-D3EF-4410-99DC-5338DACC9347}" name="SEI" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{BC273B88-930A-4795-B862-FBC8E6F6BDFE}" name="GESTOR" dataDxfId="53">
+    <tableColumn id="1" xr3:uid="{6940CE63-D3EF-4410-99DC-5338DACC9347}" name="SEI" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{BC273B88-930A-4795-B862-FBC8E6F6BDFE}" name="GESTOR" dataDxfId="4">
       <calculatedColumnFormula>UPPER(TRIM(UPPER(IFERROR(VLOOKUP(A2,INDIRECT("'BAIXADA'!$B$3:$I$51"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'NORTE'!$B$3:$I$21"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'SUL'!$B$3:$I$31"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'CONTIGENCIA'!$B$3:$I$22"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'ESPECIAIS'!$B$3:$I$27"),3,FALSE),""))))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2DD541AF-D366-4FA1-934F-2D706DEB3424}" name="REGIAO" dataDxfId="52">
+    <tableColumn id="3" xr3:uid="{2DD541AF-D366-4FA1-934F-2D706DEB3424}" name="REGIAO" dataDxfId="3">
       <calculatedColumnFormula>IF(OR(B2="CARLOS FERNANDES", B2="GISELLE G. FONSECA"), "BAIXADA",
  IF(OR(B2="ISADORA ROSALINO", B2="JEHNIFFER PIRES"), "NORTE",
  IF(OR(B2="LUIZ FILHO", B2="MARCUS", B2="JAQUELINE PASTÓRIO"), "SUL",
  IF(OR(B2="AIMAR FILHO", B2="ERICK HYLARIO", B2="IGOR CARNEIRO", B2="CESAR", B2="DANRLEI"), "ESPECIAIS",""))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{48CC14BF-DA39-4E7A-9D30-3BF4E557740A}" name="Coluna1" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{73F6C358-23B2-4118-8542-3EF0D7731680}" name="STATUS" dataDxfId="50">
+    <tableColumn id="4" xr3:uid="{48CC14BF-DA39-4E7A-9D30-3BF4E557740A}" name="Coluna1" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{73F6C358-23B2-4118-8542-3EF0D7731680}" name="STATUS" dataDxfId="1">
       <calculatedColumnFormula>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela59[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{42155D96-D90A-49EF-9ADB-3B70FF87E628}" name="LOCAL" dataDxfId="49">
+    <tableColumn id="6" xr3:uid="{42155D96-D90A-49EF-9ADB-3B70FF87E628}" name="LOCAL" dataDxfId="0">
       <calculatedColumnFormula>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A2),COUNTIF(NORTE!B:B,A2),COUNTIF(SUL!B:B,A2))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A2)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A2)&gt;0,"ESPECIAIS",""))))</calculatedColumnFormula>
     </tableColumn>
@@ -4645,7 +4639,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4668,7 +4662,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -4714,7 +4708,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4829,7 +4823,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -4921,7 +4915,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -4967,7 +4961,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -5013,7 +5007,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -5036,7 +5030,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -5082,7 +5076,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -5174,7 +5168,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -5243,7 +5237,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -5312,7 +5306,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -5335,7 +5329,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -5381,7 +5375,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -5427,7 +5421,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -5473,7 +5467,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -5496,7 +5490,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -5542,7 +5536,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -5565,7 +5559,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -5588,7 +5582,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -5611,7 +5605,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -5634,7 +5628,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -5657,7 +5651,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -5680,7 +5674,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -5703,7 +5697,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -5726,7 +5720,6 @@
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="59" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="G59" s="72"/>
     </row>
@@ -7261,7 +7254,7 @@
       <c r="C11" s="95" t="s">
         <v>299</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="27" t="s">
         <v>303</v>
       </c>
       <c r="E11" s="32" t="s">

--- a/COMISSÕES POR REGIAO.xlsx
+++ b/COMISSÕES POR REGIAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APRENDIZADO APP\MEDICOES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5795CA9D-B525-4ADE-BCB8-D3ABFF8BB97C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5068CF-1443-4BAD-B131-756089F456B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" activeTab="5" xr2:uid="{8E7E61FA-AA35-49DA-A0A0-B5261C3AB08E}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" activeTab="5" xr2:uid="{8E7E61FA-AA35-49DA-A0A0-B5261C3AB08E}"/>
   </bookViews>
   <sheets>
     <sheet name="BAIXADA" sheetId="1" r:id="rId1"/>
@@ -21,14 +21,15 @@
     <sheet name="AUXILIAR" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela111" hidden="1">Tabela11</definedName>
-    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela141" hidden="1">Tabela14</definedName>
-    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela61" hidden="1">Tabela6</definedName>
+    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela11" hidden="1">Tabela11</definedName>
+    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela14" hidden="1">Tabela14</definedName>
+    <definedName name="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela6" hidden="1">Tabela6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">BAIXADA!$B$1:$G$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">NORTE!$B$1:$G$23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">SUL!$B$1:$F$32</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -286,7 +287,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Tabela11">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela111"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela11"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -295,7 +296,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Tabela14">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela141"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela14"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -304,7 +305,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Tabela6" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela61"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_COMISSÕESPORREGIAO.xlsxTabela6"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -2605,231 +2606,6 @@
   </cellStyles>
   <dxfs count="61">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -4105,6 +3881,231 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -4147,125 +4148,125 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}" name="TBL_BAIXADA" displayName="TBL_BAIXADA" ref="B2:G51" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}" name="TBL_BAIXADA" displayName="TBL_BAIXADA" ref="B2:G51" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45" totalsRowBorderDxfId="44">
   <autoFilter ref="B2:G51" xr:uid="{CFDE9F92-1D33-4C15-B30C-5BE6DD19725A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G50">
     <sortCondition ref="D2:D50"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="2" xr3:uid="{019F32D2-C233-43C9-9576-4AE595F1C1BA}" name="SEI" dataDxfId="54"/>
-    <tableColumn id="1" xr3:uid="{AEDA410C-7924-46EC-AEAB-7AE262BECCD2}" name="FISCAL NOMEADO" dataDxfId="53"/>
-    <tableColumn id="7" xr3:uid="{19466E79-BFE7-4E2E-A742-DD97531E2EF3}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{7880C9F9-C6BC-479F-9DA9-E17F6116251F}" name="STATUS" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{DA47CCE5-2317-4B1E-8640-27A34A02D8B9}" name="MUNICIPIO" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{DCC92333-101D-46D3-9AB3-309FAD98BBFB}" name="EMPRESA" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{019F32D2-C233-43C9-9576-4AE595F1C1BA}" name="SEI" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{AEDA410C-7924-46EC-AEAB-7AE262BECCD2}" name="FISCAL NOMEADO" dataDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{19466E79-BFE7-4E2E-A742-DD97531E2EF3}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{7880C9F9-C6BC-479F-9DA9-E17F6116251F}" name="STATUS" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{DA47CCE5-2317-4B1E-8640-27A34A02D8B9}" name="MUNICIPIO" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{DCC92333-101D-46D3-9AB3-309FAD98BBFB}" name="EMPRESA" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}" name="Tabela2" displayName="Tabela2" ref="B2:G21" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47" tableBorderDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}" name="Tabela2" displayName="Tabela2" ref="B2:G21" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36" tableBorderDxfId="35">
   <autoFilter ref="B2:G21" xr:uid="{509282A1-F554-47CE-B1A2-7ECB428E2CEF}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G20">
     <sortCondition ref="D2:D20"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{16E9EBD3-F35D-4598-A9F2-0A4D20432CE9}" name="SEI" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{E30337A4-09C3-4048-9E77-97431DB2FF42}" name="FISCAL NOMEADO" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{E188BB43-7D82-4633-A725-9027F38B6D00}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{8E3CCA43-C0CA-43A2-BFF6-C18CE15835DE}" name="STATUS" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{4BDB1FC4-3FA9-4D47-842C-749A9777B396}" name="MUNICIPIO" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{080468F4-AE50-4958-86EA-366972343A8C}" name="EMPRESA" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{16E9EBD3-F35D-4598-A9F2-0A4D20432CE9}" name="SEI" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{E30337A4-09C3-4048-9E77-97431DB2FF42}" name="FISCAL NOMEADO" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{E188BB43-7D82-4633-A725-9027F38B6D00}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{8E3CCA43-C0CA-43A2-BFF6-C18CE15835DE}" name="STATUS" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{4BDB1FC4-3FA9-4D47-842C-749A9777B396}" name="MUNICIPIO" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{080468F4-AE50-4958-86EA-366972343A8C}" name="EMPRESA" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B825E509-0D21-4897-AEA1-45396A5B8904}" name="Tabela3" displayName="Tabela3" ref="B2:G31" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38" tableBorderDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B825E509-0D21-4897-AEA1-45396A5B8904}" name="Tabela3" displayName="Tabela3" ref="B2:G31" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27" tableBorderDxfId="26">
   <autoFilter ref="B2:G31" xr:uid="{B825E509-0D21-4897-AEA1-45396A5B8904}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G31">
     <sortCondition ref="D2:D31"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{AF3D376D-5669-42C7-85B7-D133DE0C7C9F}" name="SEI" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{51805C44-CC05-4045-9BCE-C493679844E5}" name="FISCAL NOMEADO" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{5E18CB63-80F1-40CE-AC25-4FF6D6C56801}" name="GESTOR(A) ATUANTE" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{8A899838-F31E-4B62-AD60-CACBA61F7301}" name="STATUS" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{A189C6A4-301D-4BC4-893D-C571D3C65C4F}" name="MUNICIPIO" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{1FE96F05-55E0-47E2-950A-C4FE6590F71E}" name="EMPRESA" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{AF3D376D-5669-42C7-85B7-D133DE0C7C9F}" name="SEI" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{51805C44-CC05-4045-9BCE-C493679844E5}" name="FISCAL NOMEADO" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{5E18CB63-80F1-40CE-AC25-4FF6D6C56801}" name="GESTOR(A) ATUANTE" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{8A899838-F31E-4B62-AD60-CACBA61F7301}" name="STATUS" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{A189C6A4-301D-4BC4-893D-C571D3C65C4F}" name="MUNICIPIO" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{1FE96F05-55E0-47E2-950A-C4FE6590F71E}" name="EMPRESA" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{07EEB8F3-2A08-4F77-A71A-F14F310E745B}" name="Tabela59" displayName="Tabela59" ref="B2:G21" totalsRowShown="0" headerRowDxfId="30" headerRowBorderDxfId="29" tableBorderDxfId="28" totalsRowBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{07EEB8F3-2A08-4F77-A71A-F14F310E745B}" name="Tabela59" displayName="Tabela59" ref="B2:G21" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
   <autoFilter ref="B2:G21" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:G10">
     <sortCondition ref="D2:D21"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{1B0B707C-42D7-439C-BC86-F2074086CDFA}" name="SEI" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{E4E4A98E-5F6A-4D1A-BF5C-90DB3AF4D029}" name="FISCAL NOMEADO" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{3F530A0F-746C-40A5-87E4-3EF4BC754B35}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{6289C995-291C-4CD2-9F38-F7B7C1C4C572}" name="STATUS" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{C32C9B37-692D-406F-BC6A-231C43E51674}" name="MUNICIPIO" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{AEFC288F-DB80-4821-8DAC-8848204495B7}" name="EMPRESA" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{1B0B707C-42D7-439C-BC86-F2074086CDFA}" name="SEI" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{E4E4A98E-5F6A-4D1A-BF5C-90DB3AF4D029}" name="FISCAL NOMEADO" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{3F530A0F-746C-40A5-87E4-3EF4BC754B35}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{6289C995-291C-4CD2-9F38-F7B7C1C4C572}" name="STATUS" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{C32C9B37-692D-406F-BC6A-231C43E51674}" name="MUNICIPIO" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{AEFC288F-DB80-4821-8DAC-8848204495B7}" name="EMPRESA" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}" name="Tabela5" displayName="Tabela5" ref="B2:G27" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}" name="Tabela5" displayName="Tabela5" ref="B2:G27" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="B2:G27" xr:uid="{230F5E5D-9A04-4FBE-BFDF-7F11F0AC71C0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:G23">
     <sortCondition ref="D2:D26"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8FECF49A-25BA-405F-A561-286D71FB284B}" name="SEI" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{88A1DC3F-1E69-48FA-B7AB-F895C771F55E}" name="FISCAL NOMEADO" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{B977B564-9125-4E72-A174-DD668115187D}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{6A4D0185-1909-4BA9-A2C1-58CDBA8CD45C}" name="STATUS" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{539417AD-B8A4-4898-AB74-66F05A603AF4}" name="MUNICIPIO" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{235BE65E-B850-4BB7-8E87-322FA0E9FAE2}" name="EMPRESA" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{8FECF49A-25BA-405F-A561-286D71FB284B}" name="SEI" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{88A1DC3F-1E69-48FA-B7AB-F895C771F55E}" name="FISCAL NOMEADO" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{B977B564-9125-4E72-A174-DD668115187D}" name="GESTOR(A)_x000a_ATUANTE" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{6A4D0185-1909-4BA9-A2C1-58CDBA8CD45C}" name="STATUS" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{539417AD-B8A4-4898-AB74-66F05A603AF4}" name="MUNICIPIO" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{235BE65E-B850-4BB7-8E87-322FA0E9FAE2}" name="EMPRESA" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}" name="TBL_AUX_COMISSAO" displayName="TBL_AUX_COMISSAO" ref="A1:F130" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}" name="TBL_AUX_COMISSAO" displayName="TBL_AUX_COMISSAO" ref="A1:F130" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
   <autoFilter ref="A1:F130" xr:uid="{219523AD-7502-4955-9305-1317053F81AC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F121">
     <sortCondition ref="A1:A124"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6940CE63-D3EF-4410-99DC-5338DACC9347}" name="SEI" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{BC273B88-930A-4795-B862-FBC8E6F6BDFE}" name="GESTOR" dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{6940CE63-D3EF-4410-99DC-5338DACC9347}" name="SEI" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{BC273B88-930A-4795-B862-FBC8E6F6BDFE}" name="GESTOR" dataDxfId="53">
       <calculatedColumnFormula>UPPER(TRIM(UPPER(IFERROR(VLOOKUP(A2,INDIRECT("'BAIXADA'!$B$3:$I$51"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'NORTE'!$B$3:$I$21"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'SUL'!$B$3:$I$31"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'CONTIGENCIA'!$B$3:$I$22"),3,FALSE),
 IFERROR(VLOOKUP(A2,INDIRECT("'ESPECIAIS'!$B$3:$I$27"),3,FALSE),""))))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2DD541AF-D366-4FA1-934F-2D706DEB3424}" name="REGIAO" dataDxfId="3">
+    <tableColumn id="3" xr3:uid="{2DD541AF-D366-4FA1-934F-2D706DEB3424}" name="REGIAO" dataDxfId="52">
       <calculatedColumnFormula>IF(OR(B2="CARLOS FERNANDES", B2="GISELLE G. FONSECA"), "BAIXADA",
  IF(OR(B2="ISADORA ROSALINO", B2="JEHNIFFER PIRES"), "NORTE",
  IF(OR(B2="LUIZ FILHO", B2="MARCUS", B2="JAQUELINE PASTÓRIO"), "SUL",
  IF(OR(B2="AIMAR FILHO", B2="ERICK HYLARIO", B2="IGOR CARNEIRO", B2="CESAR", B2="DANRLEI"), "ESPECIAIS",""))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{48CC14BF-DA39-4E7A-9D30-3BF4E557740A}" name="Coluna1" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{73F6C358-23B2-4118-8542-3EF0D7731680}" name="STATUS" dataDxfId="1">
+    <tableColumn id="4" xr3:uid="{48CC14BF-DA39-4E7A-9D30-3BF4E557740A}" name="Coluna1" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{73F6C358-23B2-4118-8542-3EF0D7731680}" name="STATUS" dataDxfId="50">
       <calculatedColumnFormula>UPPER(TRIM(IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], TBL_BAIXADA[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela2[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela3[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela59[[SEI]:[STATUS]],4,FALSE),
  IFERROR(VLOOKUP(TBL_AUX_COMISSAO[[#This Row],[SEI]], Tabela5[[SEI]:[STATUS]],4,FALSE),"Valor não encontrado")))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{42155D96-D90A-49EF-9ADB-3B70FF87E628}" name="LOCAL" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{42155D96-D90A-49EF-9ADB-3B70FF87E628}" name="LOCAL" dataDxfId="49">
       <calculatedColumnFormula>UPPER(IF(SUM(COUNTIF(BAIXADA!B:B,A2),COUNTIF(NORTE!B:B,A2),COUNTIF(SUL!B:B,A2))&gt;0,"CIVIS",
 IF(COUNTIF(CONTIGENCIA!B:B,A2)&gt;0,"CONTINGENCIA",IF(COUNTIF(ESPECIAIS!B:B,A2)&gt;0,"ESPECIAIS",""))))</calculatedColumnFormula>
     </tableColumn>
